--- a/jogos_2025-09-18.xlsx
+++ b/jogos_2025-09-18.xlsx
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>4.5</v>
+        <v>3.35</v>
       </c>
       <c r="M18" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="N18" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2772,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.35</v>
+        <v>4.5</v>
       </c>
       <c r="M19" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="N19" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.25</v>
+        <v>1.65</v>
       </c>
       <c r="M24" t="n">
-        <v>6</v>
+        <v>3.95</v>
       </c>
       <c r="N24" t="n">
-        <v>11</v>
+        <v>5.3</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,16 +3546,16 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Z24" t="n">
         <v>2.35</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.55</v>
+        <v>1.25</v>
       </c>
       <c r="M25" t="n">
-        <v>3.85</v>
+        <v>6</v>
       </c>
       <c r="N25" t="n">
-        <v>1.95</v>
+        <v>11</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,16 +3675,16 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.65</v>
+        <v>3.55</v>
       </c>
       <c r="M26" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="N26" t="n">
-        <v>5.3</v>
+        <v>1.95</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,16 +3804,16 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.35</v>
+        <v>2.7</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>

--- a/jogos_2025-09-18.xlsx
+++ b/jogos_2025-09-18.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.8</v>
+        <v>1.25</v>
       </c>
       <c r="M23" t="n">
-        <v>3.65</v>
+        <v>6</v>
       </c>
       <c r="N23" t="n">
-        <v>4.5</v>
+        <v>11</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,16 +3417,16 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="Z23" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA23" t="n">
         <v>2.25</v>
       </c>
-      <c r="AA23" t="n">
-        <v>0</v>
-      </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.25</v>
+        <v>1.8</v>
       </c>
       <c r="M25" t="n">
-        <v>6</v>
+        <v>3.65</v>
       </c>
       <c r="N25" t="n">
-        <v>11</v>
+        <v>4.5</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,16 +3675,16 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G28" t="n">

--- a/jogos_2025-09-18.xlsx
+++ b/jogos_2025-09-18.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.35</v>
+        <v>4.5</v>
       </c>
       <c r="M18" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="N18" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2772,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>4.5</v>
+        <v>3.35</v>
       </c>
       <c r="M19" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="N19" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.25</v>
+        <v>3.55</v>
       </c>
       <c r="M23" t="n">
-        <v>6</v>
+        <v>3.85</v>
       </c>
       <c r="N23" t="n">
-        <v>11</v>
+        <v>1.95</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,16 +3417,16 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.35</v>
+        <v>2.7</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.65</v>
+        <v>1.25</v>
       </c>
       <c r="M24" t="n">
-        <v>3.95</v>
+        <v>6</v>
       </c>
       <c r="N24" t="n">
-        <v>5.3</v>
+        <v>11</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,16 +3546,16 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="Z24" t="n">
         <v>2.35</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="M25" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="N25" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.55</v>
+        <v>1.8</v>
       </c>
       <c r="M26" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="N26" t="n">
-        <v>1.95</v>
+        <v>4.5</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,16 +3804,16 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.45</v>
+        <v>1.63</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.7</v>
+        <v>2.25</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G28" t="n">

--- a/jogos_2025-09-18.xlsx
+++ b/jogos_2025-09-18.xlsx
@@ -628,27 +628,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -748,7 +748,7 @@
         <v>0</v>
       </c>
       <c r="AK2" s="3" t="n">
-        <v>45918.4375</v>
+        <v>45918.25</v>
       </c>
     </row>
     <row r="3">
@@ -886,12 +886,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1006,7 +1006,7 @@
         <v>0</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>45918.45833333334</v>
+        <v>45918.4375</v>
       </c>
     </row>
     <row r="5">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1181,65 +1181,65 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4.68</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>4.66</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,19 +1252,19 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45918.47916666666</v>
+        <v>45918.45833333334</v>
       </c>
     </row>
     <row r="7">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1310,65 +1310,65 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>4.66</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,19 +1381,19 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45918.5</v>
+        <v>45918.47916666666</v>
       </c>
     </row>
     <row r="8">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>

--- a/jogos_2025-09-18.xlsx
+++ b/jogos_2025-09-18.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.25</v>
+        <v>1.8</v>
       </c>
       <c r="M24" t="n">
-        <v>6</v>
+        <v>3.65</v>
       </c>
       <c r="N24" t="n">
-        <v>11</v>
+        <v>4.5</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,16 +3546,16 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.65</v>
+        <v>1.25</v>
       </c>
       <c r="M25" t="n">
-        <v>3.95</v>
+        <v>6</v>
       </c>
       <c r="N25" t="n">
-        <v>5.3</v>
+        <v>11</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,16 +3675,16 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="Z25" t="n">
         <v>2.35</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="M26" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="N26" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>

--- a/jogos_2025-09-18.xlsx
+++ b/jogos_2025-09-18.xlsx
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>4.5</v>
+        <v>3.35</v>
       </c>
       <c r="M18" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="N18" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2772,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.35</v>
+        <v>4.5</v>
       </c>
       <c r="M19" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="N19" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.55</v>
+        <v>1.25</v>
       </c>
       <c r="M23" t="n">
-        <v>3.85</v>
+        <v>6</v>
       </c>
       <c r="N23" t="n">
-        <v>1.95</v>
+        <v>11</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,16 +3417,16 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.25</v>
+        <v>1.65</v>
       </c>
       <c r="M25" t="n">
-        <v>6</v>
+        <v>3.95</v>
       </c>
       <c r="N25" t="n">
-        <v>11</v>
+        <v>5.3</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,16 +3675,16 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Z25" t="n">
         <v>2.35</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.65</v>
+        <v>3.55</v>
       </c>
       <c r="M26" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="N26" t="n">
-        <v>5.3</v>
+        <v>1.95</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,16 +3804,16 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.35</v>
+        <v>2.7</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>

--- a/jogos_2025-09-18.xlsx
+++ b/jogos_2025-09-18.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK31"/>
+  <dimension ref="A1:AK32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45918.52777777778</v>
+        <v>45918.5</v>
       </c>
     </row>
     <row r="17">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2772,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45918.57291666666</v>
+        <v>45918.52777777778</v>
       </c>
     </row>
     <row r="19">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>4.5</v>
+        <v>3.35</v>
       </c>
       <c r="M19" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="N19" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45918.58333333334</v>
+        <v>45918.57291666666</v>
       </c>
     </row>
     <row r="21">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45918.625</v>
+        <v>45918.58333333334</v>
       </c>
     </row>
     <row r="23">
@@ -3337,12 +3337,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,16 +3417,16 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45918.66666666666</v>
+        <v>45918.625</v>
       </c>
     </row>
     <row r="24">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="M24" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="N24" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.65</v>
+        <v>3.55</v>
       </c>
       <c r="M25" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="N25" t="n">
-        <v>5.3</v>
+        <v>1.95</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,16 +3675,16 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.35</v>
+        <v>2.7</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.55</v>
+        <v>1.8</v>
       </c>
       <c r="M26" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="N26" t="n">
-        <v>1.95</v>
+        <v>4.5</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,16 +3804,16 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.45</v>
+        <v>1.63</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.7</v>
+        <v>2.25</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3853,27 +3853,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,16 +3933,16 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
-        <v>45918.79166666666</v>
+        <v>45918.66666666666</v>
       </c>
     </row>
     <row r="28">
@@ -4111,12 +4111,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>45918.85416666666</v>
+        <v>45918.79166666666</v>
       </c>
     </row>
     <row r="30">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4360,7 +4360,7 @@
         <v>0</v>
       </c>
       <c r="AK30" s="3" t="n">
-        <v>45918.89583333334</v>
+        <v>45918.85416666666</v>
       </c>
     </row>
     <row r="31">
@@ -4369,126 +4369,255 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>South America Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Estudiantes</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N31" t="n">
+        <v>13</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK31" s="3" t="n">
+        <v>45918.89583333334</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>45918</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
           <t>23:30</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>Angel City</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>Washington Spirit</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="inlineStr">
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK31" s="3" t="n">
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK32" s="3" t="n">
         <v>45918.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-09-18.xlsx
+++ b/jogos_2025-09-18.xlsx
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.65</v>
+        <v>3.55</v>
       </c>
       <c r="M24" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="N24" t="n">
-        <v>5.3</v>
+        <v>1.95</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,16 +3546,16 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.35</v>
+        <v>2.7</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.55</v>
+        <v>1.25</v>
       </c>
       <c r="M25" t="n">
-        <v>3.85</v>
+        <v>6</v>
       </c>
       <c r="N25" t="n">
-        <v>1.95</v>
+        <v>11</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,16 +3675,16 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="M26" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="N26" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.25</v>
+        <v>1.8</v>
       </c>
       <c r="M27" t="n">
-        <v>6</v>
+        <v>3.65</v>
       </c>
       <c r="N27" t="n">
-        <v>11</v>
+        <v>4.5</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,16 +3933,16 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>

--- a/jogos_2025-09-18.xlsx
+++ b/jogos_2025-09-18.xlsx
@@ -628,27 +628,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -748,7 +748,7 @@
         <v>0</v>
       </c>
       <c r="AK2" s="3" t="n">
-        <v>45918.25</v>
+        <v>45918.4375</v>
       </c>
     </row>
     <row r="3">
@@ -886,12 +886,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1006,7 +1006,7 @@
         <v>0</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>45918.4375</v>
+        <v>45918.45833333334</v>
       </c>
     </row>
     <row r="5">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1181,65 +1181,65 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>4.66</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,19 +1252,19 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45918.45833333334</v>
+        <v>45918.47916666666</v>
       </c>
     </row>
     <row r="7">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1310,65 +1310,65 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4.68</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>4.66</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,19 +1381,19 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45918.47916666666</v>
+        <v>45918.5</v>
       </c>
     </row>
     <row r="8">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.25</v>
+        <v>1.8</v>
       </c>
       <c r="M25" t="n">
-        <v>6</v>
+        <v>3.65</v>
       </c>
       <c r="N25" t="n">
-        <v>11</v>
+        <v>4.5</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,16 +3675,16 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.65</v>
+        <v>1.25</v>
       </c>
       <c r="M26" t="n">
-        <v>3.95</v>
+        <v>6</v>
       </c>
       <c r="N26" t="n">
-        <v>5.3</v>
+        <v>11</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,16 +3804,16 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="Z26" t="n">
         <v>2.35</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="M27" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="N27" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>

--- a/jogos_2025-09-18.xlsx
+++ b/jogos_2025-09-18.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.55</v>
+        <v>1.65</v>
       </c>
       <c r="M24" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="N24" t="n">
-        <v>1.95</v>
+        <v>5.3</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,16 +3546,16 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.8</v>
+        <v>3.55</v>
       </c>
       <c r="M25" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="N25" t="n">
-        <v>4.5</v>
+        <v>1.95</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,16 +3675,16 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.63</v>
+        <v>1.45</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.25</v>
+        <v>1.8</v>
       </c>
       <c r="M26" t="n">
-        <v>6</v>
+        <v>3.65</v>
       </c>
       <c r="N26" t="n">
-        <v>11</v>
+        <v>4.5</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,16 +3804,16 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.65</v>
+        <v>1.25</v>
       </c>
       <c r="M27" t="n">
-        <v>3.95</v>
+        <v>6</v>
       </c>
       <c r="N27" t="n">
-        <v>5.3</v>
+        <v>11</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,16 +3933,16 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="Z27" t="n">
         <v>2.35</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>

--- a/jogos_2025-09-18.xlsx
+++ b/jogos_2025-09-18.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.65</v>
+        <v>3.55</v>
       </c>
       <c r="M24" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="N24" t="n">
-        <v>5.3</v>
+        <v>1.95</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,16 +3546,16 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.35</v>
+        <v>2.7</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.55</v>
+        <v>1.25</v>
       </c>
       <c r="M25" t="n">
-        <v>3.85</v>
+        <v>6</v>
       </c>
       <c r="N25" t="n">
-        <v>1.95</v>
+        <v>11</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,16 +3675,16 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="M26" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="N26" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.25</v>
+        <v>1.8</v>
       </c>
       <c r="M27" t="n">
-        <v>6</v>
+        <v>3.65</v>
       </c>
       <c r="N27" t="n">
-        <v>11</v>
+        <v>4.5</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,16 +3933,16 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>

--- a/jogos_2025-09-18.xlsx
+++ b/jogos_2025-09-18.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.35</v>
+        <v>4.5</v>
       </c>
       <c r="M19" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="N19" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>4.5</v>
+        <v>3.35</v>
       </c>
       <c r="M20" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="N20" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.55</v>
+        <v>1.25</v>
       </c>
       <c r="M24" t="n">
-        <v>3.85</v>
+        <v>6</v>
       </c>
       <c r="N24" t="n">
-        <v>1.95</v>
+        <v>11</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,16 +3546,16 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.25</v>
+        <v>1.65</v>
       </c>
       <c r="M25" t="n">
-        <v>6</v>
+        <v>3.95</v>
       </c>
       <c r="N25" t="n">
-        <v>11</v>
+        <v>5.3</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,16 +3675,16 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Z25" t="n">
         <v>2.35</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="M26" t="n">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="N26" t="n">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.8</v>
+        <v>3.55</v>
       </c>
       <c r="M27" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="N27" t="n">
-        <v>4.5</v>
+        <v>1.95</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,16 +3933,16 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.63</v>
+        <v>1.45</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>

--- a/jogos_2025-09-18.xlsx
+++ b/jogos_2025-09-18.xlsx
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>4.5</v>
+        <v>3.35</v>
       </c>
       <c r="M19" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="N19" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.35</v>
+        <v>4.5</v>
       </c>
       <c r="M20" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="N20" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.25</v>
+        <v>3.55</v>
       </c>
       <c r="M24" t="n">
-        <v>6</v>
+        <v>3.85</v>
       </c>
       <c r="N24" t="n">
-        <v>11</v>
+        <v>1.95</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,16 +3546,16 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.35</v>
+        <v>2.7</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="M25" t="n">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="N25" t="n">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.8</v>
+        <v>1.25</v>
       </c>
       <c r="M26" t="n">
-        <v>3.65</v>
+        <v>6</v>
       </c>
       <c r="N26" t="n">
-        <v>4.5</v>
+        <v>11</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,16 +3804,16 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="Z26" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA26" t="n">
         <v>2.25</v>
       </c>
-      <c r="AA26" t="n">
-        <v>0</v>
-      </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.55</v>
+        <v>1.65</v>
       </c>
       <c r="M27" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="N27" t="n">
-        <v>1.95</v>
+        <v>5.3</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,16 +3933,16 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>

--- a/jogos_2025-09-18.xlsx
+++ b/jogos_2025-09-18.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK32"/>
+  <dimension ref="A1:AK34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -628,12 +628,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -748,7 +748,7 @@
         <v>0</v>
       </c>
       <c r="AK2" s="3" t="n">
-        <v>45918.4375</v>
+        <v>45918.41666666666</v>
       </c>
     </row>
     <row r="3">
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -877,7 +877,7 @@
         <v>0</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>45918.4375</v>
+        <v>45918.41666666666</v>
       </c>
     </row>
     <row r="4">
@@ -886,12 +886,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1006,7 +1006,7 @@
         <v>0</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>45918.45833333334</v>
+        <v>45918.41666666666</v>
       </c>
     </row>
     <row r="5">
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45918.45833333334</v>
+        <v>45918.4375</v>
       </c>
     </row>
     <row r="6">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1181,65 +1181,65 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4.68</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>4.66</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,19 +1252,19 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45918.47916666666</v>
+        <v>45918.4375</v>
       </c>
     </row>
     <row r="7">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45918.5</v>
+        <v>45918.45833333334</v>
       </c>
     </row>
     <row r="8">
@@ -1402,27 +1402,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45918.5</v>
+        <v>45918.45833333334</v>
       </c>
     </row>
     <row r="9">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45918.5</v>
+        <v>45918.45833333334</v>
       </c>
     </row>
     <row r="10">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45918.5</v>
+        <v>45918.45833333334</v>
       </c>
     </row>
     <row r="11">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1826,65 +1826,65 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>4.66</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,19 +1897,19 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45918.5</v>
+        <v>45918.47916666666</v>
       </c>
     </row>
     <row r="12">
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45918.5</v>
+        <v>45918.52777777778</v>
       </c>
     </row>
     <row r="14">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45918.5</v>
+        <v>45918.52777777778</v>
       </c>
     </row>
     <row r="15">
@@ -2305,27 +2305,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45918.5</v>
+        <v>45918.54166666666</v>
       </c>
     </row>
     <row r="16">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45918.5</v>
+        <v>45918.54166666666</v>
       </c>
     </row>
     <row r="17">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45918.52777777778</v>
+        <v>45918.54166666666</v>
       </c>
     </row>
     <row r="18">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45918.52777777778</v>
+        <v>45918.54166666666</v>
       </c>
     </row>
     <row r="19">
@@ -2821,12 +2821,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45918.57291666666</v>
+        <v>45918.54166666666</v>
       </c>
     </row>
     <row r="20">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45918.57291666666</v>
+        <v>45918.54166666666</v>
       </c>
     </row>
     <row r="21">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45918.58333333334</v>
+        <v>45918.57291666666</v>
       </c>
     </row>
     <row r="22">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45918.58333333334</v>
+        <v>45918.57291666666</v>
       </c>
     </row>
     <row r="23">
@@ -3337,12 +3337,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45918.625</v>
+        <v>45918.58333333334</v>
       </c>
     </row>
     <row r="24">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,16 +3546,16 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3586,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45918.66666666666</v>
+        <v>45918.58333333334</v>
       </c>
     </row>
     <row r="25">
@@ -3595,12 +3595,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>45918.66666666666</v>
+        <v>45918.625</v>
       </c>
     </row>
     <row r="26">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.25</v>
+        <v>1.8</v>
       </c>
       <c r="M26" t="n">
-        <v>6</v>
+        <v>3.65</v>
       </c>
       <c r="N26" t="n">
-        <v>11</v>
+        <v>4.5</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,16 +3804,16 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.65</v>
+        <v>3.55</v>
       </c>
       <c r="M27" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="N27" t="n">
-        <v>5.3</v>
+        <v>1.95</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,16 +3933,16 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.35</v>
+        <v>2.7</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3982,27 +3982,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,16 +4062,16 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
-        <v>45918.79166666666</v>
+        <v>45918.66666666666</v>
       </c>
     </row>
     <row r="29">
@@ -4111,27 +4111,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="M29" t="n">
-        <v>3.25</v>
+        <v>3.95</v>
       </c>
       <c r="N29" t="n">
-        <v>4.15</v>
+        <v>5.3</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.45</v>
+        <v>1.58</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.55</v>
+        <v>2.35</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>45918.79166666666</v>
+        <v>45918.66666666666</v>
       </c>
     </row>
     <row r="30">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4360,7 +4360,7 @@
         <v>0</v>
       </c>
       <c r="AK30" s="3" t="n">
-        <v>45918.85416666666</v>
+        <v>45918.79166666666</v>
       </c>
     </row>
     <row r="31">
@@ -4369,12 +4369,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="AK31" s="3" t="n">
-        <v>45918.89583333334</v>
+        <v>45918.79166666666</v>
       </c>
     </row>
     <row r="32">
@@ -4498,126 +4498,384 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>New York City II</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>New England II</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK32" s="3" t="n">
+        <v>45918.85416666666</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>45918</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>South America Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Estudiantes</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M33" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N33" t="n">
+        <v>13</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK33" s="3" t="n">
+        <v>45918.89583333334</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>45918</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
           <t>23:30</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Angel City</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>Washington Spirit</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="inlineStr">
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" t="n">
-        <v>0</v>
-      </c>
-      <c r="X32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK32" s="3" t="n">
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK34" s="3" t="n">
         <v>45918.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-09-18.xlsx
+++ b/jogos_2025-09-18.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK34"/>
+  <dimension ref="A1:AK35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.55</v>
+        <v>1.78</v>
       </c>
       <c r="M2" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="N2" t="n">
-        <v>2.65</v>
+        <v>4.2</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.57</v>
+        <v>2.55</v>
       </c>
       <c r="M3" t="n">
-        <v>3.75</v>
+        <v>3.05</v>
       </c>
       <c r="N3" t="n">
-        <v>5</v>
+        <v>2.65</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,49 +927,49 @@
         </is>
       </c>
       <c r="L4" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="M4" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N4" t="n">
+        <v>5</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Z4" t="n">
         <v>1.78</v>
-      </c>
-      <c r="M4" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.68</v>
+        <v>3.7</v>
       </c>
       <c r="M11" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="N11" t="n">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="O11" t="n">
         <v>4.66</v>
@@ -1869,10 +1869,10 @@
         <v>2.63</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AA11" t="n">
         <v>4.6</v>
@@ -2047,27 +2047,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45918.52777777778</v>
+        <v>45918.5</v>
       </c>
     </row>
     <row r="14">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2305,12 +2305,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45918.54166666666</v>
+        <v>45918.52777777778</v>
       </c>
     </row>
     <row r="16">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45918.57291666666</v>
+        <v>45918.54166666666</v>
       </c>
     </row>
     <row r="22">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="M22" t="n">
         <v>3.35</v>
       </c>
-      <c r="M22" t="n">
-        <v>3.45</v>
-      </c>
       <c r="N22" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3337,12 +3337,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45918.58333333334</v>
+        <v>45918.57291666666</v>
       </c>
     </row>
     <row r="24">
@@ -3595,12 +3595,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>45918.625</v>
+        <v>45918.58333333334</v>
       </c>
     </row>
     <row r="26">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3844,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
-        <v>45918.66666666666</v>
+        <v>45918.625</v>
       </c>
     </row>
     <row r="27">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.55</v>
+        <v>3.02</v>
       </c>
       <c r="M27" t="n">
-        <v>3.85</v>
+        <v>3.68</v>
       </c>
       <c r="N27" t="n">
-        <v>1.95</v>
+        <v>2.14</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.25</v>
+        <v>2.02</v>
       </c>
       <c r="M28" t="n">
-        <v>6</v>
+        <v>3.85</v>
       </c>
       <c r="N28" t="n">
-        <v>11</v>
+        <v>3.17</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,16 +4062,16 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="M29" t="n">
         <v>3.95</v>
       </c>
       <c r="N29" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4240,27 +4240,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2</v>
+        <v>1.11</v>
       </c>
       <c r="M30" t="n">
-        <v>3.25</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="N30" t="n">
-        <v>4.15</v>
+        <v>19</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,16 +4320,16 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.45</v>
+        <v>1.57</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.55</v>
+        <v>2.35</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4360,7 +4360,7 @@
         <v>0</v>
       </c>
       <c r="AK30" s="3" t="n">
-        <v>45918.79166666666</v>
+        <v>45918.66666666666</v>
       </c>
     </row>
     <row r="31">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4498,12 +4498,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4618,7 +4618,7 @@
         <v>0</v>
       </c>
       <c r="AK32" s="3" t="n">
-        <v>45918.85416666666</v>
+        <v>45918.79166666666</v>
       </c>
     </row>
     <row r="33">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4747,7 +4747,7 @@
         <v>0</v>
       </c>
       <c r="AK33" s="3" t="n">
-        <v>45918.89583333334</v>
+        <v>45918.85416666666</v>
       </c>
     </row>
     <row r="34">
@@ -4756,126 +4756,255 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>South America Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Estudiantes</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M34" t="n">
+        <v>4</v>
+      </c>
+      <c r="N34" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK34" s="3" t="n">
+        <v>45918.89583333334</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>45918</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
           <t>23:30</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>Angel City</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>Washington Spirit</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="inlineStr">
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0</v>
-      </c>
-      <c r="W34" t="n">
-        <v>0</v>
-      </c>
-      <c r="X34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK34" s="3" t="n">
+      <c r="L35" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="M35" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N35" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK35" s="3" t="n">
         <v>45918.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-09-18.xlsx
+++ b/jogos_2025-09-18.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,49 +669,49 @@
         </is>
       </c>
       <c r="L2" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="M2" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N2" t="n">
+        <v>5</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Z2" t="n">
         <v>1.78</v>
-      </c>
-      <c r="M2" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.55</v>
+        <v>1.78</v>
       </c>
       <c r="M3" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="N3" t="n">
-        <v>2.65</v>
+        <v>4.2</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.57</v>
+        <v>2.55</v>
       </c>
       <c r="M4" t="n">
-        <v>3.75</v>
+        <v>3.05</v>
       </c>
       <c r="N4" t="n">
-        <v>5</v>
+        <v>2.65</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.02</v>
+        <v>2.02</v>
       </c>
       <c r="M27" t="n">
-        <v>3.68</v>
+        <v>3.85</v>
       </c>
       <c r="N27" t="n">
-        <v>2.14</v>
+        <v>3.17</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,16 +3933,16 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.45</v>
+        <v>1.63</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.7</v>
+        <v>2.25</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.02</v>
+        <v>3.02</v>
       </c>
       <c r="M28" t="n">
-        <v>3.85</v>
+        <v>3.68</v>
       </c>
       <c r="N28" t="n">
-        <v>3.17</v>
+        <v>2.14</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,16 +4062,16 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.63</v>
+        <v>1.45</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.63</v>
+        <v>1.11</v>
       </c>
       <c r="M29" t="n">
-        <v>3.95</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="N29" t="n">
-        <v>4.9</v>
+        <v>19</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,16 +4191,16 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="Z29" t="n">
         <v>2.35</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.11</v>
+        <v>1.63</v>
       </c>
       <c r="M30" t="n">
-        <v>8.800000000000001</v>
+        <v>3.95</v>
       </c>
       <c r="N30" t="n">
-        <v>19</v>
+        <v>4.9</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,16 +4320,16 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Z30" t="n">
         <v>2.35</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>

--- a/jogos_2025-09-18.xlsx
+++ b/jogos_2025-09-18.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.78</v>
+        <v>2.55</v>
       </c>
       <c r="M3" t="n">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="N3" t="n">
-        <v>4.2</v>
+        <v>2.65</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.55</v>
+        <v>1.78</v>
       </c>
       <c r="M4" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="N4" t="n">
-        <v>2.65</v>
+        <v>4.2</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.7</v>
+        <v>4.75</v>
       </c>
       <c r="M11" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="N11" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="O11" t="n">
+        <v>5</v>
+      </c>
+      <c r="P11" t="n">
         <v>2</v>
       </c>
-      <c r="O11" t="n">
-        <v>4.66</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.05</v>
-      </c>
       <c r="Q11" t="n">
-        <v>2.48</v>
+        <v>2.32</v>
       </c>
       <c r="R11" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="S11" t="n">
         <v>2.45</v>
       </c>
       <c r="T11" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U11" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="V11" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="W11" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="X11" t="n">
-        <v>2.63</v>
+        <v>2.9</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.6</v>
+        <v>3.85</v>
       </c>
       <c r="AB11" t="n">
         <v>1.18</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="AI11" t="n">
         <v>2.75</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.02</v>
+        <v>1.63</v>
       </c>
       <c r="M27" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="N27" t="n">
-        <v>3.17</v>
+        <v>4.9</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.02</v>
+        <v>2.02</v>
       </c>
       <c r="M28" t="n">
-        <v>3.68</v>
+        <v>3.85</v>
       </c>
       <c r="N28" t="n">
-        <v>2.14</v>
+        <v>3.17</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,16 +4062,16 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.45</v>
+        <v>1.63</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.7</v>
+        <v>2.25</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.11</v>
+        <v>3.02</v>
       </c>
       <c r="M29" t="n">
-        <v>8.800000000000001</v>
+        <v>3.68</v>
       </c>
       <c r="N29" t="n">
-        <v>19</v>
+        <v>2.14</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,16 +4191,16 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.35</v>
+        <v>2.7</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.63</v>
+        <v>1.11</v>
       </c>
       <c r="M30" t="n">
-        <v>3.95</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="N30" t="n">
-        <v>4.9</v>
+        <v>19</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,16 +4320,16 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="Z30" t="n">
         <v>2.35</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>

--- a/jogos_2025-09-18.xlsx
+++ b/jogos_2025-09-18.xlsx
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="M2" t="n">
-        <v>3.75</v>
+        <v>3.98</v>
       </c>
       <c r="N2" t="n">
-        <v>5</v>
+        <v>5.66</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.55</v>
+        <v>1.83</v>
       </c>
       <c r="M3" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="N3" t="n">
-        <v>2.65</v>
+        <v>4.29</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.78</v>
+        <v>2.67</v>
       </c>
       <c r="M4" t="n">
-        <v>3.35</v>
+        <v>3.12</v>
       </c>
       <c r="N4" t="n">
-        <v>4.2</v>
+        <v>2.71</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.23</v>
+        <v>2.55</v>
       </c>
       <c r="M22" t="n">
-        <v>3.35</v>
+        <v>3.72</v>
       </c>
       <c r="N22" t="n">
-        <v>2.17</v>
+        <v>2.44</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.55</v>
+        <v>3.23</v>
       </c>
       <c r="M23" t="n">
-        <v>3.72</v>
+        <v>3.35</v>
       </c>
       <c r="N23" t="n">
-        <v>2.44</v>
+        <v>2.17</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.63</v>
+        <v>3.02</v>
       </c>
       <c r="M27" t="n">
-        <v>3.95</v>
+        <v>3.68</v>
       </c>
       <c r="N27" t="n">
-        <v>4.9</v>
+        <v>2.14</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,16 +3933,16 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.35</v>
+        <v>2.7</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.02</v>
+        <v>1.63</v>
       </c>
       <c r="M29" t="n">
-        <v>3.68</v>
+        <v>3.95</v>
       </c>
       <c r="N29" t="n">
-        <v>2.14</v>
+        <v>4.9</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,16 +4191,16 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>

--- a/jogos_2025-09-18.xlsx
+++ b/jogos_2025-09-18.xlsx
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1323,52 +1323,52 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.55</v>
+        <v>3.23</v>
       </c>
       <c r="M22" t="n">
-        <v>3.72</v>
+        <v>3.35</v>
       </c>
       <c r="N22" t="n">
-        <v>2.44</v>
+        <v>2.17</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.23</v>
+        <v>2.55</v>
       </c>
       <c r="M23" t="n">
-        <v>3.35</v>
+        <v>3.72</v>
       </c>
       <c r="N23" t="n">
-        <v>2.17</v>
+        <v>2.44</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3513,7 +3513,7 @@
         <v>3.6</v>
       </c>
       <c r="N24" t="n">
-        <v>7</v>
+        <v>6.1</v>
       </c>
       <c r="O24" t="n">
         <v>2.05</v>
@@ -3525,7 +3525,7 @@
         <v>8</v>
       </c>
       <c r="R24" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="S24" t="n">
         <v>2.55</v>
@@ -3537,7 +3537,7 @@
         <v>1.32</v>
       </c>
       <c r="V24" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="W24" t="n">
         <v>1.38</v>
@@ -3555,13 +3555,13 @@
         <v>4.2</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3669,10 +3669,10 @@
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Y25" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.02</v>
+        <v>2.02</v>
       </c>
       <c r="M27" t="n">
-        <v>3.68</v>
+        <v>3.85</v>
       </c>
       <c r="N27" t="n">
-        <v>2.14</v>
+        <v>3.17</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.45</v>
+        <v>1.63</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.7</v>
+        <v>2.25</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.05</v>
+        <v>2.39</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.77</v>
+        <v>1.57</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.02</v>
+        <v>1.11</v>
       </c>
       <c r="M28" t="n">
-        <v>3.85</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="N28" t="n">
-        <v>3.17</v>
+        <v>19</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4161,34 +4161,34 @@
         <v>4.9</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Y29" t="n">
         <v>1.58</v>
@@ -4197,16 +4197,16 @@
         <v>2.35</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.11</v>
+        <v>3.02</v>
       </c>
       <c r="M30" t="n">
-        <v>8.800000000000001</v>
+        <v>3.68</v>
       </c>
       <c r="N30" t="n">
-        <v>19</v>
+        <v>2.14</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.35</v>
+        <v>2.7</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>

--- a/jogos_2025-09-18.xlsx
+++ b/jogos_2025-09-18.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK35"/>
+  <dimension ref="A1:AK30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -628,12 +628,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>5.66</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -708,10 +708,10 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
@@ -748,7 +748,7 @@
         <v>0</v>
       </c>
       <c r="AK2" s="3" t="n">
-        <v>45918.41666666666</v>
+        <v>45918.4375</v>
       </c>
     </row>
     <row r="3">
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -877,7 +877,7 @@
         <v>0</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>45918.41666666666</v>
+        <v>45918.4375</v>
       </c>
     </row>
     <row r="4">
@@ -886,12 +886,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1006,7 +1006,7 @@
         <v>0</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>45918.41666666666</v>
+        <v>45918.45833333334</v>
       </c>
     </row>
     <row r="5">
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45918.4375</v>
+        <v>45918.45833333334</v>
       </c>
     </row>
     <row r="6">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,19 +1252,19 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45918.4375</v>
+        <v>45918.47916666666</v>
       </c>
     </row>
     <row r="7">
@@ -1273,27 +1273,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1323,52 +1323,52 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45918.45833333334</v>
+        <v>45918.5</v>
       </c>
     </row>
     <row r="8">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45918.45833333334</v>
+        <v>45918.52777777778</v>
       </c>
     </row>
     <row r="9">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45918.45833333334</v>
+        <v>45918.52777777778</v>
       </c>
     </row>
     <row r="10">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45918.45833333334</v>
+        <v>45918.54166666666</v>
       </c>
     </row>
     <row r="11">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1826,65 +1826,65 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,19 +1897,19 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45918.47916666666</v>
+        <v>45918.54166666666</v>
       </c>
     </row>
     <row r="12">
@@ -1918,27 +1918,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45918.5</v>
+        <v>45918.54166666666</v>
       </c>
     </row>
     <row r="13">
@@ -2047,27 +2047,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45918.5</v>
+        <v>45918.54166666666</v>
       </c>
     </row>
     <row r="14">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45918.52777777778</v>
+        <v>45918.54166666666</v>
       </c>
     </row>
     <row r="15">
@@ -2305,12 +2305,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45918.52777777778</v>
+        <v>45918.54166666666</v>
       </c>
     </row>
     <row r="16">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45918.54166666666</v>
+        <v>45918.57291666666</v>
       </c>
     </row>
     <row r="18">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45918.54166666666</v>
+        <v>45918.57291666666</v>
       </c>
     </row>
     <row r="19">
@@ -2821,12 +2821,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2895,10 +2895,10 @@
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45918.54166666666</v>
+        <v>45918.58333333334</v>
       </c>
     </row>
     <row r="20">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45918.54166666666</v>
+        <v>45918.58333333334</v>
       </c>
     </row>
     <row r="21">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45918.54166666666</v>
+        <v>45918.625</v>
       </c>
     </row>
     <row r="22">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.23</v>
+        <v>3.02</v>
       </c>
       <c r="M22" t="n">
-        <v>3.35</v>
+        <v>3.68</v>
       </c>
       <c r="N22" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="O22" t="n">
-        <v>3.75</v>
+        <v>3.56</v>
       </c>
       <c r="P22" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="S22" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="T22" t="n">
-        <v>2.82</v>
+        <v>2.1</v>
       </c>
       <c r="U22" t="n">
-        <v>1.43</v>
+        <v>1.65</v>
       </c>
       <c r="V22" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W22" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="X22" t="n">
-        <v>3.9</v>
+        <v>5.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.67</v>
+        <v>1.45</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.9</v>
+        <v>2.05</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.37</v>
+        <v>1.77</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.67</v>
+        <v>1.41</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
         <v>1.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45918.57291666666</v>
+        <v>45918.66666666666</v>
       </c>
     </row>
     <row r="23">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.55</v>
+        <v>1.63</v>
       </c>
       <c r="M23" t="n">
-        <v>3.72</v>
+        <v>3.95</v>
       </c>
       <c r="N23" t="n">
-        <v>2.44</v>
+        <v>4.9</v>
       </c>
       <c r="O23" t="n">
-        <v>3.33</v>
+        <v>2.19</v>
       </c>
       <c r="P23" t="n">
         <v>2.2</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.96</v>
+        <v>5.2</v>
       </c>
       <c r="R23" t="n">
         <v>1.3</v>
       </c>
       <c r="S23" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="T23" t="n">
-        <v>2.28</v>
+        <v>2.43</v>
       </c>
       <c r="U23" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="V23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W23" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="X23" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.6</v>
+        <v>2.74</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.51</v>
+        <v>1.75</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.5</v>
+        <v>2.03</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.44</v>
+        <v>2.26</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45918.57291666666</v>
+        <v>45918.66666666666</v>
       </c>
     </row>
     <row r="24">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="O24" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X24" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC24" t="n">
         <v>1.44</v>
       </c>
-      <c r="M24" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N24" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="O24" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="P24" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>8</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T24" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X24" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AD24" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.45</v>
+        <v>1.8</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3586,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45918.58333333334</v>
+        <v>45918.66666666666</v>
       </c>
     </row>
     <row r="25">
@@ -3595,12 +3595,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.05</v>
+        <v>1.11</v>
       </c>
       <c r="M25" t="n">
-        <v>2.75</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="N25" t="n">
-        <v>4.3</v>
+        <v>19</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W25" t="n">
-        <v>1.63</v>
+        <v>1.07</v>
       </c>
       <c r="X25" t="n">
-        <v>2.13</v>
+        <v>6.25</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>45918.58333333334</v>
+        <v>45918.66666666666</v>
       </c>
     </row>
     <row r="26">
@@ -3724,27 +3724,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3844,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
-        <v>45918.625</v>
+        <v>45918.79166666666</v>
       </c>
     </row>
     <row r="27">
@@ -3853,27 +3853,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,62 +3894,62 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.02</v>
+        <v>1.84</v>
       </c>
       <c r="M27" t="n">
-        <v>3.85</v>
+        <v>2.95</v>
       </c>
       <c r="N27" t="n">
-        <v>3.17</v>
+        <v>4.2</v>
       </c>
       <c r="O27" t="n">
-        <v>2.49</v>
+        <v>2.65</v>
       </c>
       <c r="P27" t="n">
-        <v>2.3</v>
+        <v>1.92</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="R27" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="S27" t="n">
-        <v>3.62</v>
+        <v>2.35</v>
       </c>
       <c r="T27" t="n">
-        <v>2.25</v>
+        <v>3.5</v>
       </c>
       <c r="U27" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="X27" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AD27" t="n">
         <v>1.64</v>
       </c>
-      <c r="V27" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X27" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AE27" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.21</v>
+        <v>1.35</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
-        <v>45918.66666666666</v>
+        <v>45918.79166666666</v>
       </c>
     </row>
     <row r="28">
@@ -3982,27 +3982,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
-        <v>45918.66666666666</v>
+        <v>45918.85416666666</v>
       </c>
     </row>
     <row r="29">
@@ -4111,27 +4111,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.63</v>
+        <v>1.3</v>
       </c>
       <c r="M29" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="N29" t="n">
-        <v>4.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O29" t="n">
-        <v>2.19</v>
+        <v>1.9</v>
       </c>
       <c r="P29" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X29" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Y29" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q29" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S29" t="n">
+      <c r="Z29" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AC29" t="n">
         <v>3.25</v>
       </c>
-      <c r="T29" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X29" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AD29" t="n">
-        <v>2.03</v>
+        <v>1.31</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="AH29" t="n">
-        <v>2.26</v>
+        <v>2.99</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>45918.66666666666</v>
+        <v>45918.89583333334</v>
       </c>
     </row>
     <row r="30">
@@ -4240,27 +4240,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.02</v>
+        <v>3.15</v>
       </c>
       <c r="M30" t="n">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="N30" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="O30" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.45</v>
+        <v>1.85</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.7</v>
+        <v>1.85</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4360,651 +4360,6 @@
         <v>0</v>
       </c>
       <c r="AK30" s="3" t="n">
-        <v>45918.66666666666</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="n">
-        <v>45918</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>South America Copa Libertadores</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>LDU Quito</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>São Paulo</t>
-        </is>
-      </c>
-      <c r="G31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L31" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="M31" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="N31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O31" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="P31" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="T31" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="X31" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK31" s="3" t="n">
-        <v>45918.79166666666</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="n">
-        <v>45918</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Botafogo SP</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Operário PR</t>
-        </is>
-      </c>
-      <c r="G32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" t="n">
-        <v>0</v>
-      </c>
-      <c r="X32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK32" s="3" t="n">
-        <v>45918.79166666666</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="n">
-        <v>45918</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>20:30</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>USA MLS Next Pro</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>New York City II</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>New England II</t>
-        </is>
-      </c>
-      <c r="G33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" t="n">
-        <v>0</v>
-      </c>
-      <c r="W33" t="n">
-        <v>0</v>
-      </c>
-      <c r="X33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK33" s="3" t="n">
-        <v>45918.85416666666</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="n">
-        <v>45918</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>South America Copa Libertadores</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Flamengo</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Estudiantes</t>
-        </is>
-      </c>
-      <c r="G34" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L34" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="M34" t="n">
-        <v>4</v>
-      </c>
-      <c r="N34" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0</v>
-      </c>
-      <c r="W34" t="n">
-        <v>0</v>
-      </c>
-      <c r="X34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK34" s="3" t="n">
-        <v>45918.89583333334</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="n">
-        <v>45918</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Angel City</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Washington Spirit</t>
-        </is>
-      </c>
-      <c r="G35" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L35" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="M35" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N35" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" t="n">
-        <v>0</v>
-      </c>
-      <c r="W35" t="n">
-        <v>0</v>
-      </c>
-      <c r="X35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK35" s="3" t="n">
         <v>45918.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-09-18.xlsx
+++ b/jogos_2025-09-18.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK30"/>
+  <dimension ref="A1:AK27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -886,27 +886,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -936,52 +936,52 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1006,7 +1006,7 @@
         <v>0</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>45918.45833333334</v>
+        <v>45918.4375</v>
       </c>
     </row>
     <row r="5">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.32</v>
+        <v>4.2</v>
       </c>
       <c r="R6" t="n">
-        <v>1.45</v>
+        <v>1.7</v>
       </c>
       <c r="S6" t="n">
-        <v>2.45</v>
+        <v>2.08</v>
       </c>
       <c r="T6" t="n">
-        <v>3.2</v>
+        <v>4.25</v>
       </c>
       <c r="U6" t="n">
-        <v>1.34</v>
+        <v>1.17</v>
       </c>
       <c r="V6" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="W6" t="n">
-        <v>1.34</v>
+        <v>1.71</v>
       </c>
       <c r="X6" t="n">
-        <v>2.9</v>
+        <v>2.04</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.15</v>
+        <v>3.04</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.7</v>
+        <v>1.29</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.78</v>
+        <v>6.25</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.02</v>
+        <v>2.42</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.71</v>
+        <v>1.49</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,19 +1252,19 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.15</v>
+        <v>1.51</v>
       </c>
       <c r="AI6" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45918.47916666666</v>
+        <v>45918.45833333334</v>
       </c>
     </row>
     <row r="7">
@@ -1273,27 +1273,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,19 +1381,19 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45918.5</v>
+        <v>45918.47916666666</v>
       </c>
     </row>
     <row r="8">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.41</v>
+        <v>2.03</v>
       </c>
       <c r="M9" t="n">
-        <v>3.41</v>
+        <v>3.44</v>
       </c>
       <c r="N9" t="n">
-        <v>2.7</v>
+        <v>3.26</v>
       </c>
       <c r="O9" t="n">
-        <v>2.94</v>
+        <v>2.63</v>
       </c>
       <c r="P9" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.35</v>
+        <v>3.88</v>
       </c>
       <c r="R9" t="n">
         <v>1.35</v>
       </c>
       <c r="S9" t="n">
-        <v>2.93</v>
+        <v>3.18</v>
       </c>
       <c r="T9" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="U9" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="V9" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X9" t="n">
-        <v>3.64</v>
+        <v>3.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.49</v>
+        <v>1.66</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2121,10 +2121,10 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45918.54166666666</v>
+        <v>45918.57291666666</v>
       </c>
     </row>
     <row r="15">
@@ -2305,12 +2305,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45918.54166666666</v>
+        <v>45918.57291666666</v>
       </c>
     </row>
     <row r="16">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2508,16 +2508,16 @@
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45918.54166666666</v>
+        <v>45918.58333333334</v>
       </c>
     </row>
     <row r="17">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.55</v>
+        <v>1.48</v>
       </c>
       <c r="M17" t="n">
-        <v>3.72</v>
+        <v>3.6</v>
       </c>
       <c r="N17" t="n">
-        <v>2.44</v>
+        <v>7.75</v>
       </c>
       <c r="O17" t="n">
-        <v>3.33</v>
+        <v>2.05</v>
       </c>
       <c r="P17" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.96</v>
+        <v>8</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3</v>
+        <v>1.51</v>
       </c>
       <c r="S17" t="n">
-        <v>3.4</v>
+        <v>2.39</v>
       </c>
       <c r="T17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y17" t="n">
         <v>2.28</v>
       </c>
-      <c r="U17" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.73</v>
-      </c>
       <c r="Z17" t="n">
-        <v>2.1</v>
+        <v>1.56</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.6</v>
+        <v>4.2</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.48</v>
+        <v>1.15</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.51</v>
+        <v>2.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.44</v>
+        <v>2.45</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45918.57291666666</v>
+        <v>45918.58333333334</v>
       </c>
     </row>
     <row r="18">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45918.57291666666</v>
+        <v>45918.625</v>
       </c>
     </row>
     <row r="19">
@@ -2821,12 +2821,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.05</v>
+        <v>1.63</v>
       </c>
       <c r="M19" t="n">
-        <v>2.75</v>
+        <v>3.95</v>
       </c>
       <c r="N19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X19" t="n">
         <v>4.3</v>
       </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="X19" t="n">
-        <v>2.13</v>
-      </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45918.58333333334</v>
+        <v>45918.66666666666</v>
       </c>
     </row>
     <row r="20">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.44</v>
+        <v>1.11</v>
       </c>
       <c r="M20" t="n">
-        <v>3.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>6.1</v>
+        <v>19</v>
       </c>
       <c r="O20" t="n">
-        <v>2.05</v>
+        <v>1.42</v>
       </c>
       <c r="P20" t="n">
-        <v>1.96</v>
+        <v>3.13</v>
       </c>
       <c r="Q20" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="R20" t="n">
-        <v>1.51</v>
+        <v>1.19</v>
       </c>
       <c r="S20" t="n">
-        <v>2.55</v>
+        <v>4.2</v>
       </c>
       <c r="T20" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
-        <v>1.32</v>
+        <v>1.83</v>
       </c>
       <c r="V20" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="W20" t="n">
-        <v>1.38</v>
+        <v>1.07</v>
       </c>
       <c r="X20" t="n">
-        <v>2.62</v>
+        <v>6.25</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.3</v>
+        <v>1.57</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.56</v>
+        <v>2.35</v>
       </c>
       <c r="AA20" t="n">
-        <v>4.2</v>
+        <v>1.87</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.15</v>
+        <v>1.87</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.45</v>
+        <v>7.2</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45918.58333333334</v>
+        <v>45918.66666666666</v>
       </c>
     </row>
     <row r="21">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45918.625</v>
+        <v>45918.66666666666</v>
       </c>
     </row>
     <row r="22">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,62 +3249,62 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.02</v>
+        <v>2.02</v>
       </c>
       <c r="M22" t="n">
-        <v>3.68</v>
+        <v>3.85</v>
       </c>
       <c r="N22" t="n">
-        <v>2.14</v>
+        <v>3.17</v>
       </c>
       <c r="O22" t="n">
-        <v>3.56</v>
+        <v>2.49</v>
       </c>
       <c r="P22" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X22" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AD22" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q22" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X22" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>2.75</v>
-      </c>
       <c r="AE22" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.38</v>
+        <v>1.8</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3337,27 +3337,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.63</v>
+        <v>2.6</v>
       </c>
       <c r="M23" t="n">
-        <v>3.95</v>
+        <v>3</v>
       </c>
       <c r="N23" t="n">
-        <v>4.9</v>
+        <v>2.75</v>
       </c>
       <c r="O23" t="n">
-        <v>2.19</v>
+        <v>3.6</v>
       </c>
       <c r="P23" t="n">
-        <v>2.2</v>
+        <v>1.88</v>
       </c>
       <c r="Q23" t="n">
-        <v>5.2</v>
+        <v>3.45</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="S23" t="n">
-        <v>3.25</v>
+        <v>2.4</v>
       </c>
       <c r="T23" t="n">
-        <v>2.43</v>
+        <v>3.6</v>
       </c>
       <c r="U23" t="n">
-        <v>1.54</v>
+        <v>1.25</v>
       </c>
       <c r="V23" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="W23" t="n">
-        <v>1.22</v>
+        <v>1.49</v>
       </c>
       <c r="X23" t="n">
-        <v>4.3</v>
+        <v>2.48</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.58</v>
+        <v>2.4</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.35</v>
+        <v>1.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.74</v>
+        <v>5.52</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.41</v>
+        <v>1.14</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.75</v>
+        <v>2.31</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.03</v>
+        <v>1.6</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.26</v>
+        <v>1.4</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45918.66666666666</v>
+        <v>45918.79166666666</v>
       </c>
     </row>
     <row r="24">
@@ -3466,27 +3466,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,62 +3507,62 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.02</v>
+        <v>1.84</v>
       </c>
       <c r="M24" t="n">
-        <v>3.85</v>
+        <v>2.95</v>
       </c>
       <c r="N24" t="n">
-        <v>3.17</v>
+        <v>4.2</v>
       </c>
       <c r="O24" t="n">
-        <v>2.49</v>
+        <v>2.65</v>
       </c>
       <c r="P24" t="n">
-        <v>2.3</v>
+        <v>1.92</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="R24" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="S24" t="n">
-        <v>3.62</v>
+        <v>2.35</v>
       </c>
       <c r="T24" t="n">
-        <v>2.25</v>
+        <v>3.5</v>
       </c>
       <c r="U24" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="X24" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AD24" t="n">
         <v>1.64</v>
       </c>
-      <c r="V24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X24" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AE24" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.21</v>
+        <v>1.35</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3586,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45918.66666666666</v>
+        <v>45918.79166666666</v>
       </c>
     </row>
     <row r="25">
@@ -3595,27 +3595,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>1.42</v>
+        <v>3.2</v>
       </c>
       <c r="P25" t="n">
-        <v>3.13</v>
+        <v>2.48</v>
       </c>
       <c r="Q25" t="n">
-        <v>12</v>
+        <v>2.55</v>
       </c>
       <c r="R25" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="U25" t="n">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="V25" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X25" t="n">
-        <v>6.25</v>
+        <v>4.8</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.35</v>
+        <v>2.43</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.87</v>
+        <v>2.18</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.87</v>
+        <v>1.58</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.34</v>
+        <v>1.43</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.53</v>
+        <v>2.5</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="AH25" t="n">
-        <v>7.2</v>
+        <v>1.36</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>45918.66666666666</v>
+        <v>45918.85416666666</v>
       </c>
     </row>
     <row r="26">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="M26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N26" t="n">
-        <v>2.75</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3844,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
-        <v>45918.79166666666</v>
+        <v>45918.89583333334</v>
       </c>
     </row>
     <row r="27">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,62 +3894,62 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.84</v>
+        <v>3.15</v>
       </c>
       <c r="M27" t="n">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="N27" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="O27" t="n">
-        <v>2.65</v>
+        <v>3.64</v>
       </c>
       <c r="P27" t="n">
-        <v>1.92</v>
+        <v>2.23</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.9</v>
+        <v>2.79</v>
       </c>
       <c r="R27" t="n">
-        <v>1.53</v>
+        <v>1.34</v>
       </c>
       <c r="S27" t="n">
-        <v>2.35</v>
+        <v>2.89</v>
       </c>
       <c r="T27" t="n">
-        <v>3.5</v>
+        <v>2.68</v>
       </c>
       <c r="U27" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W27" t="n">
         <v>1.23</v>
       </c>
-      <c r="V27" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.49</v>
-      </c>
       <c r="X27" t="n">
-        <v>2.6</v>
+        <v>3.65</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.45</v>
+        <v>1.85</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="AA27" t="n">
-        <v>4.7</v>
+        <v>2.85</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r="AC27" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AD27" t="n">
         <v>2.14</v>
       </c>
-      <c r="AD27" t="n">
-        <v>1.64</v>
-      </c>
       <c r="AE27" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.85</v>
+        <v>1.41</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3973,393 +3973,6 @@
         <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
-        <v>45918.79166666666</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="n">
-        <v>45918</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>20:30</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>USA MLS Next Pro</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>New York City II</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>New England II</t>
-        </is>
-      </c>
-      <c r="G28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" t="n">
-        <v>0</v>
-      </c>
-      <c r="W28" t="n">
-        <v>0</v>
-      </c>
-      <c r="X28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK28" s="3" t="n">
-        <v>45918.85416666666</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="n">
-        <v>45918</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>South America Copa Libertadores</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Flamengo</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Estudiantes</t>
-        </is>
-      </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L29" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="M29" t="n">
-        <v>4</v>
-      </c>
-      <c r="N29" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="O29" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="T29" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="X29" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK29" s="3" t="n">
-        <v>45918.89583333334</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="n">
-        <v>45918</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Angel City</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Washington Spirit</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L30" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="M30" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N30" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK30" s="3" t="n">
         <v>45918.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-09-18.xlsx
+++ b/jogos_2025-09-18.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK27"/>
+  <dimension ref="A1:AK21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -762,22 +762,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1065,52 +1065,52 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1194,52 +1194,52 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45918.52777777778</v>
+        <v>45918.54166666666</v>
       </c>
     </row>
     <row r="9">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45918.52777777778</v>
+        <v>45918.54166666666</v>
       </c>
     </row>
     <row r="10">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45918.54166666666</v>
+        <v>45918.57291666666</v>
       </c>
     </row>
     <row r="12">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45918.54166666666</v>
+        <v>45918.57291666666</v>
       </c>
     </row>
     <row r="13">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,62 +2088,62 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.86</v>
+        <v>1.48</v>
       </c>
       <c r="M13" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="N13" t="n">
-        <v>4</v>
+        <v>7.75</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD13" t="n">
         <v>1.5</v>
       </c>
-      <c r="X13" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
       <c r="AE13" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45918.54166666666</v>
+        <v>45918.58333333334</v>
       </c>
     </row>
     <row r="14">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.23</v>
+        <v>2.02</v>
       </c>
       <c r="M14" t="n">
-        <v>3.35</v>
+        <v>2.64</v>
       </c>
       <c r="N14" t="n">
-        <v>2.17</v>
+        <v>4.1</v>
       </c>
       <c r="O14" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Z14" t="n">
         <v>1.33</v>
       </c>
-      <c r="S14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AA14" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45918.57291666666</v>
+        <v>45918.58333333334</v>
       </c>
     </row>
     <row r="15">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.55</v>
+        <v>1.11</v>
       </c>
       <c r="M15" t="n">
-        <v>3.72</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>2.44</v>
+        <v>19</v>
       </c>
       <c r="O15" t="n">
-        <v>3.33</v>
+        <v>1.42</v>
       </c>
       <c r="P15" t="n">
-        <v>2.2</v>
+        <v>3.13</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.96</v>
+        <v>12</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="S15" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="T15" t="n">
-        <v>2.28</v>
+        <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="V15" t="n">
         <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="X15" t="n">
-        <v>4.5</v>
+        <v>6.25</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.6</v>
+        <v>1.87</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.48</v>
+        <v>1.87</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.51</v>
+        <v>2.34</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.5</v>
+        <v>1.53</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.44</v>
+        <v>7.2</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45918.57291666666</v>
+        <v>45918.66666666666</v>
       </c>
     </row>
     <row r="16">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.02</v>
+        <v>1.63</v>
       </c>
       <c r="M16" t="n">
-        <v>2.64</v>
+        <v>3.95</v>
       </c>
       <c r="N16" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W16" t="n">
-        <v>1.63</v>
+        <v>1.22</v>
       </c>
       <c r="X16" t="n">
-        <v>2.13</v>
+        <v>4.3</v>
       </c>
       <c r="Y16" t="n">
-        <v>3.25</v>
+        <v>1.58</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.33</v>
+        <v>2.35</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45918.58333333334</v>
+        <v>45918.66666666666</v>
       </c>
     </row>
     <row r="17">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,78 +2604,78 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.48</v>
+        <v>3.02</v>
       </c>
       <c r="M17" t="n">
-        <v>3.6</v>
+        <v>3.68</v>
       </c>
       <c r="N17" t="n">
-        <v>7.75</v>
+        <v>2.14</v>
       </c>
       <c r="O17" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA17" t="n">
         <v>2.05</v>
       </c>
-      <c r="P17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>8</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W17" t="n">
+      <c r="AB17" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH17" t="n">
         <v>1.38</v>
       </c>
-      <c r="X17" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>2.45</v>
-      </c>
       <c r="AI17" t="n">
         <v>0</v>
       </c>
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45918.58333333334</v>
+        <v>45918.66666666666</v>
       </c>
     </row>
     <row r="18">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45918.625</v>
+        <v>45918.66666666666</v>
       </c>
     </row>
     <row r="19">
@@ -2821,27 +2821,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.63</v>
+        <v>2.6</v>
       </c>
       <c r="M19" t="n">
-        <v>3.95</v>
+        <v>3</v>
       </c>
       <c r="N19" t="n">
-        <v>4.9</v>
+        <v>2.75</v>
       </c>
       <c r="O19" t="n">
-        <v>2.19</v>
+        <v>3.6</v>
       </c>
       <c r="P19" t="n">
-        <v>2.2</v>
+        <v>1.88</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.2</v>
+        <v>3.45</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="S19" t="n">
-        <v>3.25</v>
+        <v>2.4</v>
       </c>
       <c r="T19" t="n">
-        <v>2.43</v>
+        <v>3.6</v>
       </c>
       <c r="U19" t="n">
-        <v>1.54</v>
+        <v>1.25</v>
       </c>
       <c r="V19" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="W19" t="n">
-        <v>1.22</v>
+        <v>1.49</v>
       </c>
       <c r="X19" t="n">
-        <v>4.3</v>
+        <v>2.48</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.58</v>
+        <v>2.4</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.35</v>
+        <v>1.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.74</v>
+        <v>5.52</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.41</v>
+        <v>1.14</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.75</v>
+        <v>2.31</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.03</v>
+        <v>1.6</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.26</v>
+        <v>1.4</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45918.66666666666</v>
+        <v>45918.79166666666</v>
       </c>
     </row>
     <row r="20">
@@ -2950,27 +2950,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>1.42</v>
+        <v>3.2</v>
       </c>
       <c r="P20" t="n">
-        <v>3.13</v>
+        <v>2.48</v>
       </c>
       <c r="Q20" t="n">
-        <v>12</v>
+        <v>2.55</v>
       </c>
       <c r="R20" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="U20" t="n">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="V20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X20" t="n">
-        <v>6.25</v>
+        <v>4.8</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.35</v>
+        <v>2.43</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.87</v>
+        <v>2.18</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.87</v>
+        <v>1.58</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.34</v>
+        <v>1.43</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.53</v>
+        <v>2.5</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="AH20" t="n">
-        <v>7.2</v>
+        <v>1.36</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45918.66666666666</v>
+        <v>45918.85416666666</v>
       </c>
     </row>
     <row r="21">
@@ -3079,27 +3079,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,78 +3120,78 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.02</v>
+        <v>3.15</v>
       </c>
       <c r="M21" t="n">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="N21" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="O21" t="n">
-        <v>3.56</v>
+        <v>3.64</v>
       </c>
       <c r="P21" t="n">
-        <v>2.5</v>
+        <v>2.23</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.5</v>
+        <v>2.79</v>
       </c>
       <c r="R21" t="n">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="S21" t="n">
-        <v>3.7</v>
+        <v>2.89</v>
       </c>
       <c r="T21" t="n">
-        <v>2.1</v>
+        <v>2.68</v>
       </c>
       <c r="U21" t="n">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="V21" t="n">
         <v>1.01</v>
       </c>
       <c r="W21" t="n">
-        <v>1.1</v>
+        <v>1.23</v>
       </c>
       <c r="X21" t="n">
-        <v>5.5</v>
+        <v>3.65</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.45</v>
+        <v>1.85</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.7</v>
+        <v>1.85</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.05</v>
+        <v>2.85</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.77</v>
+        <v>1.29</v>
       </c>
       <c r="AC21" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AH21" t="n">
         <v>1.41</v>
       </c>
-      <c r="AD21" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AI21" t="n">
         <v>0</v>
       </c>
@@ -3199,780 +3199,6 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45918.66666666666</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>45918</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Europe UEFA Champions League</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Eintracht Frankfurt</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Galatasaray</t>
-        </is>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L22" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="M22" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="N22" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="O22" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X22" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK22" s="3" t="n">
-        <v>45918.66666666666</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="n">
-        <v>45918</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Botafogo SP</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Operário PR</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L23" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="M23" t="n">
-        <v>3</v>
-      </c>
-      <c r="N23" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="O23" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T23" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="X23" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>5.52</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK23" s="3" t="n">
-        <v>45918.79166666666</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
-        <v>45918</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>South America Copa Libertadores</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>LDU Quito</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>São Paulo</t>
-        </is>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L24" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="M24" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="N24" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O24" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="P24" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="T24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="X24" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK24" s="3" t="n">
-        <v>45918.79166666666</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
-        <v>45918</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>20:30</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>USA MLS Next Pro</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>New York City II</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>New England II</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X25" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK25" s="3" t="n">
-        <v>45918.85416666666</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
-        <v>45918</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>South America Copa Libertadores</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Flamengo</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Estudiantes</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L26" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="M26" t="n">
-        <v>4</v>
-      </c>
-      <c r="N26" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="P26" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="T26" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="X26" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK26" s="3" t="n">
-        <v>45918.89583333334</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="n">
-        <v>45918</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Angel City</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Washington Spirit</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L27" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="M27" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N27" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="O27" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="P27" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X27" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK27" s="3" t="n">
         <v>45918.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-09-18.xlsx
+++ b/jogos_2025-09-18.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK21"/>
+  <dimension ref="A1:AK26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -762,22 +762,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1068,49 +1068,49 @@
         <v>3.1</v>
       </c>
       <c r="P5" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="Q5" t="n">
         <v>4.2</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="S5" t="n">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="T5" t="n">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="U5" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="V5" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="W5" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="X5" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1329,13 +1329,13 @@
         <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="R7" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S7" t="n">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="T7" t="n">
         <v>3.2</v>
@@ -1359,7 +1359,7 @@
         <v>1.7</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.78</v>
+        <v>4.1</v>
       </c>
       <c r="AB7" t="n">
         <v>1.19</v>
@@ -1384,7 +1384,7 @@
         <v>1.27</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AI7" t="n">
         <v>2.75</v>
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45918.54166666666</v>
+        <v>45918.52777777778</v>
       </c>
     </row>
     <row r="9">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45918.54166666666</v>
+        <v>45918.52777777778</v>
       </c>
     </row>
     <row r="10">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45918.57291666666</v>
+        <v>45918.54166666666</v>
       </c>
     </row>
     <row r="12">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45918.57291666666</v>
+        <v>45918.54166666666</v>
       </c>
     </row>
     <row r="13">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.48</v>
+        <v>3.23</v>
       </c>
       <c r="M13" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="N13" t="n">
-        <v>7.75</v>
+        <v>2.17</v>
       </c>
       <c r="O13" t="n">
-        <v>2.05</v>
+        <v>3.75</v>
       </c>
       <c r="P13" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>8</v>
+        <v>2.52</v>
       </c>
       <c r="R13" t="n">
-        <v>1.51</v>
+        <v>1.33</v>
       </c>
       <c r="S13" t="n">
-        <v>2.39</v>
+        <v>3.3</v>
       </c>
       <c r="T13" t="n">
-        <v>3.2</v>
+        <v>2.82</v>
       </c>
       <c r="U13" t="n">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="V13" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W13" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="X13" t="n">
-        <v>2.62</v>
+        <v>3.9</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.28</v>
+        <v>1.67</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.56</v>
+        <v>2.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.15</v>
+        <v>1.37</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.4</v>
+        <v>1.67</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.45</v>
+        <v>1.34</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45918.58333333334</v>
+        <v>45918.57291666666</v>
       </c>
     </row>
     <row r="14">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.02</v>
+        <v>2.55</v>
       </c>
       <c r="M14" t="n">
-        <v>2.64</v>
+        <v>3.72</v>
       </c>
       <c r="N14" t="n">
-        <v>4.1</v>
+        <v>2.44</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>1.63</v>
+        <v>1.18</v>
       </c>
       <c r="X14" t="n">
-        <v>2.13</v>
+        <v>4.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>3.25</v>
+        <v>1.73</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.33</v>
+        <v>2.1</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45918.58333333334</v>
+        <v>45918.57291666666</v>
       </c>
     </row>
     <row r="15">
@@ -2305,12 +2305,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.11</v>
+        <v>1.39</v>
       </c>
       <c r="M15" t="n">
-        <v>8.800000000000001</v>
+        <v>3.78</v>
       </c>
       <c r="N15" t="n">
-        <v>19</v>
+        <v>6.8</v>
       </c>
       <c r="O15" t="n">
-        <v>1.42</v>
+        <v>2.02</v>
       </c>
       <c r="P15" t="n">
-        <v>3.13</v>
+        <v>2.23</v>
       </c>
       <c r="Q15" t="n">
-        <v>12</v>
+        <v>8.4</v>
       </c>
       <c r="R15" t="n">
-        <v>1.19</v>
+        <v>1.46</v>
       </c>
       <c r="S15" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA15" t="n">
         <v>4.2</v>
       </c>
-      <c r="T15" t="n">
-        <v>2</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X15" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.87</v>
-      </c>
       <c r="AB15" t="n">
-        <v>1.87</v>
+        <v>1.21</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AH15" t="n">
-        <v>7.2</v>
+        <v>2.45</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45918.66666666666</v>
+        <v>45918.58333333334</v>
       </c>
     </row>
     <row r="16">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="N16" t="n">
+        <v>4</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
         <v>1.63</v>
       </c>
-      <c r="M16" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="N16" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="O16" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.22</v>
-      </c>
       <c r="X16" t="n">
-        <v>4.3</v>
+        <v>2.13</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.58</v>
+        <v>2.75</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.35</v>
+        <v>1.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45918.66666666666</v>
+        <v>45918.58333333334</v>
       </c>
     </row>
     <row r="17">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45918.66666666666</v>
+        <v>45918.625</v>
       </c>
     </row>
     <row r="18">
@@ -2778,10 +2778,10 @@
         <v>2.25</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AC18" t="n">
         <v>1.44</v>
@@ -2821,27 +2821,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.6</v>
+        <v>1.63</v>
       </c>
       <c r="M19" t="n">
-        <v>3</v>
+        <v>3.95</v>
       </c>
       <c r="N19" t="n">
-        <v>2.75</v>
+        <v>4.9</v>
       </c>
       <c r="O19" t="n">
-        <v>3.6</v>
+        <v>2.19</v>
       </c>
       <c r="P19" t="n">
-        <v>1.88</v>
+        <v>2.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.45</v>
+        <v>5.2</v>
       </c>
       <c r="R19" t="n">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="S19" t="n">
-        <v>2.4</v>
+        <v>3.25</v>
       </c>
       <c r="T19" t="n">
-        <v>3.6</v>
+        <v>2.43</v>
       </c>
       <c r="U19" t="n">
-        <v>1.25</v>
+        <v>1.54</v>
       </c>
       <c r="V19" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="W19" t="n">
-        <v>1.49</v>
+        <v>1.22</v>
       </c>
       <c r="X19" t="n">
-        <v>2.48</v>
+        <v>4.3</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.4</v>
+        <v>1.58</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.5</v>
+        <v>2.35</v>
       </c>
       <c r="AA19" t="n">
-        <v>5.52</v>
+        <v>2.74</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.14</v>
+        <v>1.41</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.31</v>
+        <v>1.75</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.6</v>
+        <v>2.03</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.4</v>
+        <v>2.26</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45918.79166666666</v>
+        <v>45918.66666666666</v>
       </c>
     </row>
     <row r="20">
@@ -2950,27 +2950,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O20" t="n">
-        <v>3.2</v>
+        <v>3.56</v>
       </c>
       <c r="P20" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="T20" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="U20" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W20" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X20" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.43</v>
+        <v>2.7</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.18</v>
+        <v>2.05</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.58</v>
+        <v>1.77</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45918.85416666666</v>
+        <v>45918.66666666666</v>
       </c>
     </row>
     <row r="21">
@@ -3079,27 +3079,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,85 +3120,730 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.15</v>
+        <v>1.11</v>
       </c>
       <c r="M21" t="n">
-        <v>3.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="N21" t="n">
-        <v>2.1</v>
+        <v>19</v>
       </c>
       <c r="O21" t="n">
-        <v>3.64</v>
+        <v>1.42</v>
       </c>
       <c r="P21" t="n">
-        <v>2.23</v>
+        <v>3.13</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.79</v>
+        <v>12</v>
       </c>
       <c r="R21" t="n">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="S21" t="n">
-        <v>2.89</v>
+        <v>4.2</v>
       </c>
       <c r="T21" t="n">
-        <v>2.68</v>
+        <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>1.4</v>
+        <v>1.83</v>
       </c>
       <c r="V21" t="n">
         <v>1.01</v>
       </c>
       <c r="W21" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X21" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" s="3" t="n">
+        <v>45918.66666666666</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>45918</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Botafogo SP</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Operário PR</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M22" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="O22" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="X22" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK22" s="3" t="n">
+        <v>45918.79166666666</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>45918</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>South America Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>LDU Quito</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="M23" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="N23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O23" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U23" t="n">
         <v>1.23</v>
       </c>
-      <c r="X21" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="Y21" t="n">
+      <c r="V23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="X23" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH23" t="n">
         <v>1.85</v>
       </c>
-      <c r="Z21" t="n">
+      <c r="AI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK23" s="3" t="n">
+        <v>45918.79166666666</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>45918</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>New York City II</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>New England II</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X24" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK24" s="3" t="n">
+        <v>45918.85416666666</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>45918</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>South America Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Estudiantes</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M25" t="n">
+        <v>4</v>
+      </c>
+      <c r="N25" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X25" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK25" s="3" t="n">
+        <v>45918.89583333334</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>45918</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Angel City</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Washington Spirit</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="M26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N26" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O26" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X26" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="Y26" t="n">
         <v>1.85</v>
       </c>
-      <c r="AA21" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AB21" t="n">
+      <c r="Z26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AB26" t="n">
         <v>1.29</v>
       </c>
-      <c r="AC21" t="n">
+      <c r="AC26" t="n">
         <v>1.61</v>
       </c>
-      <c r="AD21" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
+      <c r="AD26" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
         <v>1.24</v>
       </c>
-      <c r="AH21" t="n">
+      <c r="AH26" t="n">
         <v>1.41</v>
       </c>
-      <c r="AI21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK21" s="3" t="n">
+      <c r="AI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK26" s="3" t="n">
         <v>45918.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-09-18.xlsx
+++ b/jogos_2025-09-18.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK26"/>
+  <dimension ref="A1:AK24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -762,22 +762,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O5" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.97</v>
+        <v>2.35</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1194,52 +1194,52 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.7</v>
+        <v>4.33</v>
       </c>
       <c r="M7" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="N7" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="O7" t="n">
         <v>5</v>
@@ -1329,46 +1329,46 @@
         <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R7" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="S7" t="n">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="T7" t="n">
         <v>3.2</v>
       </c>
       <c r="U7" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V7" t="n">
         <v>1.02</v>
       </c>
       <c r="W7" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="X7" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="Y7" t="n">
         <v>2.15</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AI7" t="n">
         <v>2.75</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.3</v>
+        <v>2.03</v>
       </c>
       <c r="M8" t="n">
-        <v>3.37</v>
+        <v>3.44</v>
       </c>
       <c r="N8" t="n">
-        <v>2.76</v>
+        <v>3.26</v>
       </c>
       <c r="O8" t="n">
-        <v>2.91</v>
+        <v>2.63</v>
       </c>
       <c r="P8" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.44</v>
+        <v>3.88</v>
       </c>
       <c r="R8" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S8" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="T8" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="U8" t="n">
         <v>1.42</v>
       </c>
       <c r="V8" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="W8" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="X8" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="Y8" t="n">
         <v>1.85</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AA8" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AC8" t="n">
         <v>1.65</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.51</v>
+        <v>1.66</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.03</v>
+        <v>2.3</v>
       </c>
       <c r="M9" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="Q9" t="n">
         <v>3.44</v>
       </c>
-      <c r="N9" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="O9" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>3.88</v>
-      </c>
       <c r="R9" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="T9" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="U9" t="n">
         <v>1.42</v>
       </c>
       <c r="V9" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="W9" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="X9" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="Y9" t="n">
         <v>1.85</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AC9" t="n">
         <v>1.65</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.66</v>
+        <v>1.51</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45918.54166666666</v>
+        <v>45918.57291666666</v>
       </c>
     </row>
     <row r="12">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45918.54166666666</v>
+        <v>45918.57291666666</v>
       </c>
     </row>
     <row r="13">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.23</v>
+        <v>2.07</v>
       </c>
       <c r="M13" t="n">
-        <v>3.35</v>
+        <v>2.8</v>
       </c>
       <c r="N13" t="n">
-        <v>2.17</v>
+        <v>3.9</v>
       </c>
       <c r="O13" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.25</v>
+        <v>1.63</v>
       </c>
       <c r="X13" t="n">
-        <v>3.9</v>
+        <v>2.13</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.67</v>
+        <v>2.62</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.2</v>
+        <v>1.44</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45918.57291666666</v>
+        <v>45918.58333333334</v>
       </c>
     </row>
     <row r="14">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,78 +2217,78 @@
         </is>
       </c>
       <c r="L14" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N14" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>7</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH14" t="n">
         <v>2.55</v>
       </c>
-      <c r="M14" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="N14" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="O14" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AI14" t="n">
         <v>0</v>
       </c>
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45918.57291666666</v>
+        <v>45918.58333333334</v>
       </c>
     </row>
     <row r="15">
@@ -2305,12 +2305,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45918.58333333334</v>
+        <v>45918.625</v>
       </c>
     </row>
     <row r="16">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.09</v>
+        <v>1.11</v>
       </c>
       <c r="M16" t="n">
-        <v>2.75</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>1.63</v>
+        <v>1.07</v>
       </c>
       <c r="X16" t="n">
-        <v>2.13</v>
+        <v>6.25</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.75</v>
+        <v>1.57</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.4</v>
+        <v>2.35</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45918.58333333334</v>
+        <v>45918.66666666666</v>
       </c>
     </row>
     <row r="17">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45918.625</v>
+        <v>45918.66666666666</v>
       </c>
     </row>
     <row r="18">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.63</v>
+        <v>3.02</v>
       </c>
       <c r="M19" t="n">
-        <v>3.95</v>
+        <v>3.68</v>
       </c>
       <c r="N19" t="n">
-        <v>4.9</v>
+        <v>2.14</v>
       </c>
       <c r="O19" t="n">
-        <v>2.19</v>
+        <v>3.56</v>
       </c>
       <c r="P19" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.2</v>
+        <v>2.5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="S19" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="T19" t="n">
-        <v>2.43</v>
+        <v>2.1</v>
       </c>
       <c r="U19" t="n">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="V19" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W19" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="X19" t="n">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.35</v>
+        <v>2.7</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.74</v>
+        <v>2.05</v>
       </c>
       <c r="AB19" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC19" t="n">
         <v>1.41</v>
       </c>
-      <c r="AC19" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AD19" t="n">
-        <v>2.03</v>
+        <v>2.75</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.26</v>
+        <v>1.38</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2950,27 +2950,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.02</v>
+        <v>1.84</v>
       </c>
       <c r="M20" t="n">
-        <v>3.68</v>
+        <v>2.95</v>
       </c>
       <c r="N20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="X20" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC20" t="n">
         <v>2.14</v>
       </c>
-      <c r="O20" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X20" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.41</v>
-      </c>
       <c r="AD20" t="n">
-        <v>2.75</v>
+        <v>1.64</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.38</v>
+        <v>1.85</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45918.66666666666</v>
+        <v>45918.79166666666</v>
       </c>
     </row>
     <row r="21">
@@ -3079,27 +3079,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.11</v>
+        <v>2.7</v>
       </c>
       <c r="M21" t="n">
-        <v>8.800000000000001</v>
+        <v>2.85</v>
       </c>
       <c r="N21" t="n">
-        <v>19</v>
+        <v>2.75</v>
       </c>
       <c r="O21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X21" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Z21" t="n">
         <v>1.42</v>
       </c>
-      <c r="P21" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>12</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S21" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X21" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2.35</v>
-      </c>
       <c r="AA21" t="n">
-        <v>1.87</v>
+        <v>6.01</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.87</v>
+        <v>1.13</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.34</v>
+        <v>2.19</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="AH21" t="n">
-        <v>7.2</v>
+        <v>1.42</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45918.66666666666</v>
+        <v>45918.79166666666</v>
       </c>
     </row>
     <row r="22">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,62 +3249,62 @@
         </is>
       </c>
       <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X22" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AD22" t="n">
         <v>2.5</v>
       </c>
-      <c r="M22" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="N22" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="O22" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="X22" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>5.52</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.64</v>
-      </c>
       <c r="AE22" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.39</v>
+        <v>1.21</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45918.79166666666</v>
+        <v>45918.85416666666</v>
       </c>
     </row>
     <row r="23">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.84</v>
+        <v>1.3</v>
       </c>
       <c r="M23" t="n">
-        <v>2.95</v>
+        <v>4</v>
       </c>
       <c r="N23" t="n">
-        <v>4.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O23" t="n">
-        <v>2.65</v>
+        <v>1.9</v>
       </c>
       <c r="P23" t="n">
-        <v>1.92</v>
+        <v>2.01</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.9</v>
+        <v>9.5</v>
       </c>
       <c r="R23" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="S23" t="n">
-        <v>2.35</v>
+        <v>2.43</v>
       </c>
       <c r="T23" t="n">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="U23" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="V23" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="W23" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="X23" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AA23" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.14</v>
+        <v>3.25</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.64</v>
+        <v>1.31</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.35</v>
+        <v>1.17</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.85</v>
+        <v>2.99</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45918.79166666666</v>
+        <v>45918.89583333334</v>
       </c>
     </row>
     <row r="24">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O24" t="n">
-        <v>3.2</v>
+        <v>3.64</v>
       </c>
       <c r="P24" t="n">
-        <v>2.48</v>
+        <v>2.23</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.55</v>
+        <v>2.79</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="T24" t="n">
-        <v>2.12</v>
+        <v>2.68</v>
       </c>
       <c r="U24" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W24" t="n">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="X24" t="n">
-        <v>4.8</v>
+        <v>3.42</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.48</v>
+        <v>1.91</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.43</v>
+        <v>1.87</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.18</v>
+        <v>3.04</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.58</v>
+        <v>1.36</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.43</v>
+        <v>1.61</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3586,264 +3586,6 @@
         <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45918.85416666666</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
-        <v>45918</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>South America Copa Libertadores</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Flamengo</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Estudiantes</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L25" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="M25" t="n">
-        <v>4</v>
-      </c>
-      <c r="N25" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="O25" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="T25" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="X25" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK25" s="3" t="n">
-        <v>45918.89583333334</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
-        <v>45918</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Angel City</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Washington Spirit</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L26" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="M26" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N26" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="O26" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="P26" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X26" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK26" s="3" t="n">
         <v>45918.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-09-18.xlsx
+++ b/jogos_2025-09-18.xlsx
@@ -762,22 +762,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.23</v>
+        <v>2.55</v>
       </c>
       <c r="M11" t="n">
-        <v>3.35</v>
+        <v>3.72</v>
       </c>
       <c r="N11" t="n">
-        <v>2.17</v>
+        <v>2.44</v>
       </c>
       <c r="O11" t="n">
-        <v>3.75</v>
+        <v>3.33</v>
       </c>
       <c r="P11" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.52</v>
+        <v>2.96</v>
       </c>
       <c r="R11" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S11" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="T11" t="n">
-        <v>2.82</v>
+        <v>2.28</v>
       </c>
       <c r="U11" t="n">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="V11" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="X11" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.67</v>
+        <v>1.51</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>1.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.55</v>
+        <v>3.23</v>
       </c>
       <c r="M12" t="n">
-        <v>3.72</v>
+        <v>3.35</v>
       </c>
       <c r="N12" t="n">
-        <v>2.44</v>
+        <v>2.17</v>
       </c>
       <c r="O12" t="n">
-        <v>3.33</v>
+        <v>3.75</v>
       </c>
       <c r="P12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z12" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q12" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AA12" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.51</v>
+        <v>1.67</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>1.25</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.11</v>
+        <v>1.63</v>
       </c>
       <c r="M16" t="n">
-        <v>8.800000000000001</v>
+        <v>3.95</v>
       </c>
       <c r="N16" t="n">
-        <v>19</v>
+        <v>4.9</v>
       </c>
       <c r="O16" t="n">
-        <v>1.42</v>
+        <v>2.19</v>
       </c>
       <c r="P16" t="n">
-        <v>3.13</v>
+        <v>2.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>12</v>
+        <v>5.2</v>
       </c>
       <c r="R16" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="S16" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="T16" t="n">
-        <v>2</v>
+        <v>2.43</v>
       </c>
       <c r="U16" t="n">
-        <v>1.83</v>
+        <v>1.54</v>
       </c>
       <c r="V16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W16" t="n">
-        <v>1.07</v>
+        <v>1.22</v>
       </c>
       <c r="X16" t="n">
-        <v>6.25</v>
+        <v>4.3</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Z16" t="n">
         <v>2.35</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.87</v>
+        <v>2.74</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.87</v>
+        <v>1.41</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.34</v>
+        <v>1.75</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.53</v>
+        <v>2.03</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="AH16" t="n">
-        <v>7.2</v>
+        <v>2.26</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.63</v>
+        <v>1.11</v>
       </c>
       <c r="M17" t="n">
-        <v>3.95</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>4.9</v>
+        <v>19</v>
       </c>
       <c r="O17" t="n">
-        <v>2.19</v>
+        <v>1.42</v>
       </c>
       <c r="P17" t="n">
-        <v>2.2</v>
+        <v>3.13</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.2</v>
+        <v>12</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="S17" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="T17" t="n">
-        <v>2.43</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
-        <v>1.54</v>
+        <v>1.83</v>
       </c>
       <c r="V17" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W17" t="n">
-        <v>1.22</v>
+        <v>1.07</v>
       </c>
       <c r="X17" t="n">
-        <v>4.3</v>
+        <v>6.25</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="Z17" t="n">
         <v>2.35</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.74</v>
+        <v>1.87</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.41</v>
+        <v>1.87</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.75</v>
+        <v>2.34</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.03</v>
+        <v>1.53</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.26</v>
+        <v>7.2</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,77 +2733,77 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.02</v>
+        <v>3.02</v>
       </c>
       <c r="M18" t="n">
-        <v>3.85</v>
+        <v>3.68</v>
       </c>
       <c r="N18" t="n">
-        <v>3.17</v>
+        <v>2.14</v>
       </c>
       <c r="O18" t="n">
-        <v>2.49</v>
+        <v>3.56</v>
       </c>
       <c r="P18" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="R18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
         <v>1.25</v>
       </c>
-      <c r="S18" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X18" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AH18" t="n">
-        <v>1.8</v>
+        <v>1.38</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,62 +2862,62 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.02</v>
+        <v>2.02</v>
       </c>
       <c r="M19" t="n">
-        <v>3.68</v>
+        <v>3.85</v>
       </c>
       <c r="N19" t="n">
-        <v>2.14</v>
+        <v>3.17</v>
       </c>
       <c r="O19" t="n">
-        <v>3.56</v>
+        <v>2.49</v>
       </c>
       <c r="P19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AD19" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X19" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>2.75</v>
-      </c>
       <c r="AE19" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.38</v>
+        <v>1.8</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.84</v>
+        <v>2.7</v>
       </c>
       <c r="M20" t="n">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="N20" t="n">
-        <v>4.2</v>
+        <v>2.75</v>
       </c>
       <c r="O20" t="n">
-        <v>2.65</v>
+        <v>3.5</v>
       </c>
       <c r="P20" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.9</v>
+        <v>3.45</v>
       </c>
       <c r="R20" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="S20" t="n">
-        <v>2.35</v>
+        <v>2.23</v>
       </c>
       <c r="T20" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="U20" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="V20" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="W20" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="X20" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AA20" t="n">
-        <v>4.7</v>
+        <v>6.01</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.85</v>
+        <v>1.42</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.7</v>
+        <v>1.84</v>
       </c>
       <c r="M21" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="N21" t="n">
-        <v>2.75</v>
+        <v>4.2</v>
       </c>
       <c r="O21" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="T21" t="n">
         <v>3.5</v>
       </c>
-      <c r="P21" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3.8</v>
-      </c>
       <c r="U21" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="V21" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="W21" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="X21" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="AA21" t="n">
-        <v>6.01</v>
+        <v>4.7</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.19</v>
+        <v>2.14</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.42</v>
+        <v>1.85</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3516,13 +3516,13 @@
         <v>2.1</v>
       </c>
       <c r="O24" t="n">
-        <v>3.64</v>
+        <v>3.52</v>
       </c>
       <c r="P24" t="n">
         <v>2.23</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.79</v>
+        <v>2.77</v>
       </c>
       <c r="R24" t="n">
         <v>1.34</v>
@@ -3543,13 +3543,13 @@
         <v>1.23</v>
       </c>
       <c r="X24" t="n">
-        <v>3.42</v>
+        <v>3.65</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AA24" t="n">
         <v>3.04</v>

--- a/jogos_2025-09-18.xlsx
+++ b/jogos_2025-09-18.xlsx
@@ -633,22 +633,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.35</v>
+        <v>2.97</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O6" t="n">
-        <v>3.12</v>
+        <v>7.9</v>
       </c>
       <c r="P6" t="n">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.2</v>
+        <v>2.09</v>
       </c>
       <c r="R6" t="n">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="S6" t="n">
-        <v>2.06</v>
+        <v>2.41</v>
       </c>
       <c r="T6" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="U6" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="V6" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="W6" t="n">
-        <v>1.71</v>
+        <v>1.38</v>
       </c>
       <c r="X6" t="n">
-        <v>2.05</v>
+        <v>2.62</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.97</v>
+        <v>2.35</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.5</v>
+        <v>4.1</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.37</v>
+        <v>1.23</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.52</v>
+        <v>1.06</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1314,16 +1314,16 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4.33</v>
+        <v>3.7</v>
       </c>
       <c r="M7" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="N7" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="O7" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="P7" t="n">
         <v>2</v>
@@ -1332,59 +1332,59 @@
         <v>2.32</v>
       </c>
       <c r="R7" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="S7" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="T7" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="U7" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="V7" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="W7" t="n">
         <v>1.33</v>
       </c>
       <c r="X7" t="n">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="Y7" t="n">
         <v>2.15</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AA7" t="n">
-        <v>4</v>
+        <v>3.79</v>
       </c>
       <c r="AB7" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH7" t="n">
         <v>1.18</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.2</v>
       </c>
       <c r="AI7" t="n">
         <v>2.75</v>
@@ -1443,40 +1443,40 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="M8" t="n">
-        <v>3.44</v>
+        <v>3.48</v>
       </c>
       <c r="N8" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="O8" t="n">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="P8" t="n">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.88</v>
+        <v>3.6</v>
       </c>
       <c r="R8" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="T8" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="U8" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="V8" t="n">
         <v>1.05</v>
       </c>
       <c r="W8" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X8" t="n">
         <v>3.5</v>
@@ -1485,7 +1485,7 @@
         <v>1.85</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="AA8" t="n">
         <v>2.97</v>
@@ -1494,10 +1494,10 @@
         <v>1.35</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.66</v>
+        <v>1.83</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1572,52 +1572,52 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="M9" t="n">
-        <v>3.37</v>
+        <v>3.1</v>
       </c>
       <c r="N9" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="O9" t="n">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="P9" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="Q9" t="n">
         <v>3.44</v>
       </c>
       <c r="R9" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S9" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="T9" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="U9" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="V9" t="n">
         <v>1</v>
       </c>
       <c r="W9" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="X9" t="n">
-        <v>3.65</v>
+        <v>3.69</v>
       </c>
       <c r="Y9" t="n">
         <v>1.85</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AA9" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="AB9" t="n">
         <v>1.38</v>
@@ -1626,7 +1626,7 @@
         <v>1.65</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.55</v>
+        <v>3.23</v>
       </c>
       <c r="M11" t="n">
-        <v>3.72</v>
+        <v>3.35</v>
       </c>
       <c r="N11" t="n">
-        <v>2.44</v>
+        <v>2.17</v>
       </c>
       <c r="O11" t="n">
-        <v>3.33</v>
+        <v>3.75</v>
       </c>
       <c r="P11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z11" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q11" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AA11" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.51</v>
+        <v>1.67</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>1.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.23</v>
+        <v>2.55</v>
       </c>
       <c r="M12" t="n">
-        <v>3.35</v>
+        <v>3.72</v>
       </c>
       <c r="N12" t="n">
-        <v>2.17</v>
+        <v>2.44</v>
       </c>
       <c r="O12" t="n">
-        <v>3.75</v>
+        <v>3.33</v>
       </c>
       <c r="P12" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.52</v>
+        <v>2.96</v>
       </c>
       <c r="R12" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S12" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="T12" t="n">
-        <v>2.82</v>
+        <v>2.28</v>
       </c>
       <c r="U12" t="n">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="V12" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="X12" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.67</v>
+        <v>1.51</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>1.25</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M13" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="O13" t="n">
         <v>2.07</v>
       </c>
-      <c r="M13" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N13" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W13" t="n">
-        <v>1.63</v>
+        <v>1.41</v>
       </c>
       <c r="X13" t="n">
-        <v>2.13</v>
+        <v>2.74</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.62</v>
+        <v>2.2</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.39</v>
+        <v>2.02</v>
       </c>
       <c r="M14" t="n">
-        <v>3.8</v>
+        <v>2.64</v>
       </c>
       <c r="N14" t="n">
-        <v>6.8</v>
+        <v>4.1</v>
       </c>
       <c r="O14" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.35</v>
+        <v>1.63</v>
       </c>
       <c r="X14" t="n">
-        <v>2.74</v>
+        <v>2.13</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="AA14" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X16" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Y16" t="n">
         <v>1.63</v>
       </c>
-      <c r="M16" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="N16" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="O16" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X16" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.58</v>
-      </c>
       <c r="Z16" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.74</v>
+        <v>2.25</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.41</v>
+        <v>1.57</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.03</v>
+        <v>2.5</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.26</v>
+        <v>1.8</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.02</v>
+        <v>1.63</v>
       </c>
       <c r="M19" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="N19" t="n">
-        <v>3.17</v>
+        <v>4.9</v>
       </c>
       <c r="O19" t="n">
-        <v>2.49</v>
+        <v>2.19</v>
       </c>
       <c r="P19" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.6</v>
+        <v>5.2</v>
       </c>
       <c r="R19" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S19" t="n">
-        <v>3.62</v>
+        <v>3.25</v>
       </c>
       <c r="T19" t="n">
-        <v>2.25</v>
+        <v>2.43</v>
       </c>
       <c r="U19" t="n">
-        <v>1.64</v>
+        <v>1.54</v>
       </c>
       <c r="V19" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W19" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="X19" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.25</v>
+        <v>2.74</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.57</v>
+        <v>1.41</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.5</v>
+        <v>2.03</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.8</v>
+        <v>2.26</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.7</v>
+        <v>1.84</v>
       </c>
       <c r="M20" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="N20" t="n">
-        <v>2.75</v>
+        <v>4.2</v>
       </c>
       <c r="O20" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="T20" t="n">
         <v>3.5</v>
       </c>
-      <c r="P20" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3.8</v>
-      </c>
       <c r="U20" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="V20" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="W20" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="X20" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="AA20" t="n">
-        <v>6.01</v>
+        <v>4.7</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.19</v>
+        <v>2.14</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.42</v>
+        <v>1.85</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.84</v>
+        <v>2.5</v>
       </c>
       <c r="M21" t="n">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="N21" t="n">
-        <v>4.2</v>
+        <v>2.69</v>
       </c>
       <c r="O21" t="n">
-        <v>2.65</v>
+        <v>3.6</v>
       </c>
       <c r="P21" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.9</v>
+        <v>3.45</v>
       </c>
       <c r="R21" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="S21" t="n">
-        <v>2.35</v>
+        <v>2.23</v>
       </c>
       <c r="T21" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="U21" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="V21" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="W21" t="n">
         <v>1.49</v>
       </c>
       <c r="X21" t="n">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>4.7</v>
+        <v>5.15</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.14</v>
+        <v>2.35</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.85</v>
+        <v>1.4</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3258,10 +3258,10 @@
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="P22" t="n">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="Q22" t="n">
         <v>2.7</v>
@@ -3273,10 +3273,10 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="U22" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -3285,7 +3285,7 @@
         <v>1.1</v>
       </c>
       <c r="X22" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="Y22" t="n">
         <v>1.43</v>
@@ -3297,7 +3297,7 @@
         <v>2.16</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AC22" t="n">
         <v>1.48</v>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3516,13 +3516,13 @@
         <v>2.1</v>
       </c>
       <c r="O24" t="n">
-        <v>3.52</v>
+        <v>3.64</v>
       </c>
       <c r="P24" t="n">
-        <v>2.23</v>
+        <v>2.12</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="R24" t="n">
         <v>1.34</v>
@@ -3534,7 +3534,7 @@
         <v>2.68</v>
       </c>
       <c r="U24" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="V24" t="n">
         <v>1.01</v>
@@ -3543,25 +3543,25 @@
         <v>1.23</v>
       </c>
       <c r="X24" t="n">
-        <v>3.65</v>
+        <v>3.42</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>

--- a/jogos_2025-09-18.xlsx
+++ b/jogos_2025-09-18.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK24"/>
+  <dimension ref="A1:AK25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -633,22 +633,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -762,22 +762,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.01</v>
+        <v>2.35</v>
       </c>
       <c r="M8" t="n">
-        <v>3.48</v>
+        <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="O8" t="n">
-        <v>2.56</v>
+        <v>2.49</v>
       </c>
       <c r="P8" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S8" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="T8" t="n">
         <v>3.6</v>
       </c>
-      <c r="R8" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.6</v>
-      </c>
       <c r="U8" t="n">
-        <v>1.4</v>
+        <v>1.21</v>
       </c>
       <c r="V8" t="n">
         <v>1.05</v>
       </c>
       <c r="W8" t="n">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="X8" t="n">
-        <v>3.5</v>
+        <v>2.39</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.85</v>
+        <v>2.49</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.98</v>
+        <v>1.42</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.97</v>
+        <v>5</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.35</v>
+        <v>1.1</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.68</v>
+        <v>2.28</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.09</v>
+        <v>1.55</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,19 +1510,19 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45918.52777777778</v>
+        <v>45918.47916666666</v>
       </c>
     </row>
     <row r="9">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.45</v>
+        <v>2.01</v>
       </c>
       <c r="M9" t="n">
-        <v>3.1</v>
+        <v>3.48</v>
       </c>
       <c r="N9" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="O9" t="n">
-        <v>3</v>
+        <v>2.56</v>
       </c>
       <c r="P9" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.44</v>
+        <v>3.6</v>
       </c>
       <c r="R9" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="T9" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="U9" t="n">
         <v>1.4</v>
       </c>
       <c r="V9" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="W9" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X9" t="n">
-        <v>3.69</v>
+        <v>3.5</v>
       </c>
       <c r="Y9" t="n">
         <v>1.85</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45918.54166666666</v>
+        <v>45918.52777777778</v>
       </c>
     </row>
     <row r="11">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45918.57291666666</v>
+        <v>45918.54166666666</v>
       </c>
     </row>
     <row r="12">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.55</v>
+        <v>3.23</v>
       </c>
       <c r="M12" t="n">
-        <v>3.72</v>
+        <v>3.35</v>
       </c>
       <c r="N12" t="n">
-        <v>2.44</v>
+        <v>2.17</v>
       </c>
       <c r="O12" t="n">
-        <v>3.33</v>
+        <v>3.75</v>
       </c>
       <c r="P12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z12" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q12" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AA12" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.51</v>
+        <v>1.67</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>1.25</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,78 +2088,78 @@
         </is>
       </c>
       <c r="L13" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="M13" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="O13" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH13" t="n">
         <v>1.44</v>
       </c>
-      <c r="M13" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="N13" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O13" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>2.65</v>
-      </c>
       <c r="AI13" t="n">
         <v>0</v>
       </c>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45918.58333333334</v>
+        <v>45918.57291666666</v>
       </c>
     </row>
     <row r="14">
@@ -2305,12 +2305,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45918.625</v>
+        <v>45918.58333333334</v>
       </c>
     </row>
     <row r="16">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45918.66666666666</v>
+        <v>45918.625</v>
       </c>
     </row>
     <row r="17">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.11</v>
+        <v>2.02</v>
       </c>
       <c r="M17" t="n">
-        <v>8.800000000000001</v>
+        <v>3.85</v>
       </c>
       <c r="N17" t="n">
-        <v>19</v>
+        <v>3.17</v>
       </c>
       <c r="O17" t="n">
-        <v>1.42</v>
+        <v>2.49</v>
       </c>
       <c r="P17" t="n">
-        <v>3.13</v>
+        <v>2.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>12</v>
+        <v>3.6</v>
       </c>
       <c r="R17" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="S17" t="n">
-        <v>4.2</v>
+        <v>3.62</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="U17" t="n">
-        <v>1.83</v>
+        <v>1.64</v>
       </c>
       <c r="V17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W17" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X17" t="n">
-        <v>6.25</v>
+        <v>4.9</v>
       </c>
       <c r="Y17" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB17" t="n">
         <v>1.57</v>
       </c>
-      <c r="Z17" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.87</v>
-      </c>
       <c r="AC17" t="n">
-        <v>2.34</v>
+        <v>1.44</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.53</v>
+        <v>2.5</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="AH17" t="n">
-        <v>7.2</v>
+        <v>1.8</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.02</v>
+        <v>1.63</v>
       </c>
       <c r="M18" t="n">
-        <v>3.68</v>
+        <v>3.95</v>
       </c>
       <c r="N18" t="n">
-        <v>2.14</v>
+        <v>4.9</v>
       </c>
       <c r="O18" t="n">
-        <v>3.56</v>
+        <v>2.19</v>
       </c>
       <c r="P18" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.5</v>
+        <v>5.2</v>
       </c>
       <c r="R18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W18" t="n">
         <v>1.22</v>
       </c>
-      <c r="S18" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.1</v>
-      </c>
       <c r="X18" t="n">
-        <v>5.5</v>
+        <v>4.3</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.05</v>
+        <v>2.74</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.77</v>
+        <v>1.41</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.41</v>
+        <v>1.75</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.75</v>
+        <v>2.03</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.38</v>
+        <v>2.26</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.63</v>
+        <v>1.11</v>
       </c>
       <c r="M19" t="n">
-        <v>3.95</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="N19" t="n">
-        <v>4.9</v>
+        <v>19</v>
       </c>
       <c r="O19" t="n">
-        <v>2.19</v>
+        <v>1.42</v>
       </c>
       <c r="P19" t="n">
-        <v>2.2</v>
+        <v>3.13</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.2</v>
+        <v>12</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="S19" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="T19" t="n">
-        <v>2.43</v>
+        <v>2</v>
       </c>
       <c r="U19" t="n">
-        <v>1.54</v>
+        <v>1.83</v>
       </c>
       <c r="V19" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W19" t="n">
-        <v>1.22</v>
+        <v>1.07</v>
       </c>
       <c r="X19" t="n">
-        <v>4.3</v>
+        <v>6.25</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="Z19" t="n">
         <v>2.35</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.74</v>
+        <v>1.87</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.41</v>
+        <v>1.87</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.75</v>
+        <v>2.34</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.03</v>
+        <v>1.53</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.26</v>
+        <v>7.2</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2950,27 +2950,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.84</v>
+        <v>3.02</v>
       </c>
       <c r="M20" t="n">
-        <v>2.95</v>
+        <v>3.68</v>
       </c>
       <c r="N20" t="n">
-        <v>4.2</v>
+        <v>2.14</v>
       </c>
       <c r="O20" t="n">
-        <v>2.65</v>
+        <v>3.56</v>
       </c>
       <c r="P20" t="n">
-        <v>1.92</v>
+        <v>2.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.9</v>
+        <v>2.5</v>
       </c>
       <c r="R20" t="n">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="S20" t="n">
-        <v>2.35</v>
+        <v>3.7</v>
       </c>
       <c r="T20" t="n">
-        <v>3.5</v>
+        <v>2.1</v>
       </c>
       <c r="U20" t="n">
-        <v>1.23</v>
+        <v>1.65</v>
       </c>
       <c r="V20" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W20" t="n">
-        <v>1.49</v>
+        <v>1.1</v>
       </c>
       <c r="X20" t="n">
-        <v>2.6</v>
+        <v>5.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.45</v>
+        <v>1.45</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.55</v>
+        <v>2.7</v>
       </c>
       <c r="AA20" t="n">
-        <v>4.7</v>
+        <v>2.05</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.14</v>
+        <v>1.77</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.14</v>
+        <v>1.41</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.64</v>
+        <v>2.75</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.85</v>
+        <v>1.38</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45918.79166666666</v>
+        <v>45918.66666666666</v>
       </c>
     </row>
     <row r="21">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.5</v>
+        <v>1.84</v>
       </c>
       <c r="M21" t="n">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="N21" t="n">
-        <v>2.69</v>
+        <v>4.2</v>
       </c>
       <c r="O21" t="n">
-        <v>3.6</v>
+        <v>2.65</v>
       </c>
       <c r="P21" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.45</v>
+        <v>4.9</v>
       </c>
       <c r="R21" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="S21" t="n">
-        <v>2.23</v>
+        <v>2.35</v>
       </c>
       <c r="T21" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="U21" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="V21" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="W21" t="n">
         <v>1.49</v>
       </c>
       <c r="X21" t="n">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AA21" t="n">
-        <v>5.15</v>
+        <v>4.7</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.35</v>
+        <v>2.14</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.4</v>
+        <v>1.85</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3208,12 +3208,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,62 +3249,62 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="O22" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="P22" t="n">
-        <v>2.45</v>
+        <v>1.88</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.7</v>
+        <v>3.45</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="T22" t="n">
-        <v>2.18</v>
+        <v>3.8</v>
       </c>
       <c r="U22" t="n">
-        <v>1.64</v>
+        <v>1.22</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W22" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="X22" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="AB22" t="n">
         <v>1.1</v>
       </c>
-      <c r="X22" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AB22" t="n">
+      <c r="AC22" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AD22" t="n">
         <v>1.58</v>
       </c>
-      <c r="AC22" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AE22" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45918.85416666666</v>
+        <v>45918.79166666666</v>
       </c>
     </row>
     <row r="23">
@@ -3337,12 +3337,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>1.9</v>
+        <v>3.35</v>
       </c>
       <c r="P23" t="n">
-        <v>2.01</v>
+        <v>2.45</v>
       </c>
       <c r="Q23" t="n">
-        <v>9.5</v>
+        <v>2.7</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z23" t="n">
         <v>2.43</v>
       </c>
-      <c r="T23" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="X23" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AA23" t="n">
-        <v>4.8</v>
+        <v>2.16</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.13</v>
+        <v>1.58</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.25</v>
+        <v>1.48</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.31</v>
+        <v>2.5</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.99</v>
+        <v>1.37</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45918.89583333334</v>
+        <v>45918.85416666666</v>
       </c>
     </row>
     <row r="24">
@@ -3466,126 +3466,255 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>South America Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Estudiantes</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M24" t="n">
+        <v>4</v>
+      </c>
+      <c r="N24" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X24" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK24" s="3" t="n">
+        <v>45918.89583333334</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>45918</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
           <t>23:30</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Angel City</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>Washington Spirit</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="inlineStr">
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L24" t="n">
+      <c r="L25" t="n">
         <v>3.15</v>
       </c>
-      <c r="M24" t="n">
+      <c r="M25" t="n">
         <v>3.5</v>
       </c>
-      <c r="N24" t="n">
+      <c r="N25" t="n">
         <v>2.1</v>
       </c>
-      <c r="O24" t="n">
+      <c r="O25" t="n">
         <v>3.64</v>
       </c>
-      <c r="P24" t="n">
+      <c r="P25" t="n">
         <v>2.12</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="Q25" t="n">
         <v>2.79</v>
       </c>
-      <c r="R24" t="n">
+      <c r="R25" t="n">
         <v>1.34</v>
       </c>
-      <c r="S24" t="n">
+      <c r="S25" t="n">
         <v>2.89</v>
       </c>
-      <c r="T24" t="n">
+      <c r="T25" t="n">
         <v>2.68</v>
       </c>
-      <c r="U24" t="n">
+      <c r="U25" t="n">
         <v>1.39</v>
       </c>
-      <c r="V24" t="n">
+      <c r="V25" t="n">
         <v>1.01</v>
       </c>
-      <c r="W24" t="n">
+      <c r="W25" t="n">
         <v>1.23</v>
       </c>
-      <c r="X24" t="n">
+      <c r="X25" t="n">
         <v>3.42</v>
       </c>
-      <c r="Y24" t="n">
+      <c r="Y25" t="n">
         <v>1.85</v>
       </c>
-      <c r="Z24" t="n">
+      <c r="Z25" t="n">
         <v>1.85</v>
       </c>
-      <c r="AA24" t="n">
+      <c r="AA25" t="n">
         <v>2.97</v>
       </c>
-      <c r="AB24" t="n">
+      <c r="AB25" t="n">
         <v>1.3</v>
       </c>
-      <c r="AC24" t="n">
+      <c r="AC25" t="n">
         <v>1.66</v>
       </c>
-      <c r="AD24" t="n">
+      <c r="AD25" t="n">
         <v>2.04</v>
       </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
         <v>1.24</v>
       </c>
-      <c r="AH24" t="n">
+      <c r="AH25" t="n">
         <v>1.32</v>
       </c>
-      <c r="AI24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK24" s="3" t="n">
+      <c r="AI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK25" s="3" t="n">
         <v>45918.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-09-18.xlsx
+++ b/jogos_2025-09-18.xlsx
@@ -762,22 +762,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1068,25 +1068,25 @@
         <v>3.15</v>
       </c>
       <c r="P5" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.56</v>
+        <v>4.57</v>
       </c>
       <c r="R5" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="S5" t="n">
         <v>2.06</v>
       </c>
       <c r="T5" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="U5" t="n">
         <v>1.17</v>
       </c>
       <c r="V5" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="W5" t="n">
         <v>1.57</v>
@@ -1095,7 +1095,7 @@
         <v>2.07</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.97</v>
+        <v>3.22</v>
       </c>
       <c r="Z5" t="n">
         <v>1.3</v>
@@ -1194,22 +1194,22 @@
         <v>1.45</v>
       </c>
       <c r="O6" t="n">
-        <v>7.9</v>
+        <v>7</v>
       </c>
       <c r="P6" t="n">
         <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.09</v>
+        <v>1.98</v>
       </c>
       <c r="R6" t="n">
         <v>1.5</v>
       </c>
       <c r="S6" t="n">
-        <v>2.41</v>
+        <v>2.55</v>
       </c>
       <c r="T6" t="n">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="U6" t="n">
         <v>1.28</v>
@@ -1218,7 +1218,7 @@
         <v>1.04</v>
       </c>
       <c r="W6" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="X6" t="n">
         <v>2.62</v>
@@ -1230,16 +1230,16 @@
         <v>1.53</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.7</v>
+        <v>4.68</v>
       </c>
       <c r="M7" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="N7" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="O7" t="n">
         <v>4.8</v>
@@ -1332,43 +1332,43 @@
         <v>2.32</v>
       </c>
       <c r="R7" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S7" t="n">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="T7" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="U7" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V7" t="n">
         <v>1.07</v>
       </c>
       <c r="W7" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="X7" t="n">
-        <v>3.08</v>
+        <v>2.88</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AA7" t="n">
         <v>3.79</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AC7" t="n">
         <v>2</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AI7" t="n">
         <v>2.75</v>
@@ -1476,10 +1476,10 @@
         <v>1.05</v>
       </c>
       <c r="W8" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="X8" t="n">
-        <v>2.39</v>
+        <v>2.25</v>
       </c>
       <c r="Y8" t="n">
         <v>2.49</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.01</v>
+        <v>2.45</v>
       </c>
       <c r="M9" t="n">
-        <v>3.48</v>
+        <v>3.1</v>
       </c>
       <c r="N9" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="O9" t="n">
-        <v>2.56</v>
+        <v>3</v>
       </c>
       <c r="P9" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.6</v>
+        <v>3.44</v>
       </c>
       <c r="R9" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S9" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="T9" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="U9" t="n">
         <v>1.4</v>
       </c>
       <c r="V9" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="W9" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X9" t="n">
-        <v>3.5</v>
+        <v>3.69</v>
       </c>
       <c r="Y9" t="n">
         <v>1.85</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.45</v>
+        <v>2.01</v>
       </c>
       <c r="M10" t="n">
-        <v>3.1</v>
+        <v>3.48</v>
       </c>
       <c r="N10" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="O10" t="n">
-        <v>3</v>
+        <v>2.56</v>
       </c>
       <c r="P10" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.44</v>
+        <v>3.6</v>
       </c>
       <c r="R10" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="T10" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="U10" t="n">
         <v>1.4</v>
       </c>
       <c r="V10" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="W10" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X10" t="n">
-        <v>3.69</v>
+        <v>3.5</v>
       </c>
       <c r="Y10" t="n">
         <v>1.85</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.23</v>
+        <v>2.55</v>
       </c>
       <c r="M12" t="n">
-        <v>3.35</v>
+        <v>3.72</v>
       </c>
       <c r="N12" t="n">
-        <v>2.17</v>
+        <v>2.44</v>
       </c>
       <c r="O12" t="n">
-        <v>3.75</v>
+        <v>3.33</v>
       </c>
       <c r="P12" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.52</v>
+        <v>2.96</v>
       </c>
       <c r="R12" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S12" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="T12" t="n">
-        <v>2.82</v>
+        <v>2.28</v>
       </c>
       <c r="U12" t="n">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="V12" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="X12" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.67</v>
+        <v>1.51</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>1.25</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.55</v>
+        <v>3.23</v>
       </c>
       <c r="M13" t="n">
-        <v>3.72</v>
+        <v>3.35</v>
       </c>
       <c r="N13" t="n">
-        <v>2.44</v>
+        <v>2.17</v>
       </c>
       <c r="O13" t="n">
-        <v>3.33</v>
+        <v>3.75</v>
       </c>
       <c r="P13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z13" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q13" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AA13" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.51</v>
+        <v>1.67</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>1.25</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>2.13</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2346,40 +2346,40 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="M15" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="N15" t="n">
         <v>6.8</v>
       </c>
       <c r="O15" t="n">
-        <v>2.07</v>
+        <v>1.96</v>
       </c>
       <c r="P15" t="n">
         <v>2.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="R15" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="S15" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="T15" t="n">
         <v>3.26</v>
       </c>
       <c r="U15" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="V15" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="W15" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="X15" t="n">
         <v>2.74</v>
@@ -2388,16 +2388,16 @@
         <v>2.2</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.96</v>
+        <v>4.15</v>
       </c>
       <c r="AB15" t="n">
         <v>1.17</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.61</v>
+        <v>2.42</v>
       </c>
       <c r="AD15" t="n">
         <v>1.48</v>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.07</v>
+        <v>1.22</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.02</v>
+        <v>1.11</v>
       </c>
       <c r="M17" t="n">
-        <v>3.85</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>3.17</v>
+        <v>19</v>
       </c>
       <c r="O17" t="n">
-        <v>2.49</v>
+        <v>1.42</v>
       </c>
       <c r="P17" t="n">
-        <v>2.3</v>
+        <v>3.13</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.6</v>
+        <v>12</v>
       </c>
       <c r="R17" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="S17" t="n">
-        <v>3.62</v>
+        <v>4.2</v>
       </c>
       <c r="T17" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="V17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W17" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X17" t="n">
-        <v>4.9</v>
+        <v>6.25</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.25</v>
+        <v>1.87</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.57</v>
+        <v>1.87</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.44</v>
+        <v>2.34</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.5</v>
+        <v>1.53</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.8</v>
+        <v>7.2</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.63</v>
+        <v>3.02</v>
       </c>
       <c r="M18" t="n">
-        <v>3.95</v>
+        <v>3.68</v>
       </c>
       <c r="N18" t="n">
-        <v>4.9</v>
+        <v>2.14</v>
       </c>
       <c r="O18" t="n">
-        <v>2.19</v>
+        <v>3.56</v>
       </c>
       <c r="P18" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.2</v>
+        <v>2.5</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="S18" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="T18" t="n">
-        <v>2.43</v>
+        <v>2.1</v>
       </c>
       <c r="U18" t="n">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="V18" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W18" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="X18" t="n">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.35</v>
+        <v>2.7</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.74</v>
+        <v>2.05</v>
       </c>
       <c r="AB18" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC18" t="n">
         <v>1.41</v>
       </c>
-      <c r="AC18" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AD18" t="n">
-        <v>2.03</v>
+        <v>2.75</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.26</v>
+        <v>1.38</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.11</v>
+        <v>1.63</v>
       </c>
       <c r="M19" t="n">
-        <v>8.800000000000001</v>
+        <v>3.95</v>
       </c>
       <c r="N19" t="n">
-        <v>19</v>
+        <v>4.9</v>
       </c>
       <c r="O19" t="n">
-        <v>1.42</v>
+        <v>2.19</v>
       </c>
       <c r="P19" t="n">
-        <v>3.13</v>
+        <v>2.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>12</v>
+        <v>5.2</v>
       </c>
       <c r="R19" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="S19" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="T19" t="n">
-        <v>2</v>
+        <v>2.43</v>
       </c>
       <c r="U19" t="n">
-        <v>1.83</v>
+        <v>1.54</v>
       </c>
       <c r="V19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W19" t="n">
-        <v>1.07</v>
+        <v>1.22</v>
       </c>
       <c r="X19" t="n">
-        <v>6.25</v>
+        <v>4.3</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Z19" t="n">
         <v>2.35</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.87</v>
+        <v>2.74</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.87</v>
+        <v>1.41</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.34</v>
+        <v>1.75</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.53</v>
+        <v>2.03</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="AH19" t="n">
-        <v>7.2</v>
+        <v>2.26</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,62 +2991,62 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.02</v>
+        <v>2.02</v>
       </c>
       <c r="M20" t="n">
-        <v>3.68</v>
+        <v>3.85</v>
       </c>
       <c r="N20" t="n">
-        <v>2.14</v>
+        <v>3.17</v>
       </c>
       <c r="O20" t="n">
-        <v>3.56</v>
+        <v>2.49</v>
       </c>
       <c r="P20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X20" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AD20" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X20" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>2.75</v>
-      </c>
       <c r="AE20" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.38</v>
+        <v>1.8</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.84</v>
+        <v>2.5</v>
       </c>
       <c r="M21" t="n">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="N21" t="n">
-        <v>4.2</v>
+        <v>2.69</v>
       </c>
       <c r="O21" t="n">
-        <v>2.65</v>
+        <v>3.5</v>
       </c>
       <c r="P21" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.9</v>
+        <v>3.45</v>
       </c>
       <c r="R21" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="S21" t="n">
-        <v>2.35</v>
+        <v>2.23</v>
       </c>
       <c r="T21" t="n">
-        <v>3.5</v>
+        <v>3.66</v>
       </c>
       <c r="U21" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="V21" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="W21" t="n">
         <v>1.49</v>
       </c>
       <c r="X21" t="n">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>4.7</v>
+        <v>5.15</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.85</v>
+        <v>1.42</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.5</v>
+        <v>1.84</v>
       </c>
       <c r="M22" t="n">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="N22" t="n">
-        <v>2.69</v>
+        <v>4.2</v>
       </c>
       <c r="O22" t="n">
-        <v>3.6</v>
+        <v>2.65</v>
       </c>
       <c r="P22" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.45</v>
+        <v>4.9</v>
       </c>
       <c r="R22" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="S22" t="n">
-        <v>2.23</v>
+        <v>2.35</v>
       </c>
       <c r="T22" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="U22" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="V22" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="W22" t="n">
         <v>1.49</v>
       </c>
       <c r="X22" t="n">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AA22" t="n">
-        <v>5.15</v>
+        <v>4.7</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.35</v>
+        <v>2.14</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.4</v>
+        <v>1.85</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3645,25 +3645,25 @@
         <v>2.1</v>
       </c>
       <c r="O25" t="n">
-        <v>3.64</v>
+        <v>3.15</v>
       </c>
       <c r="P25" t="n">
         <v>2.12</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.79</v>
+        <v>2.9</v>
       </c>
       <c r="R25" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S25" t="n">
-        <v>2.89</v>
+        <v>2.83</v>
       </c>
       <c r="T25" t="n">
         <v>2.68</v>
       </c>
       <c r="U25" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="V25" t="n">
         <v>1.01</v>
@@ -3681,16 +3681,16 @@
         <v>1.85</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.97</v>
+        <v>2.85</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.24</v>
+        <v>1.48</v>
       </c>
       <c r="AH25" t="n">
         <v>1.32</v>

--- a/jogos_2025-09-18.xlsx
+++ b/jogos_2025-09-18.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O5" t="n">
-        <v>3.15</v>
+        <v>7</v>
       </c>
       <c r="P5" t="n">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.57</v>
+        <v>1.98</v>
       </c>
       <c r="R5" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="S5" t="n">
-        <v>2.06</v>
+        <v>2.55</v>
       </c>
       <c r="T5" t="n">
-        <v>4.2</v>
+        <v>3.34</v>
       </c>
       <c r="U5" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="V5" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="W5" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Z5" t="n">
         <v>1.57</v>
       </c>
-      <c r="X5" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AA5" t="n">
-        <v>6.1</v>
+        <v>4.33</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="AC5" t="n">
         <v>2.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.37</v>
+        <v>1.2</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.52</v>
+        <v>1.05</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>7</v>
+        <v>3.25</v>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.98</v>
+        <v>4.57</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="S6" t="n">
-        <v>2.55</v>
+        <v>2.06</v>
       </c>
       <c r="T6" t="n">
-        <v>3.34</v>
+        <v>4.2</v>
       </c>
       <c r="U6" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="V6" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="W6" t="n">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="X6" t="n">
-        <v>2.62</v>
+        <v>2.07</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.35</v>
+        <v>3.22</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.33</v>
+        <v>6.15</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.38</v>
+        <v>2.57</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.2</v>
+        <v>1.37</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.05</v>
+        <v>1.52</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1476,10 +1476,10 @@
         <v>1.05</v>
       </c>
       <c r="W8" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="X8" t="n">
-        <v>2.25</v>
+        <v>2.39</v>
       </c>
       <c r="Y8" t="n">
         <v>2.49</v>
@@ -1572,34 +1572,34 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.45</v>
+        <v>2.36</v>
       </c>
       <c r="M9" t="n">
         <v>3.1</v>
       </c>
       <c r="N9" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="O9" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="P9" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.44</v>
+        <v>3.43</v>
       </c>
       <c r="R9" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="T9" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="U9" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="V9" t="n">
         <v>1</v>
@@ -1608,13 +1608,13 @@
         <v>1.25</v>
       </c>
       <c r="X9" t="n">
-        <v>3.69</v>
+        <v>3.7</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AA9" t="n">
         <v>2.92</v>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1704,19 +1704,19 @@
         <v>2.01</v>
       </c>
       <c r="M10" t="n">
-        <v>3.48</v>
+        <v>3.65</v>
       </c>
       <c r="N10" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="O10" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="P10" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="R10" t="n">
         <v>1.34</v>
@@ -1725,7 +1725,7 @@
         <v>2.98</v>
       </c>
       <c r="T10" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="U10" t="n">
         <v>1.4</v>
@@ -1737,25 +1737,25 @@
         <v>1.22</v>
       </c>
       <c r="X10" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="AA10" t="n">
         <v>2.97</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AC10" t="n">
         <v>1.68</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>1.25</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.02</v>
+        <v>1.4</v>
       </c>
       <c r="M14" t="n">
-        <v>2.64</v>
+        <v>3.88</v>
       </c>
       <c r="N14" t="n">
-        <v>4.1</v>
+        <v>6.8</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W14" t="n">
-        <v>1.63</v>
+        <v>1.4</v>
       </c>
       <c r="X14" t="n">
-        <v>2.13</v>
+        <v>2.78</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Z15" t="n">
         <v>1.4</v>
       </c>
-      <c r="M15" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N15" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>7</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X15" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.61</v>
-      </c>
       <c r="AA15" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2484,52 +2484,52 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>5.89</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.11</v>
+        <v>3.02</v>
       </c>
       <c r="M17" t="n">
-        <v>8.800000000000001</v>
+        <v>3.68</v>
       </c>
       <c r="N17" t="n">
-        <v>19</v>
+        <v>2.14</v>
       </c>
       <c r="O17" t="n">
-        <v>1.42</v>
+        <v>3.56</v>
       </c>
       <c r="P17" t="n">
-        <v>3.13</v>
+        <v>2.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>12</v>
+        <v>2.5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="S17" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="U17" t="n">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="V17" t="n">
         <v>1.01</v>
       </c>
       <c r="W17" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X17" t="n">
-        <v>6.25</v>
+        <v>5.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.35</v>
+        <v>2.7</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.34</v>
+        <v>1.41</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.53</v>
+        <v>2.75</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>7.2</v>
+        <v>1.38</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,62 +2733,62 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.02</v>
+        <v>2.02</v>
       </c>
       <c r="M18" t="n">
-        <v>3.68</v>
+        <v>3.85</v>
       </c>
       <c r="N18" t="n">
-        <v>2.14</v>
+        <v>3.17</v>
       </c>
       <c r="O18" t="n">
-        <v>3.56</v>
+        <v>2.49</v>
       </c>
       <c r="P18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X18" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AD18" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X18" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>2.75</v>
-      </c>
       <c r="AE18" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.38</v>
+        <v>1.8</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.02</v>
+        <v>1.11</v>
       </c>
       <c r="M20" t="n">
-        <v>3.85</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>3.17</v>
+        <v>19</v>
       </c>
       <c r="O20" t="n">
-        <v>2.49</v>
+        <v>1.42</v>
       </c>
       <c r="P20" t="n">
-        <v>2.3</v>
+        <v>3.13</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.6</v>
+        <v>12</v>
       </c>
       <c r="R20" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="S20" t="n">
-        <v>3.62</v>
+        <v>4.2</v>
       </c>
       <c r="T20" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="V20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W20" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X20" t="n">
-        <v>4.9</v>
+        <v>6.25</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.25</v>
+        <v>1.87</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.57</v>
+        <v>1.87</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.44</v>
+        <v>2.34</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.5</v>
+        <v>1.53</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.8</v>
+        <v>7.2</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>

--- a/jogos_2025-09-18.xlsx
+++ b/jogos_2025-09-18.xlsx
@@ -762,22 +762,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>7</v>
+        <v>3.25</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.98</v>
+        <v>4.57</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="S5" t="n">
-        <v>2.55</v>
+        <v>2.06</v>
       </c>
       <c r="T5" t="n">
-        <v>3.34</v>
+        <v>4.2</v>
       </c>
       <c r="U5" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="V5" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="W5" t="n">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="X5" t="n">
-        <v>2.62</v>
+        <v>2.07</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.26</v>
+        <v>3.22</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.57</v>
+        <v>1.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.33</v>
+        <v>6.15</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.4</v>
+        <v>2.57</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.2</v>
+        <v>1.37</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.05</v>
+        <v>1.52</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O6" t="n">
-        <v>3.25</v>
+        <v>7</v>
       </c>
       <c r="P6" t="n">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.57</v>
+        <v>1.98</v>
       </c>
       <c r="R6" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="S6" t="n">
-        <v>2.06</v>
+        <v>2.55</v>
       </c>
       <c r="T6" t="n">
-        <v>4.2</v>
+        <v>3.34</v>
       </c>
       <c r="U6" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="V6" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="W6" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Z6" t="n">
         <v>1.57</v>
       </c>
-      <c r="X6" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AA6" t="n">
-        <v>6.15</v>
+        <v>4.33</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.57</v>
+        <v>2.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.37</v>
+        <v>1.2</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.52</v>
+        <v>1.05</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1317,31 +1317,31 @@
         <v>4.68</v>
       </c>
       <c r="M7" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N7" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="O7" t="n">
         <v>4.8</v>
       </c>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q7" t="n">
         <v>2.32</v>
       </c>
       <c r="R7" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="S7" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="T7" t="n">
         <v>3</v>
       </c>
       <c r="U7" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="V7" t="n">
         <v>1.07</v>
@@ -1362,13 +1362,13 @@
         <v>3.79</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AC7" t="n">
         <v>2</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1452,13 +1452,13 @@
         <v>3.1</v>
       </c>
       <c r="O8" t="n">
-        <v>2.49</v>
+        <v>2.54</v>
       </c>
       <c r="P8" t="n">
         <v>1.89</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.73</v>
+        <v>5.51</v>
       </c>
       <c r="R8" t="n">
         <v>1.55</v>
@@ -1467,10 +1467,10 @@
         <v>2.3</v>
       </c>
       <c r="T8" t="n">
-        <v>3.6</v>
+        <v>3.52</v>
       </c>
       <c r="U8" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="V8" t="n">
         <v>1.05</v>
@@ -1488,16 +1488,16 @@
         <v>1.42</v>
       </c>
       <c r="AA8" t="n">
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.28</v>
+        <v>2.23</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AI8" t="n">
         <v>1.65</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.55</v>
+        <v>3.23</v>
       </c>
       <c r="M12" t="n">
-        <v>3.72</v>
+        <v>3.35</v>
       </c>
       <c r="N12" t="n">
-        <v>2.44</v>
+        <v>2.17</v>
       </c>
       <c r="O12" t="n">
-        <v>3.33</v>
+        <v>3.75</v>
       </c>
       <c r="P12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z12" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q12" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AA12" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.51</v>
+        <v>1.67</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>1.25</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.23</v>
+        <v>2.55</v>
       </c>
       <c r="M13" t="n">
-        <v>3.35</v>
+        <v>3.72</v>
       </c>
       <c r="N13" t="n">
-        <v>2.17</v>
+        <v>2.44</v>
       </c>
       <c r="O13" t="n">
-        <v>3.75</v>
+        <v>3.33</v>
       </c>
       <c r="P13" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.52</v>
+        <v>2.96</v>
       </c>
       <c r="R13" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S13" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="T13" t="n">
-        <v>2.82</v>
+        <v>2.28</v>
       </c>
       <c r="U13" t="n">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="V13" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W13" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="X13" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.67</v>
+        <v>1.51</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>1.25</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Z14" t="n">
         <v>1.4</v>
       </c>
-      <c r="M14" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="N14" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>7</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AA14" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.09</v>
+        <v>1.4</v>
       </c>
       <c r="M15" t="n">
-        <v>2.82</v>
+        <v>3.88</v>
       </c>
       <c r="N15" t="n">
-        <v>3.9</v>
+        <v>6.8</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W15" t="n">
-        <v>1.63</v>
+        <v>1.4</v>
       </c>
       <c r="X15" t="n">
-        <v>2.13</v>
+        <v>2.78</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.02</v>
+        <v>1.11</v>
       </c>
       <c r="M17" t="n">
-        <v>3.68</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>2.14</v>
+        <v>19</v>
       </c>
       <c r="O17" t="n">
-        <v>3.56</v>
+        <v>1.42</v>
       </c>
       <c r="P17" t="n">
-        <v>2.5</v>
+        <v>3.13</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.5</v>
+        <v>12</v>
       </c>
       <c r="R17" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="S17" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="T17" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="V17" t="n">
         <v>1.01</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X17" t="n">
-        <v>5.5</v>
+        <v>6.25</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.41</v>
+        <v>2.34</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.75</v>
+        <v>1.53</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.38</v>
+        <v>7.2</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.02</v>
+        <v>1.63</v>
       </c>
       <c r="M18" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="N18" t="n">
-        <v>3.17</v>
+        <v>4.9</v>
       </c>
       <c r="O18" t="n">
-        <v>2.49</v>
+        <v>2.19</v>
       </c>
       <c r="P18" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.6</v>
+        <v>5.2</v>
       </c>
       <c r="R18" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S18" t="n">
-        <v>3.62</v>
+        <v>3.25</v>
       </c>
       <c r="T18" t="n">
-        <v>2.25</v>
+        <v>2.43</v>
       </c>
       <c r="U18" t="n">
-        <v>1.64</v>
+        <v>1.54</v>
       </c>
       <c r="V18" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W18" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="X18" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.25</v>
+        <v>2.74</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.57</v>
+        <v>1.41</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.5</v>
+        <v>2.03</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.8</v>
+        <v>2.26</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Y19" t="n">
         <v>1.63</v>
       </c>
-      <c r="M19" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="N19" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="O19" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X19" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.58</v>
-      </c>
       <c r="Z19" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.74</v>
+        <v>2.25</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.41</v>
+        <v>1.57</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.03</v>
+        <v>2.5</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.26</v>
+        <v>1.8</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.11</v>
+        <v>3.02</v>
       </c>
       <c r="M20" t="n">
-        <v>8.800000000000001</v>
+        <v>3.68</v>
       </c>
       <c r="N20" t="n">
-        <v>19</v>
+        <v>2.14</v>
       </c>
       <c r="O20" t="n">
-        <v>1.42</v>
+        <v>3.56</v>
       </c>
       <c r="P20" t="n">
-        <v>3.13</v>
+        <v>2.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>12</v>
+        <v>2.5</v>
       </c>
       <c r="R20" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="S20" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="T20" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="U20" t="n">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="V20" t="n">
         <v>1.01</v>
       </c>
       <c r="W20" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X20" t="n">
-        <v>6.25</v>
+        <v>5.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.35</v>
+        <v>2.7</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.34</v>
+        <v>1.41</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.53</v>
+        <v>2.75</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>7.2</v>
+        <v>1.38</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="M21" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="N21" t="n">
-        <v>2.69</v>
+        <v>2.57</v>
       </c>
       <c r="O21" t="n">
         <v>3.5</v>
@@ -3138,31 +3138,31 @@
         <v>3.45</v>
       </c>
       <c r="R21" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="S21" t="n">
         <v>2.23</v>
       </c>
       <c r="T21" t="n">
-        <v>3.66</v>
+        <v>3.75</v>
       </c>
       <c r="U21" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="V21" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="W21" t="n">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="X21" t="n">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.4</v>
+        <v>2.94</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="AA21" t="n">
         <v>5.15</v>
@@ -3171,10 +3171,10 @@
         <v>1.1</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>1.4</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>

--- a/jogos_2025-09-18.xlsx
+++ b/jogos_2025-09-18.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK25"/>
+  <dimension ref="A1:AK23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="M2" t="n">
         <v>3.25</v>
@@ -678,13 +678,13 @@
         <v>2.4</v>
       </c>
       <c r="O2" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="R2" t="n">
         <v>1.41</v>
@@ -708,10 +708,10 @@
         <v>2.92</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AA2" t="n">
         <v>3.58</v>
@@ -720,10 +720,10 @@
         <v>1.21</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -742,10 +742,10 @@
         <v>1.39</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>45918.4375</v>
@@ -762,22 +762,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,16 +865,16 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45918.4375</v>
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O5" t="n">
-        <v>3.25</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.57</v>
+        <v>1.98</v>
       </c>
       <c r="R5" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="S5" t="n">
-        <v>2.06</v>
+        <v>2.41</v>
       </c>
       <c r="T5" t="n">
-        <v>4.2</v>
+        <v>3.34</v>
       </c>
       <c r="U5" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="V5" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="W5" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="X5" t="n">
-        <v>2.07</v>
+        <v>2.62</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.22</v>
+        <v>2.35</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.15</v>
+        <v>4.6</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.57</v>
+        <v>2.35</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,16 +1123,16 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.37</v>
+        <v>1.2</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.52</v>
+        <v>1.05</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45918.45833333334</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,83 +1185,83 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>6.5</v>
+        <v>2.33</v>
       </c>
       <c r="M6" t="n">
-        <v>3.6</v>
+        <v>2.82</v>
       </c>
       <c r="N6" t="n">
-        <v>1.48</v>
+        <v>3.28</v>
       </c>
       <c r="O6" t="n">
-        <v>7</v>
+        <v>3.16</v>
       </c>
       <c r="P6" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AI6" t="n">
         <v>2</v>
       </c>
-      <c r="Q6" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X6" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45918.45833333334</v>
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4.68</v>
+        <v>3.7</v>
       </c>
       <c r="M7" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="N7" t="n">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="O7" t="n">
         <v>4.8</v>
       </c>
       <c r="P7" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="R7" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="S7" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="T7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X7" t="n">
         <v>3</v>
       </c>
-      <c r="U7" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="X7" t="n">
-        <v>2.88</v>
-      </c>
       <c r="Y7" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.79</v>
+        <v>3.9</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AC7" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AI7" t="n">
         <v>2.75</v>
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.35</v>
+        <v>1.88</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="N8" t="n">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="O8" t="n">
-        <v>2.54</v>
+        <v>2.45</v>
       </c>
       <c r="P8" t="n">
-        <v>1.89</v>
+        <v>2.11</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.51</v>
+        <v>3.68</v>
       </c>
       <c r="R8" t="n">
-        <v>1.55</v>
+        <v>1.34</v>
       </c>
       <c r="S8" t="n">
-        <v>2.3</v>
+        <v>2.98</v>
       </c>
       <c r="T8" t="n">
-        <v>3.52</v>
+        <v>2.62</v>
       </c>
       <c r="U8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W8" t="n">
         <v>1.22</v>
       </c>
-      <c r="V8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.5</v>
-      </c>
       <c r="X8" t="n">
-        <v>2.39</v>
+        <v>3.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.49</v>
+        <v>1.79</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.42</v>
+        <v>1.92</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.95</v>
+        <v>2.92</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.11</v>
+        <v>1.31</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.23</v>
+        <v>1.69</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.57</v>
+        <v>2.04</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,19 +1510,19 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45918.47916666666</v>
+        <v>45918.52777777778</v>
       </c>
     </row>
     <row r="9">
@@ -1572,34 +1572,34 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="M9" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="N9" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="O9" t="n">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
       <c r="P9" t="n">
         <v>2.25</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.43</v>
+        <v>3.2</v>
       </c>
       <c r="R9" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S9" t="n">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="T9" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="U9" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="V9" t="n">
         <v>1</v>
@@ -1611,22 +1611,22 @@
         <v>3.7</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AA9" t="n">
         <v>2.92</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.39</v>
+        <v>1.24</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.01</v>
+        <v>3.23</v>
       </c>
       <c r="M10" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="N10" t="n">
-        <v>3.6</v>
+        <v>2.17</v>
       </c>
       <c r="O10" t="n">
-        <v>2.5</v>
+        <v>3.75</v>
       </c>
       <c r="P10" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.85</v>
+        <v>2.52</v>
       </c>
       <c r="R10" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S10" t="n">
-        <v>2.98</v>
+        <v>3.3</v>
       </c>
       <c r="T10" t="n">
-        <v>2.65</v>
+        <v>2.82</v>
       </c>
       <c r="U10" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="V10" t="n">
         <v>1.05</v>
       </c>
       <c r="W10" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X10" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.97</v>
+        <v>2.9</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>1.25</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.77</v>
+        <v>1.34</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45918.52777777778</v>
+        <v>45918.57291666666</v>
       </c>
     </row>
     <row r="11">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45918.54166666666</v>
+        <v>45918.57291666666</v>
       </c>
     </row>
     <row r="12">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.23</v>
+        <v>2.02</v>
       </c>
       <c r="M12" t="n">
-        <v>3.35</v>
+        <v>2.64</v>
       </c>
       <c r="N12" t="n">
-        <v>2.17</v>
+        <v>4.1</v>
       </c>
       <c r="O12" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.25</v>
+        <v>1.63</v>
       </c>
       <c r="X12" t="n">
-        <v>3.9</v>
+        <v>2.13</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.67</v>
+        <v>2.73</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45918.57291666666</v>
+        <v>45918.58333333334</v>
       </c>
     </row>
     <row r="13">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,62 +2088,62 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.55</v>
+        <v>1.43</v>
       </c>
       <c r="M13" t="n">
-        <v>3.72</v>
+        <v>3.85</v>
       </c>
       <c r="N13" t="n">
-        <v>2.44</v>
+        <v>6.8</v>
       </c>
       <c r="O13" t="n">
-        <v>3.33</v>
+        <v>2.06</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.96</v>
+        <v>7.4</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="S13" t="n">
-        <v>3.4</v>
+        <v>2.62</v>
       </c>
       <c r="T13" t="n">
-        <v>2.28</v>
+        <v>3.1</v>
       </c>
       <c r="U13" t="n">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="V13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W13" t="n">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="X13" t="n">
-        <v>4.5</v>
+        <v>2.78</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.73</v>
+        <v>2.25</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.1</v>
+        <v>1.61</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.6</v>
+        <v>3.96</v>
       </c>
       <c r="AB13" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AD13" t="n">
         <v>1.48</v>
       </c>
-      <c r="AC13" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AE13" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.44</v>
+        <v>2.78</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45918.57291666666</v>
+        <v>45918.58333333334</v>
       </c>
     </row>
     <row r="14">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>5.99</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W14" t="n">
-        <v>1.63</v>
+        <v>1.17</v>
       </c>
       <c r="X14" t="n">
-        <v>2.13</v>
+        <v>4.05</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.75</v>
+        <v>1.68</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.4</v>
+        <v>2.14</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45918.58333333334</v>
+        <v>45918.625</v>
       </c>
     </row>
     <row r="15">
@@ -2305,12 +2305,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.4</v>
+        <v>1.63</v>
       </c>
       <c r="M15" t="n">
-        <v>3.88</v>
+        <v>3.95</v>
       </c>
       <c r="N15" t="n">
-        <v>6.8</v>
+        <v>4.9</v>
       </c>
       <c r="O15" t="n">
-        <v>1.96</v>
+        <v>2.19</v>
       </c>
       <c r="P15" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>7</v>
+        <v>5.2</v>
       </c>
       <c r="R15" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="S15" t="n">
-        <v>2.55</v>
+        <v>3.25</v>
       </c>
       <c r="T15" t="n">
-        <v>3.2</v>
+        <v>2.43</v>
       </c>
       <c r="U15" t="n">
-        <v>1.33</v>
+        <v>1.54</v>
       </c>
       <c r="V15" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="W15" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="X15" t="n">
-        <v>2.78</v>
+        <v>4.3</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.2</v>
+        <v>1.58</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.62</v>
+        <v>2.35</v>
       </c>
       <c r="AA15" t="n">
-        <v>4.15</v>
+        <v>2.74</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.2</v>
+        <v>1.41</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.42</v>
+        <v>1.75</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.46</v>
+        <v>2.03</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.55</v>
+        <v>2.26</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45918.58333333334</v>
+        <v>45918.66666666666</v>
       </c>
     </row>
     <row r="16">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="O16" t="n">
-        <v>2.07</v>
+        <v>1.42</v>
       </c>
       <c r="P16" t="n">
-        <v>2.26</v>
+        <v>3.13</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.89</v>
+        <v>12</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="S16" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="T16" t="n">
-        <v>2.49</v>
+        <v>2</v>
       </c>
       <c r="U16" t="n">
-        <v>1.47</v>
+        <v>1.83</v>
       </c>
       <c r="V16" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="X16" t="n">
-        <v>3.98</v>
+        <v>6.25</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.7</v>
+        <v>1.31</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.08</v>
+        <v>3.27</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.69</v>
+        <v>1.87</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.42</v>
+        <v>1.87</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.78</v>
+        <v>2.34</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.48</v>
+        <v>7.2</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45918.625</v>
+        <v>45918.66666666666</v>
       </c>
     </row>
     <row r="17">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.11</v>
+        <v>2.02</v>
       </c>
       <c r="M17" t="n">
-        <v>8.800000000000001</v>
+        <v>3.85</v>
       </c>
       <c r="N17" t="n">
-        <v>19</v>
+        <v>3.17</v>
       </c>
       <c r="O17" t="n">
-        <v>1.42</v>
+        <v>2.49</v>
       </c>
       <c r="P17" t="n">
-        <v>3.13</v>
+        <v>2.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>12</v>
+        <v>3.6</v>
       </c>
       <c r="R17" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="S17" t="n">
-        <v>4.2</v>
+        <v>3.62</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="U17" t="n">
-        <v>1.83</v>
+        <v>1.64</v>
       </c>
       <c r="V17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W17" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X17" t="n">
-        <v>6.25</v>
+        <v>4.9</v>
       </c>
       <c r="Y17" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB17" t="n">
         <v>1.57</v>
       </c>
-      <c r="Z17" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.87</v>
-      </c>
       <c r="AC17" t="n">
-        <v>2.34</v>
+        <v>1.44</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.53</v>
+        <v>2.5</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="AH17" t="n">
-        <v>7.2</v>
+        <v>1.8</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.63</v>
+        <v>3.02</v>
       </c>
       <c r="M18" t="n">
-        <v>3.95</v>
+        <v>3.68</v>
       </c>
       <c r="N18" t="n">
-        <v>4.9</v>
+        <v>2.14</v>
       </c>
       <c r="O18" t="n">
-        <v>2.19</v>
+        <v>3.56</v>
       </c>
       <c r="P18" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.2</v>
+        <v>2.5</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="S18" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="T18" t="n">
-        <v>2.43</v>
+        <v>2.1</v>
       </c>
       <c r="U18" t="n">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="V18" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W18" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="X18" t="n">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.58</v>
+        <v>1.43</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.35</v>
+        <v>2.7</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.74</v>
+        <v>2.05</v>
       </c>
       <c r="AB18" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC18" t="n">
         <v>1.41</v>
       </c>
-      <c r="AC18" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AD18" t="n">
-        <v>2.03</v>
+        <v>2.75</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.26</v>
+        <v>1.38</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2821,27 +2821,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,62 +2862,62 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.02</v>
+        <v>1.84</v>
       </c>
       <c r="M19" t="n">
-        <v>3.85</v>
+        <v>2.95</v>
       </c>
       <c r="N19" t="n">
-        <v>3.17</v>
+        <v>4.2</v>
       </c>
       <c r="O19" t="n">
-        <v>2.49</v>
+        <v>2.65</v>
       </c>
       <c r="P19" t="n">
-        <v>2.3</v>
+        <v>1.92</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="R19" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="S19" t="n">
-        <v>3.62</v>
+        <v>2.35</v>
       </c>
       <c r="T19" t="n">
-        <v>2.25</v>
+        <v>3.5</v>
       </c>
       <c r="U19" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AD19" t="n">
         <v>1.64</v>
       </c>
-      <c r="V19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X19" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AE19" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.21</v>
+        <v>1.35</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45918.66666666666</v>
+        <v>45918.79166666666</v>
       </c>
     </row>
     <row r="20">
@@ -2950,27 +2950,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.02</v>
+        <v>2.5</v>
       </c>
       <c r="M20" t="n">
-        <v>3.68</v>
+        <v>2.88</v>
       </c>
       <c r="N20" t="n">
-        <v>2.14</v>
+        <v>2.69</v>
       </c>
       <c r="O20" t="n">
-        <v>3.56</v>
+        <v>3.4</v>
       </c>
       <c r="P20" t="n">
-        <v>2.5</v>
+        <v>1.74</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.5</v>
+        <v>3.32</v>
       </c>
       <c r="R20" t="n">
-        <v>1.22</v>
+        <v>1.61</v>
       </c>
       <c r="S20" t="n">
-        <v>3.7</v>
+        <v>2.23</v>
       </c>
       <c r="T20" t="n">
-        <v>2.1</v>
+        <v>3.66</v>
       </c>
       <c r="U20" t="n">
-        <v>1.65</v>
+        <v>1.25</v>
       </c>
       <c r="V20" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="W20" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="AB20" t="n">
         <v>1.1</v>
       </c>
-      <c r="X20" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.77</v>
-      </c>
       <c r="AC20" t="n">
-        <v>1.41</v>
+        <v>2.24</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.75</v>
+        <v>1.61</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45918.66666666666</v>
+        <v>45918.79166666666</v>
       </c>
     </row>
     <row r="21">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q21" t="n">
         <v>2.7</v>
       </c>
-      <c r="M21" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N21" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="O21" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>3.45</v>
-      </c>
       <c r="R21" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>3.75</v>
+        <v>2.18</v>
       </c>
       <c r="U21" t="n">
-        <v>1.26</v>
+        <v>1.64</v>
       </c>
       <c r="V21" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="X21" t="n">
-        <v>2.55</v>
+        <v>4.8</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.94</v>
+        <v>1.43</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.39</v>
+        <v>2.43</v>
       </c>
       <c r="AA21" t="n">
-        <v>5.15</v>
+        <v>2.16</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.1</v>
+        <v>1.58</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.1</v>
+        <v>1.48</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.62</v>
+        <v>2.5</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45918.79166666666</v>
+        <v>45918.85416666666</v>
       </c>
     </row>
     <row r="22">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.84</v>
+        <v>1.3</v>
       </c>
       <c r="M22" t="n">
-        <v>2.95</v>
+        <v>4</v>
       </c>
       <c r="N22" t="n">
-        <v>4.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O22" t="n">
-        <v>2.65</v>
+        <v>1.9</v>
       </c>
       <c r="P22" t="n">
-        <v>1.92</v>
+        <v>2.01</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.9</v>
+        <v>9.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="S22" t="n">
-        <v>2.35</v>
+        <v>2.43</v>
       </c>
       <c r="T22" t="n">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="U22" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="V22" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="W22" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="X22" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AA22" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.14</v>
+        <v>3.25</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.64</v>
+        <v>1.31</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.35</v>
+        <v>1.17</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.85</v>
+        <v>2.99</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45918.79166666666</v>
+        <v>45918.89583333334</v>
       </c>
     </row>
     <row r="23">
@@ -3337,12 +3337,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O23" t="n">
-        <v>3.35</v>
+        <v>3.64</v>
       </c>
       <c r="P23" t="n">
-        <v>2.45</v>
+        <v>2.12</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="T23" t="n">
-        <v>2.18</v>
+        <v>2.65</v>
       </c>
       <c r="U23" t="n">
-        <v>1.64</v>
+        <v>1.4</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W23" t="n">
-        <v>1.1</v>
+        <v>1.23</v>
       </c>
       <c r="X23" t="n">
-        <v>4.8</v>
+        <v>3.42</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.43</v>
+        <v>1.85</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.43</v>
+        <v>1.85</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.16</v>
+        <v>3.04</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.58</v>
+        <v>1.29</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.48</v>
+        <v>1.61</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3457,264 +3457,6 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45918.85416666666</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
-        <v>45918</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>South America Copa Libertadores</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Flamengo</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Estudiantes</t>
-        </is>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="M24" t="n">
-        <v>4</v>
-      </c>
-      <c r="N24" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="T24" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="X24" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK24" s="3" t="n">
-        <v>45918.89583333334</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
-        <v>45918</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Angel City</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Washington Spirit</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L25" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="M25" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N25" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="O25" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X25" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK25" s="3" t="n">
         <v>45918.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-09-18.xlsx
+++ b/jogos_2025-09-18.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK23"/>
+  <dimension ref="A1:AK24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.65</v>
+        <v>1.53</v>
       </c>
       <c r="M2" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="N2" t="n">
-        <v>2.4</v>
+        <v>5.8</v>
       </c>
       <c r="O2" t="n">
-        <v>3.34</v>
+        <v>2.11</v>
       </c>
       <c r="P2" t="n">
-        <v>2.01</v>
+        <v>2.12</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.12</v>
+        <v>5.8</v>
       </c>
       <c r="R2" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="S2" t="n">
-        <v>2.61</v>
+        <v>2.72</v>
       </c>
       <c r="T2" t="n">
-        <v>2.99</v>
+        <v>2.84</v>
       </c>
       <c r="U2" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="V2" t="n">
         <v>1.03</v>
       </c>
       <c r="W2" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="X2" t="n">
-        <v>2.92</v>
+        <v>3.14</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.58</v>
+        <v>3.28</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.39</v>
+        <v>2.24</v>
       </c>
       <c r="AI2" t="n">
-        <v>2.05</v>
+        <v>1.5</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>45918.4375</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,83 +798,83 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.53</v>
+        <v>2.65</v>
       </c>
       <c r="M3" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="N3" t="n">
-        <v>5.8</v>
+        <v>2.4</v>
       </c>
       <c r="O3" t="n">
-        <v>2.11</v>
+        <v>3.34</v>
       </c>
       <c r="P3" t="n">
-        <v>2.12</v>
+        <v>2.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.8</v>
+        <v>3.12</v>
       </c>
       <c r="R3" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="S3" t="n">
-        <v>2.72</v>
+        <v>2.61</v>
       </c>
       <c r="T3" t="n">
-        <v>2.84</v>
+        <v>2.99</v>
       </c>
       <c r="U3" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="V3" t="n">
         <v>1.03</v>
       </c>
       <c r="W3" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
         <v>1.27</v>
       </c>
-      <c r="X3" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="Y3" t="n">
+      <c r="AH3" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ3" t="n">
         <v>2</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>3</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45918.4375</v>
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="M8" t="n">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="N8" t="n">
-        <v>3.65</v>
+        <v>4.35</v>
       </c>
       <c r="O8" t="n">
-        <v>2.45</v>
+        <v>2.54</v>
       </c>
       <c r="P8" t="n">
-        <v>2.11</v>
+        <v>1.91</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.68</v>
+        <v>5.1</v>
       </c>
       <c r="R8" t="n">
-        <v>1.34</v>
+        <v>1.55</v>
       </c>
       <c r="S8" t="n">
-        <v>2.98</v>
+        <v>2.3</v>
       </c>
       <c r="T8" t="n">
-        <v>2.62</v>
+        <v>3.52</v>
       </c>
       <c r="U8" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="V8" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="W8" t="n">
-        <v>1.22</v>
+        <v>1.53</v>
       </c>
       <c r="X8" t="n">
-        <v>3.5</v>
+        <v>2.39</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.79</v>
+        <v>2.49</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.92</v>
+        <v>1.42</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.92</v>
+        <v>4.95</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.31</v>
+        <v>1.12</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.69</v>
+        <v>2.33</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.04</v>
+        <v>1.52</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,19 +1510,19 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45918.52777777778</v>
+        <v>45918.47916666666</v>
       </c>
     </row>
     <row r="9">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,28 +1572,28 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.4</v>
+        <v>1.88</v>
       </c>
       <c r="M9" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="N9" t="n">
-        <v>2.72</v>
+        <v>3.65</v>
       </c>
       <c r="O9" t="n">
-        <v>2.95</v>
+        <v>2.45</v>
       </c>
       <c r="P9" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.2</v>
+        <v>3.68</v>
       </c>
       <c r="R9" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="T9" t="n">
         <v>2.62</v>
@@ -1602,16 +1602,16 @@
         <v>1.4</v>
       </c>
       <c r="V9" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X9" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="Z9" t="n">
         <v>1.92</v>
@@ -1620,13 +1620,13 @@
         <v>2.92</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.44</v>
+        <v>1.9</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.23</v>
+        <v>2.4</v>
       </c>
       <c r="M10" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="N10" t="n">
-        <v>2.17</v>
+        <v>2.72</v>
       </c>
       <c r="O10" t="n">
-        <v>3.75</v>
+        <v>2.95</v>
       </c>
       <c r="P10" t="n">
         <v>2.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.52</v>
+        <v>3.2</v>
       </c>
       <c r="R10" t="n">
         <v>1.33</v>
       </c>
       <c r="S10" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="T10" t="n">
-        <v>2.82</v>
+        <v>2.62</v>
       </c>
       <c r="U10" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="V10" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="W10" t="n">
         <v>1.25</v>
       </c>
       <c r="X10" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45918.57291666666</v>
+        <v>45918.52777777778</v>
       </c>
     </row>
     <row r="11">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.02</v>
+        <v>3.23</v>
       </c>
       <c r="M12" t="n">
-        <v>2.64</v>
+        <v>3.35</v>
       </c>
       <c r="N12" t="n">
-        <v>4.1</v>
+        <v>2.17</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W12" t="n">
-        <v>1.63</v>
+        <v>1.25</v>
       </c>
       <c r="X12" t="n">
-        <v>2.13</v>
+        <v>3.9</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.73</v>
+        <v>1.77</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.4</v>
+        <v>1.98</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45918.58333333334</v>
+        <v>45918.57291666666</v>
       </c>
     </row>
     <row r="13">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O14" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.99</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.17</v>
+        <v>1.63</v>
       </c>
       <c r="X14" t="n">
-        <v>4.05</v>
+        <v>2.13</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.68</v>
+        <v>2.73</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.14</v>
+        <v>1.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45918.625</v>
+        <v>45918.58333333334</v>
       </c>
     </row>
     <row r="15">
@@ -2305,12 +2305,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>2.19</v>
+        <v>1.97</v>
       </c>
       <c r="P15" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.2</v>
+        <v>5.99</v>
       </c>
       <c r="R15" t="n">
         <v>1.3</v>
       </c>
       <c r="S15" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T15" t="n">
-        <v>2.43</v>
+        <v>2.49</v>
       </c>
       <c r="U15" t="n">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="V15" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W15" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="X15" t="n">
-        <v>4.3</v>
+        <v>4.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.35</v>
+        <v>2.14</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.74</v>
+        <v>2.69</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.26</v>
+        <v>2.51</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45918.66666666666</v>
+        <v>45918.625</v>
       </c>
     </row>
     <row r="16">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.11</v>
+        <v>3.02</v>
       </c>
       <c r="M16" t="n">
-        <v>8.800000000000001</v>
+        <v>3.68</v>
       </c>
       <c r="N16" t="n">
-        <v>19</v>
+        <v>2.14</v>
       </c>
       <c r="O16" t="n">
-        <v>1.42</v>
+        <v>3.56</v>
       </c>
       <c r="P16" t="n">
-        <v>3.13</v>
+        <v>2.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>12</v>
+        <v>2.5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="S16" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="T16" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="U16" t="n">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="V16" t="n">
         <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X16" t="n">
-        <v>6.25</v>
+        <v>5.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.27</v>
+        <v>2.7</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.34</v>
+        <v>1.41</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.53</v>
+        <v>2.75</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="AH16" t="n">
-        <v>7.2</v>
+        <v>1.38</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.02</v>
+        <v>1.11</v>
       </c>
       <c r="M17" t="n">
-        <v>3.85</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>3.17</v>
+        <v>19</v>
       </c>
       <c r="O17" t="n">
-        <v>2.49</v>
+        <v>1.42</v>
       </c>
       <c r="P17" t="n">
-        <v>2.3</v>
+        <v>3.13</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.6</v>
+        <v>12</v>
       </c>
       <c r="R17" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="S17" t="n">
-        <v>3.62</v>
+        <v>4.2</v>
       </c>
       <c r="T17" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="V17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W17" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X17" t="n">
-        <v>4.9</v>
+        <v>6.25</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.63</v>
+        <v>1.31</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.25</v>
+        <v>3.27</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.25</v>
+        <v>1.87</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.57</v>
+        <v>1.87</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.44</v>
+        <v>2.34</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.5</v>
+        <v>1.53</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.8</v>
+        <v>7.2</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.02</v>
+        <v>1.63</v>
       </c>
       <c r="M18" t="n">
-        <v>3.68</v>
+        <v>3.95</v>
       </c>
       <c r="N18" t="n">
-        <v>2.14</v>
+        <v>4.9</v>
       </c>
       <c r="O18" t="n">
-        <v>3.56</v>
+        <v>2.19</v>
       </c>
       <c r="P18" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.5</v>
+        <v>5.2</v>
       </c>
       <c r="R18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W18" t="n">
         <v>1.22</v>
       </c>
-      <c r="S18" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.1</v>
-      </c>
       <c r="X18" t="n">
-        <v>5.5</v>
+        <v>4.3</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.43</v>
+        <v>1.58</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.05</v>
+        <v>2.74</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.77</v>
+        <v>1.41</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.41</v>
+        <v>1.75</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.75</v>
+        <v>2.03</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.38</v>
+        <v>2.26</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2821,27 +2821,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.84</v>
+        <v>2.02</v>
       </c>
       <c r="M19" t="n">
-        <v>2.95</v>
+        <v>3.85</v>
       </c>
       <c r="N19" t="n">
-        <v>4.2</v>
+        <v>3.17</v>
       </c>
       <c r="O19" t="n">
-        <v>2.65</v>
+        <v>2.49</v>
       </c>
       <c r="P19" t="n">
-        <v>1.92</v>
+        <v>2.3</v>
       </c>
       <c r="Q19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X19" t="n">
         <v>4.9</v>
       </c>
-      <c r="R19" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="X19" t="n">
-        <v>2.6</v>
-      </c>
       <c r="Y19" t="n">
-        <v>2.45</v>
+        <v>1.63</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.55</v>
+        <v>2.25</v>
       </c>
       <c r="AA19" t="n">
-        <v>4.7</v>
+        <v>2.25</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.14</v>
+        <v>1.57</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.14</v>
+        <v>1.44</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.64</v>
+        <v>2.5</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.35</v>
+        <v>1.21</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45918.79166666666</v>
+        <v>45918.66666666666</v>
       </c>
     </row>
     <row r="20">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.5</v>
+        <v>1.84</v>
       </c>
       <c r="M20" t="n">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="N20" t="n">
-        <v>2.69</v>
+        <v>4.2</v>
       </c>
       <c r="O20" t="n">
-        <v>3.4</v>
+        <v>2.65</v>
       </c>
       <c r="P20" t="n">
-        <v>1.74</v>
+        <v>1.92</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.32</v>
+        <v>4.9</v>
       </c>
       <c r="R20" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="S20" t="n">
-        <v>2.23</v>
+        <v>2.35</v>
       </c>
       <c r="T20" t="n">
-        <v>3.66</v>
+        <v>3.5</v>
       </c>
       <c r="U20" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="V20" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="W20" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="X20" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Z20" t="n">
         <v>1.55</v>
       </c>
-      <c r="X20" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AA20" t="n">
-        <v>5.15</v>
+        <v>4.7</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.24</v>
+        <v>2.14</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.39</v>
+        <v>1.85</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,77 +3120,77 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="O21" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P21" t="n">
-        <v>2.45</v>
+        <v>1.74</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.7</v>
+        <v>3.32</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="T21" t="n">
-        <v>2.18</v>
+        <v>3.66</v>
       </c>
       <c r="U21" t="n">
-        <v>1.64</v>
+        <v>1.25</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W21" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="AB21" t="n">
         <v>1.1</v>
       </c>
-      <c r="X21" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="Y21" t="n">
+      <c r="AC21" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
         <v>1.43</v>
       </c>
-      <c r="Z21" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH21" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45918.85416666666</v>
+        <v>45918.79166666666</v>
       </c>
     </row>
     <row r="22">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>1.9</v>
+        <v>3.2</v>
       </c>
       <c r="P22" t="n">
-        <v>2.01</v>
+        <v>2.36</v>
       </c>
       <c r="Q22" t="n">
-        <v>9.5</v>
+        <v>2.61</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X22" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z22" t="n">
         <v>2.43</v>
       </c>
-      <c r="T22" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="X22" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AA22" t="n">
-        <v>4.8</v>
+        <v>2.16</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.13</v>
+        <v>1.58</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.25</v>
+        <v>1.48</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.31</v>
+        <v>2.6</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.17</v>
+        <v>1.59</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.99</v>
+        <v>1.36</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45918.89583333334</v>
+        <v>45918.85416666666</v>
       </c>
     </row>
     <row r="23">
@@ -3337,126 +3337,255 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>South America Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Estudiantes</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M23" t="n">
+        <v>4</v>
+      </c>
+      <c r="N23" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X23" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK23" s="3" t="n">
+        <v>45918.89583333334</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>45918</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
           <t>23:30</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Angel City</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>Washington Spirit</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="inlineStr">
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L23" t="n">
+      <c r="L24" t="n">
         <v>3.15</v>
       </c>
-      <c r="M23" t="n">
+      <c r="M24" t="n">
         <v>3.5</v>
       </c>
-      <c r="N23" t="n">
+      <c r="N24" t="n">
         <v>2.1</v>
       </c>
-      <c r="O23" t="n">
+      <c r="O24" t="n">
         <v>3.64</v>
       </c>
-      <c r="P23" t="n">
+      <c r="P24" t="n">
         <v>2.12</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="Q24" t="n">
         <v>2.9</v>
       </c>
-      <c r="R23" t="n">
+      <c r="R24" t="n">
         <v>1.35</v>
       </c>
-      <c r="S23" t="n">
+      <c r="S24" t="n">
         <v>2.89</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T24" t="n">
         <v>2.65</v>
       </c>
-      <c r="U23" t="n">
+      <c r="U24" t="n">
         <v>1.4</v>
       </c>
-      <c r="V23" t="n">
+      <c r="V24" t="n">
         <v>1.01</v>
       </c>
-      <c r="W23" t="n">
+      <c r="W24" t="n">
         <v>1.23</v>
       </c>
-      <c r="X23" t="n">
+      <c r="X24" t="n">
         <v>3.42</v>
       </c>
-      <c r="Y23" t="n">
+      <c r="Y24" t="n">
         <v>1.85</v>
       </c>
-      <c r="Z23" t="n">
+      <c r="Z24" t="n">
         <v>1.85</v>
       </c>
-      <c r="AA23" t="n">
+      <c r="AA24" t="n">
         <v>3.04</v>
       </c>
-      <c r="AB23" t="n">
+      <c r="AB24" t="n">
         <v>1.29</v>
       </c>
-      <c r="AC23" t="n">
+      <c r="AC24" t="n">
         <v>1.61</v>
       </c>
-      <c r="AD23" t="n">
+      <c r="AD24" t="n">
         <v>2.14</v>
       </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG23" t="n">
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
         <v>1.24</v>
       </c>
-      <c r="AH23" t="n">
+      <c r="AH24" t="n">
         <v>1.32</v>
       </c>
-      <c r="AI23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK23" s="3" t="n">
+      <c r="AI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK24" s="3" t="n">
         <v>45918.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-09-18.xlsx
+++ b/jogos_2025-09-18.xlsx
@@ -633,22 +633,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="M2" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="N2" t="n">
-        <v>5.8</v>
+        <v>4.33</v>
       </c>
       <c r="O2" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.8</v>
+        <v>1.58</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>45918.4375</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.65</v>
+        <v>1.48</v>
       </c>
       <c r="M3" t="n">
-        <v>3.25</v>
+        <v>3.43</v>
       </c>
       <c r="N3" t="n">
-        <v>2.4</v>
+        <v>5.42</v>
       </c>
       <c r="O3" t="n">
-        <v>3.34</v>
+        <v>2.11</v>
       </c>
       <c r="P3" t="n">
-        <v>2.01</v>
+        <v>2.12</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.12</v>
+        <v>5.8</v>
       </c>
       <c r="R3" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="S3" t="n">
-        <v>2.61</v>
+        <v>2.72</v>
       </c>
       <c r="T3" t="n">
-        <v>2.99</v>
+        <v>2.84</v>
       </c>
       <c r="U3" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="V3" t="n">
         <v>1.03</v>
       </c>
       <c r="W3" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="X3" t="n">
-        <v>2.92</v>
+        <v>3.08</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.58</v>
+        <v>3.28</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,16 +865,16 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.39</v>
+        <v>2.24</v>
       </c>
       <c r="AI3" t="n">
-        <v>2.05</v>
+        <v>1.5</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45918.4375</v>
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,16 +994,16 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45918.4375</v>
@@ -1065,7 +1065,7 @@
         <v>1.45</v>
       </c>
       <c r="O5" t="n">
-        <v>8.050000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="P5" t="n">
         <v>2</v>
@@ -1077,22 +1077,22 @@
         <v>1.5</v>
       </c>
       <c r="S5" t="n">
-        <v>2.41</v>
+        <v>2.55</v>
       </c>
       <c r="T5" t="n">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="U5" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="V5" t="n">
         <v>1.04</v>
       </c>
       <c r="W5" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="X5" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="Y5" t="n">
         <v>2.35</v>
@@ -1101,16 +1101,16 @@
         <v>1.53</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.6</v>
+        <v>4.15</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.35</v>
+        <v>2.48</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1185,28 +1185,28 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="M6" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="N6" t="n">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="O6" t="n">
-        <v>3.16</v>
+        <v>3.25</v>
       </c>
       <c r="P6" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.49</v>
+        <v>4.3</v>
       </c>
       <c r="R6" t="n">
         <v>1.67</v>
       </c>
       <c r="S6" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="T6" t="n">
         <v>4.1</v>
@@ -1215,31 +1215,31 @@
         <v>1.18</v>
       </c>
       <c r="V6" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="W6" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="X6" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.88</v>
+        <v>3.13</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AA6" t="n">
         <v>5.95</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.35</v>
+        <v>2.23</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AI6" t="n">
         <v>2</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.7</v>
+        <v>1.83</v>
       </c>
       <c r="M7" t="n">
-        <v>3.55</v>
+        <v>3</v>
       </c>
       <c r="N7" t="n">
-        <v>2</v>
+        <v>4.1</v>
       </c>
       <c r="O7" t="n">
-        <v>4.8</v>
+        <v>2.52</v>
       </c>
       <c r="P7" t="n">
-        <v>2.05</v>
+        <v>1.89</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.38</v>
+        <v>5.25</v>
       </c>
       <c r="R7" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="S7" t="n">
-        <v>2.6</v>
+        <v>2.23</v>
       </c>
       <c r="T7" t="n">
-        <v>3.1</v>
+        <v>3.52</v>
       </c>
       <c r="U7" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="V7" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="W7" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="X7" t="n">
-        <v>3</v>
+        <v>2.32</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.15</v>
+        <v>2.49</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.7</v>
+        <v>1.42</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.9</v>
+        <v>4.95</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.95</v>
+        <v>2.23</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,16 +1381,16 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.18</v>
+        <v>1.8</v>
       </c>
       <c r="AI7" t="n">
-        <v>2.75</v>
+        <v>1.65</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.57</v>
+        <v>2.81</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45918.47916666666</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.83</v>
+        <v>4.2</v>
       </c>
       <c r="M8" t="n">
-        <v>3.05</v>
+        <v>3.58</v>
       </c>
       <c r="N8" t="n">
-        <v>4.35</v>
+        <v>1.72</v>
       </c>
       <c r="O8" t="n">
-        <v>2.54</v>
+        <v>4.8</v>
       </c>
       <c r="P8" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.1</v>
+        <v>2.32</v>
       </c>
       <c r="R8" t="n">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="S8" t="n">
-        <v>2.3</v>
+        <v>2.68</v>
       </c>
       <c r="T8" t="n">
-        <v>3.52</v>
+        <v>3</v>
       </c>
       <c r="U8" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="V8" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="W8" t="n">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="X8" t="n">
-        <v>2.39</v>
+        <v>2.84</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.49</v>
+        <v>2.15</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.42</v>
+        <v>1.7</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.95</v>
+        <v>3.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,16 +1510,16 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.3</v>
+        <v>2.04</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.85</v>
+        <v>1.2</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.65</v>
+        <v>2.75</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.81</v>
+        <v>1.57</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45918.47916666666</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.88</v>
+        <v>2.4</v>
       </c>
       <c r="M9" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="N9" t="n">
-        <v>3.65</v>
+        <v>2.75</v>
       </c>
       <c r="O9" t="n">
-        <v>2.45</v>
+        <v>3</v>
       </c>
       <c r="P9" t="n">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.68</v>
+        <v>3.04</v>
       </c>
       <c r="R9" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S9" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="T9" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="U9" t="n">
         <v>1.4</v>
       </c>
       <c r="V9" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W9" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X9" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AA9" t="n">
         <v>2.92</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,16 +1639,16 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AH9" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AI9" t="n">
         <v>1.9</v>
       </c>
-      <c r="AI9" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45918.52777777778</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,22 +1701,22 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.4</v>
+        <v>1.88</v>
       </c>
       <c r="M10" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="N10" t="n">
-        <v>2.72</v>
+        <v>3.9</v>
       </c>
       <c r="O10" t="n">
-        <v>2.95</v>
+        <v>2.45</v>
       </c>
       <c r="P10" t="n">
         <v>2.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="R10" t="n">
         <v>1.33</v>
@@ -1725,37 +1725,37 @@
         <v>3</v>
       </c>
       <c r="T10" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="U10" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V10" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="W10" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="X10" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,16 +1768,16 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.44</v>
+        <v>1.9</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45918.52777777778</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.55</v>
+        <v>3.23</v>
       </c>
       <c r="M11" t="n">
-        <v>3.72</v>
+        <v>3.35</v>
       </c>
       <c r="N11" t="n">
-        <v>2.44</v>
+        <v>2.17</v>
       </c>
       <c r="O11" t="n">
-        <v>3.33</v>
+        <v>3.75</v>
       </c>
       <c r="P11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD11" t="n">
         <v>2.2</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>2.5</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1900,13 +1900,13 @@
         <v>1.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45918.57291666666</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.23</v>
+        <v>2.55</v>
       </c>
       <c r="M12" t="n">
-        <v>3.35</v>
+        <v>3.72</v>
       </c>
       <c r="N12" t="n">
-        <v>2.17</v>
+        <v>2.44</v>
       </c>
       <c r="O12" t="n">
-        <v>3.75</v>
+        <v>3.33</v>
       </c>
       <c r="P12" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.52</v>
+        <v>2.96</v>
       </c>
       <c r="R12" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S12" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="T12" t="n">
-        <v>2.82</v>
+        <v>2.28</v>
       </c>
       <c r="U12" t="n">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="V12" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="X12" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.67</v>
+        <v>1.51</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2029,13 +2029,13 @@
         <v>1.25</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45918.57291666666</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.43</v>
+        <v>2.02</v>
       </c>
       <c r="M13" t="n">
-        <v>3.85</v>
+        <v>2.64</v>
       </c>
       <c r="N13" t="n">
-        <v>6.8</v>
+        <v>4.1</v>
       </c>
       <c r="O13" t="n">
-        <v>2.06</v>
+        <v>2.75</v>
       </c>
       <c r="P13" t="n">
-        <v>2.08</v>
+        <v>1.83</v>
       </c>
       <c r="Q13" t="n">
-        <v>7.4</v>
+        <v>4.75</v>
       </c>
       <c r="R13" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="Z13" t="n">
         <v>1.4</v>
       </c>
-      <c r="X13" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1.61</v>
-      </c>
       <c r="AA13" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,16 +2155,16 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45918.58333333334</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,83 +2217,83 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.02</v>
+        <v>1.41</v>
       </c>
       <c r="M14" t="n">
-        <v>2.64</v>
+        <v>3.9</v>
       </c>
       <c r="N14" t="n">
-        <v>4.1</v>
+        <v>6.5</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>8.35</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W14" t="n">
-        <v>1.63</v>
+        <v>1.34</v>
       </c>
       <c r="X14" t="n">
-        <v>2.13</v>
+        <v>2.8</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.73</v>
+        <v>2.2</v>
       </c>
       <c r="Z14" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AI14" t="n">
         <v>1.4</v>
       </c>
-      <c r="AA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45918.58333333334</v>
@@ -2346,22 +2346,22 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O15" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="P15" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.99</v>
+        <v>5</v>
       </c>
       <c r="R15" t="n">
         <v>1.3</v>
@@ -2370,34 +2370,34 @@
         <v>3.2</v>
       </c>
       <c r="T15" t="n">
-        <v>2.49</v>
+        <v>2.45</v>
       </c>
       <c r="U15" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="V15" t="n">
         <v>1.03</v>
       </c>
       <c r="W15" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X15" t="n">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AD15" t="n">
         <v>1.95</v>
@@ -2413,16 +2413,16 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45918.625</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.02</v>
+        <v>1.63</v>
       </c>
       <c r="M16" t="n">
-        <v>3.68</v>
+        <v>3.95</v>
       </c>
       <c r="N16" t="n">
-        <v>2.14</v>
+        <v>4.9</v>
       </c>
       <c r="O16" t="n">
-        <v>3.56</v>
+        <v>2.19</v>
       </c>
       <c r="P16" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.5</v>
+        <v>5.2</v>
       </c>
       <c r="R16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W16" t="n">
         <v>1.22</v>
       </c>
-      <c r="S16" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.1</v>
-      </c>
       <c r="X16" t="n">
-        <v>5.5</v>
+        <v>4.3</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.43</v>
+        <v>1.58</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.05</v>
+        <v>2.74</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.77</v>
+        <v>1.41</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.41</v>
+        <v>1.75</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.75</v>
+        <v>2.03</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,16 +2542,16 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.38</v>
+        <v>2.26</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45918.66666666666</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.11</v>
+        <v>2.02</v>
       </c>
       <c r="M17" t="n">
-        <v>8.800000000000001</v>
+        <v>3.85</v>
       </c>
       <c r="N17" t="n">
-        <v>19</v>
+        <v>3.17</v>
       </c>
       <c r="O17" t="n">
-        <v>1.42</v>
+        <v>2.49</v>
       </c>
       <c r="P17" t="n">
-        <v>3.13</v>
+        <v>2.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>12</v>
+        <v>3.6</v>
       </c>
       <c r="R17" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="S17" t="n">
-        <v>4.2</v>
+        <v>3.62</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="U17" t="n">
-        <v>1.83</v>
+        <v>1.64</v>
       </c>
       <c r="V17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W17" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X17" t="n">
-        <v>6.25</v>
+        <v>4.9</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.31</v>
+        <v>1.63</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.27</v>
+        <v>2.25</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.87</v>
+        <v>2.25</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.87</v>
+        <v>1.57</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.34</v>
+        <v>1.44</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.53</v>
+        <v>2.5</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,16 +2671,16 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="AH17" t="n">
-        <v>7.2</v>
+        <v>1.8</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45918.66666666666</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.63</v>
+        <v>3.02</v>
       </c>
       <c r="M18" t="n">
-        <v>3.95</v>
+        <v>3.68</v>
       </c>
       <c r="N18" t="n">
-        <v>4.9</v>
+        <v>2.14</v>
       </c>
       <c r="O18" t="n">
-        <v>2.19</v>
+        <v>3.56</v>
       </c>
       <c r="P18" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.2</v>
+        <v>2.5</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="S18" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="T18" t="n">
-        <v>2.43</v>
+        <v>2.1</v>
       </c>
       <c r="U18" t="n">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="V18" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W18" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="X18" t="n">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.58</v>
+        <v>1.43</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.35</v>
+        <v>2.7</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.74</v>
+        <v>2.05</v>
       </c>
       <c r="AB18" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC18" t="n">
         <v>1.41</v>
       </c>
-      <c r="AC18" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AD18" t="n">
-        <v>2.03</v>
+        <v>2.75</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,16 +2800,16 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.26</v>
+        <v>1.38</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45918.66666666666</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.02</v>
+        <v>1.11</v>
       </c>
       <c r="M19" t="n">
-        <v>3.85</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="N19" t="n">
-        <v>3.17</v>
+        <v>19</v>
       </c>
       <c r="O19" t="n">
-        <v>2.49</v>
+        <v>1.42</v>
       </c>
       <c r="P19" t="n">
-        <v>2.3</v>
+        <v>3.13</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.6</v>
+        <v>12</v>
       </c>
       <c r="R19" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="S19" t="n">
-        <v>3.62</v>
+        <v>4.2</v>
       </c>
       <c r="T19" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="U19" t="n">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="V19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W19" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X19" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AI19" t="n">
         <v>1.12</v>
       </c>
-      <c r="X19" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45918.66666666666</v>
@@ -3064,10 +3064,10 @@
         <v>1.85</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45918.79166666666</v>
@@ -3129,28 +3129,28 @@
         <v>2.69</v>
       </c>
       <c r="O21" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P21" t="n">
         <v>1.74</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.32</v>
+        <v>3.6</v>
       </c>
       <c r="R21" t="n">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="S21" t="n">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="T21" t="n">
-        <v>3.66</v>
+        <v>3.75</v>
       </c>
       <c r="U21" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="V21" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="W21" t="n">
         <v>1.55</v>
@@ -3165,16 +3165,16 @@
         <v>1.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>5.15</v>
+        <v>6.38</v>
       </c>
       <c r="AB21" t="n">
         <v>1.1</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.24</v>
+        <v>2.19</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3451,10 +3451,10 @@
         <v>2.99</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45918.89583333334</v>
@@ -3519,7 +3519,7 @@
         <v>3.64</v>
       </c>
       <c r="P24" t="n">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="Q24" t="n">
         <v>2.9</v>
@@ -3531,10 +3531,10 @@
         <v>2.89</v>
       </c>
       <c r="T24" t="n">
-        <v>2.65</v>
+        <v>2.68</v>
       </c>
       <c r="U24" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="V24" t="n">
         <v>1.01</v>
@@ -3543,7 +3543,7 @@
         <v>1.23</v>
       </c>
       <c r="X24" t="n">
-        <v>3.42</v>
+        <v>3.65</v>
       </c>
       <c r="Y24" t="n">
         <v>1.85</v>
@@ -3552,7 +3552,7 @@
         <v>1.85</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.04</v>
+        <v>2.85</v>
       </c>
       <c r="AB24" t="n">
         <v>1.29</v>

--- a/jogos_2025-09-18.xlsx
+++ b/jogos_2025-09-18.xlsx
@@ -633,22 +633,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.73</v>
+        <v>1.48</v>
       </c>
       <c r="M2" t="n">
-        <v>3.25</v>
+        <v>3.43</v>
       </c>
       <c r="N2" t="n">
-        <v>4.33</v>
+        <v>5.42</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.58</v>
+        <v>1.76</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>45918.4375</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,83 +798,83 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.48</v>
+        <v>2.8</v>
       </c>
       <c r="M3" t="n">
-        <v>3.43</v>
+        <v>3.09</v>
       </c>
       <c r="N3" t="n">
-        <v>5.42</v>
+        <v>2.18</v>
       </c>
       <c r="O3" t="n">
-        <v>2.11</v>
+        <v>3.85</v>
       </c>
       <c r="P3" t="n">
-        <v>2.12</v>
+        <v>2.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.8</v>
+        <v>2.8</v>
       </c>
       <c r="R3" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="S3" t="n">
-        <v>2.72</v>
+        <v>2.61</v>
       </c>
       <c r="T3" t="n">
-        <v>2.84</v>
+        <v>2.99</v>
       </c>
       <c r="U3" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="V3" t="n">
         <v>1.03</v>
       </c>
       <c r="W3" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AH3" t="n">
         <v>1.28</v>
       </c>
-      <c r="X3" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="Y3" t="n">
+      <c r="AI3" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ3" t="n">
         <v>2</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>3</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45918.4375</v>
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.8</v>
+        <v>1.68</v>
       </c>
       <c r="M4" t="n">
-        <v>3.09</v>
+        <v>3.3</v>
       </c>
       <c r="N4" t="n">
-        <v>2.18</v>
+        <v>4.65</v>
       </c>
       <c r="O4" t="n">
-        <v>3.85</v>
+        <v>2.24</v>
       </c>
       <c r="P4" t="n">
-        <v>2.01</v>
+        <v>2.19</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.8</v>
+        <v>5.49</v>
       </c>
       <c r="R4" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S4" t="n">
-        <v>2.61</v>
+        <v>2.69</v>
       </c>
       <c r="T4" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="U4" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="V4" t="n">
         <v>1.03</v>
       </c>
       <c r="W4" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="X4" t="n">
-        <v>2.92</v>
+        <v>3.06</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.82</v>
+        <v>1.97</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,16 +994,16 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.58</v>
+        <v>1.25</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.28</v>
+        <v>2.04</v>
       </c>
       <c r="AI4" t="n">
-        <v>2.05</v>
+        <v>1.61</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2</v>
+        <v>2.87</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45918.4375</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,83 +1056,83 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>7</v>
+        <v>2.28</v>
       </c>
       <c r="M5" t="n">
-        <v>3.47</v>
+        <v>2.72</v>
       </c>
       <c r="N5" t="n">
-        <v>1.45</v>
+        <v>3.5</v>
       </c>
       <c r="O5" t="n">
-        <v>7.3</v>
+        <v>3.1</v>
       </c>
       <c r="P5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI5" t="n">
         <v>2</v>
       </c>
-      <c r="Q5" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>3.6</v>
-      </c>
       <c r="AJ5" t="n">
-        <v>1.44</v>
+        <v>2.45</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45918.45833333334</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.31</v>
+        <v>7.15</v>
       </c>
       <c r="M6" t="n">
-        <v>2.8</v>
+        <v>3.62</v>
       </c>
       <c r="N6" t="n">
-        <v>3.25</v>
+        <v>1.5</v>
       </c>
       <c r="O6" t="n">
-        <v>3.25</v>
+        <v>6.8</v>
       </c>
       <c r="P6" t="n">
-        <v>1.83</v>
+        <v>1.99</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.3</v>
+        <v>1.98</v>
       </c>
       <c r="R6" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="S6" t="n">
-        <v>2.13</v>
+        <v>2.55</v>
       </c>
       <c r="T6" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="U6" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="V6" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="W6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Z6" t="n">
         <v>1.57</v>
       </c>
-      <c r="X6" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AA6" t="n">
-        <v>5.95</v>
+        <v>4.15</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,16 +1252,16 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.55</v>
+        <v>1.05</v>
       </c>
       <c r="AI6" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="AJ6" t="n">
-        <v>2.45</v>
+        <v>1.44</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45918.45833333334</v>
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>4.2</v>
+        <v>4.68</v>
       </c>
       <c r="M8" t="n">
-        <v>3.58</v>
+        <v>3.68</v>
       </c>
       <c r="N8" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="O8" t="n">
-        <v>4.8</v>
+        <v>4.73</v>
       </c>
       <c r="P8" t="n">
         <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.32</v>
+        <v>2.6</v>
       </c>
       <c r="R8" t="n">
         <v>1.4</v>
       </c>
       <c r="S8" t="n">
-        <v>2.68</v>
+        <v>2.55</v>
       </c>
       <c r="T8" t="n">
         <v>3</v>
       </c>
       <c r="U8" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V8" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="W8" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="X8" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AC8" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>2.04</v>
+        <v>1.28</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AI8" t="n">
         <v>2.75</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.4</v>
+        <v>1.88</v>
       </c>
       <c r="M9" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="N9" t="n">
-        <v>2.75</v>
+        <v>3.9</v>
       </c>
       <c r="O9" t="n">
-        <v>3</v>
+        <v>2.45</v>
       </c>
       <c r="P9" t="n">
         <v>2.25</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.04</v>
+        <v>3.8</v>
       </c>
       <c r="R9" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
       </c>
       <c r="T9" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="U9" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V9" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="W9" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="X9" t="n">
-        <v>3.42</v>
+        <v>3.65</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1642,13 +1642,13 @@
         <v>1.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.51</v>
+        <v>1.9</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.9</v>
+        <v>1.61</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2</v>
+        <v>2.37</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45918.52777777778</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.88</v>
+        <v>2.4</v>
       </c>
       <c r="M10" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="N10" t="n">
-        <v>3.9</v>
+        <v>2.75</v>
       </c>
       <c r="O10" t="n">
-        <v>2.45</v>
+        <v>3</v>
       </c>
       <c r="P10" t="n">
         <v>2.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.8</v>
+        <v>3.04</v>
       </c>
       <c r="R10" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
       </c>
       <c r="T10" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="U10" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="V10" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="W10" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="X10" t="n">
-        <v>3.65</v>
+        <v>3.42</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>1.3</v>
       </c>
       <c r="AH10" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AI10" t="n">
         <v>1.9</v>
       </c>
-      <c r="AI10" t="n">
-        <v>1.61</v>
-      </c>
       <c r="AJ10" t="n">
-        <v>2.37</v>
+        <v>2</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45918.52777777778</v>
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="M13" t="n">
-        <v>2.64</v>
+        <v>2.75</v>
       </c>
       <c r="N13" t="n">
-        <v>4.1</v>
+        <v>4.09</v>
       </c>
       <c r="O13" t="n">
         <v>2.75</v>
@@ -2127,7 +2127,7 @@
         <v>2.13</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="Z13" t="n">
         <v>1.4</v>
@@ -2217,7 +2217,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="M14" t="n">
         <v>3.9</v>
@@ -2226,31 +2226,31 @@
         <v>6.5</v>
       </c>
       <c r="O14" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="P14" t="n">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.35</v>
+        <v>6.5</v>
       </c>
       <c r="R14" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="S14" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="T14" t="n">
         <v>3.15</v>
       </c>
       <c r="U14" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="V14" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="W14" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="X14" t="n">
         <v>2.8</v>
@@ -2262,16 +2262,16 @@
         <v>1.7</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.92</v>
+        <v>3.88</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AC14" t="n">
         <v>2.25</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>1.25</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.62</v>
+        <v>2.83</v>
       </c>
       <c r="AI14" t="n">
         <v>1.4</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X16" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Y16" t="n">
         <v>1.63</v>
       </c>
-      <c r="M16" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="N16" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="O16" t="n">
+      <c r="Z16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AJ16" t="n">
         <v>2.19</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X16" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>2.6</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45918.66666666666</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.02</v>
+        <v>1.63</v>
       </c>
       <c r="M17" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="N17" t="n">
-        <v>3.17</v>
+        <v>4.9</v>
       </c>
       <c r="O17" t="n">
-        <v>2.49</v>
+        <v>2.19</v>
       </c>
       <c r="P17" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.6</v>
+        <v>5.2</v>
       </c>
       <c r="R17" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S17" t="n">
-        <v>3.62</v>
+        <v>3.25</v>
       </c>
       <c r="T17" t="n">
-        <v>2.25</v>
+        <v>2.43</v>
       </c>
       <c r="U17" t="n">
-        <v>1.64</v>
+        <v>1.54</v>
       </c>
       <c r="V17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W17" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="X17" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.25</v>
+        <v>2.74</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.57</v>
+        <v>1.41</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.5</v>
+        <v>2.03</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,16 +2671,16 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.8</v>
+        <v>2.26</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.72</v>
+        <v>1.53</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.19</v>
+        <v>2.6</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45918.66666666666</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.02</v>
+        <v>1.11</v>
       </c>
       <c r="M18" t="n">
-        <v>3.68</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>2.14</v>
+        <v>19</v>
       </c>
       <c r="O18" t="n">
-        <v>3.56</v>
+        <v>1.42</v>
       </c>
       <c r="P18" t="n">
-        <v>2.5</v>
+        <v>3.13</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.5</v>
+        <v>12</v>
       </c>
       <c r="R18" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="S18" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="T18" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="U18" t="n">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="V18" t="n">
         <v>1.01</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X18" t="n">
-        <v>5.5</v>
+        <v>6.25</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.43</v>
+        <v>1.31</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.7</v>
+        <v>3.27</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.41</v>
+        <v>2.34</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.75</v>
+        <v>1.53</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,16 +2800,16 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.38</v>
+        <v>7.2</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.95</v>
+        <v>1.12</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.8</v>
+        <v>6</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45918.66666666666</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.11</v>
+        <v>3.02</v>
       </c>
       <c r="M19" t="n">
-        <v>8.800000000000001</v>
+        <v>3.68</v>
       </c>
       <c r="N19" t="n">
-        <v>19</v>
+        <v>2.14</v>
       </c>
       <c r="O19" t="n">
-        <v>1.42</v>
+        <v>3.56</v>
       </c>
       <c r="P19" t="n">
-        <v>3.13</v>
+        <v>2.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>12</v>
+        <v>2.5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="S19" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="T19" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="U19" t="n">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="V19" t="n">
         <v>1.01</v>
       </c>
       <c r="W19" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X19" t="n">
-        <v>6.25</v>
+        <v>5.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.27</v>
+        <v>2.7</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.34</v>
+        <v>1.41</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.53</v>
+        <v>2.75</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,16 +2929,16 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>7.2</v>
+        <v>1.38</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.12</v>
+        <v>1.95</v>
       </c>
       <c r="AJ19" t="n">
-        <v>6</v>
+        <v>1.8</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45918.66666666666</v>
@@ -3120,58 +3120,58 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.5</v>
+        <v>2.78</v>
       </c>
       <c r="M21" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="N21" t="n">
-        <v>2.69</v>
+        <v>2.85</v>
       </c>
       <c r="O21" t="n">
         <v>3.5</v>
       </c>
       <c r="P21" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="Q21" t="n">
         <v>3.6</v>
       </c>
       <c r="R21" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="S21" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="T21" t="n">
         <v>3.75</v>
       </c>
       <c r="U21" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="V21" t="n">
         <v>1.09</v>
       </c>
       <c r="W21" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="X21" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="AA21" t="n">
-        <v>6.38</v>
+        <v>6.48</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.19</v>
+        <v>2.27</v>
       </c>
       <c r="AD21" t="n">
         <v>1.62</v>
@@ -3187,16 +3187,16 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45918.79166666666</v>
@@ -3249,22 +3249,22 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O22" t="n">
         <v>3.2</v>
       </c>
       <c r="P22" t="n">
-        <v>2.36</v>
+        <v>2.45</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.61</v>
+        <v>2.7</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -3276,7 +3276,7 @@
         <v>2.18</v>
       </c>
       <c r="U22" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -3285,25 +3285,25 @@
         <v>1.14</v>
       </c>
       <c r="X22" t="n">
-        <v>4.8</v>
+        <v>5.45</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.43</v>
+        <v>2.7</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.58</v>
+        <v>1.72</v>
       </c>
       <c r="AC22" t="n">
         <v>1.48</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,16 +3316,16 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.59</v>
+        <v>1.25</v>
       </c>
       <c r="AH22" t="n">
         <v>1.36</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45918.85416666666</v>
@@ -3525,13 +3525,13 @@
         <v>2.9</v>
       </c>
       <c r="R24" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S24" t="n">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="T24" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="U24" t="n">
         <v>1.45</v>
@@ -3540,22 +3540,22 @@
         <v>1.01</v>
       </c>
       <c r="W24" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="X24" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AA24" t="n">
         <v>2.85</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AC24" t="n">
         <v>1.61</v>
@@ -3577,13 +3577,13 @@
         <v>1.24</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45918.97916666666</v>

--- a/jogos_2025-09-18.xlsx
+++ b/jogos_2025-09-18.xlsx
@@ -633,22 +633,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -665,35 +665,35 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.48</v>
+        <v>1.73</v>
       </c>
       <c r="M2" t="n">
-        <v>3.43</v>
+        <v>3.25</v>
       </c>
       <c r="N2" t="n">
-        <v>5.42</v>
+        <v>4.33</v>
       </c>
       <c r="O2" t="n">
-        <v>2.11</v>
+        <v>2.17</v>
       </c>
       <c r="P2" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.8</v>
+        <v>4.84</v>
       </c>
       <c r="R2" t="n">
         <v>1.38</v>
       </c>
       <c r="S2" t="n">
-        <v>2.72</v>
+        <v>2.55</v>
       </c>
       <c r="T2" t="n">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="U2" t="n">
         <v>1.35</v>
@@ -702,28 +702,28 @@
         <v>1.03</v>
       </c>
       <c r="W2" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="X2" t="n">
-        <v>3.08</v>
+        <v>2.74</v>
       </c>
       <c r="Y2" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.76</v>
+        <v>1.58</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.28</v>
+        <v>3.8</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.98</v>
+        <v>2.03</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.24</v>
+        <v>2.02</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>45918.4375</v>
@@ -781,33 +781,33 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="M3" t="n">
-        <v>3.09</v>
+        <v>3.35</v>
       </c>
       <c r="N3" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="O3" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="P3" t="n">
         <v>2.01</v>
@@ -816,16 +816,16 @@
         <v>2.8</v>
       </c>
       <c r="R3" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="S3" t="n">
-        <v>2.61</v>
+        <v>2.53</v>
       </c>
       <c r="T3" t="n">
-        <v>2.99</v>
+        <v>2.84</v>
       </c>
       <c r="U3" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="V3" t="n">
         <v>1.03</v>
@@ -834,41 +834,41 @@
         <v>1.31</v>
       </c>
       <c r="X3" t="n">
-        <v>2.92</v>
+        <v>2.87</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['72']</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['9', '29', '35', '47']</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.58</v>
+        <v>1.25</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AI3" t="n">
         <v>2.05</v>
@@ -891,119 +891,119 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="M4" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="N4" t="n">
-        <v>4.65</v>
+        <v>5.8</v>
       </c>
       <c r="O4" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="P4" t="n">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.49</v>
+        <v>5.71</v>
       </c>
       <c r="R4" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S4" t="n">
-        <v>2.69</v>
+        <v>2.57</v>
       </c>
       <c r="T4" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>['31', '43', '75']</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>3</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="X4" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>2.87</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45918.4375</v>
@@ -1039,94 +1039,94 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="M5" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="N5" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="O5" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="P5" t="n">
         <v>1.83</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.2</v>
+        <v>4.66</v>
       </c>
       <c r="R5" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="S5" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="T5" t="n">
         <v>4</v>
       </c>
       <c r="U5" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="V5" t="n">
         <v>1.15</v>
       </c>
       <c r="W5" t="n">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="X5" t="n">
         <v>2.1</v>
       </c>
       <c r="Y5" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.9</v>
+        <v>6.79</v>
       </c>
       <c r="AB5" t="n">
         <v>1.1</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['53', '90+5']</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['39', '79']</t>
         </is>
       </c>
       <c r="AG5" t="n">
         <v>1.44</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AI5" t="n">
         <v>2</v>
@@ -1171,75 +1171,75 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>7.15</v>
+        <v>7</v>
       </c>
       <c r="M6" t="n">
-        <v>3.62</v>
+        <v>3.47</v>
       </c>
       <c r="N6" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="O6" t="n">
-        <v>6.8</v>
+        <v>9.25</v>
       </c>
       <c r="P6" t="n">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="R6" t="n">
         <v>1.44</v>
       </c>
       <c r="S6" t="n">
-        <v>2.55</v>
+        <v>2.44</v>
       </c>
       <c r="T6" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U6" t="n">
         <v>1.33</v>
       </c>
       <c r="V6" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="W6" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="X6" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.12</v>
+        <v>2.35</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.15</v>
+        <v>3.9</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1248,11 +1248,11 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['7', '56']</t>
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AH6" t="n">
         <v>1.05</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,16 +1288,16 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -1310,87 +1310,87 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.83</v>
+        <v>4.2</v>
       </c>
       <c r="M7" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="O7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="T7" t="n">
         <v>3</v>
       </c>
-      <c r="N7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O7" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="R7" t="n">
+      <c r="U7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>['89']</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AJ7" t="n">
         <v>1.57</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="X7" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>2.81</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45918.47916666666</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,16 +1417,16 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1439,69 +1439,69 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>4.68</v>
+        <v>2.35</v>
       </c>
       <c r="M8" t="n">
-        <v>3.68</v>
+        <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>1.74</v>
+        <v>3.1</v>
       </c>
       <c r="O8" t="n">
-        <v>4.73</v>
+        <v>2.3</v>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.6</v>
+        <v>5.89</v>
       </c>
       <c r="R8" t="n">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="S8" t="n">
-        <v>2.55</v>
+        <v>2.34</v>
       </c>
       <c r="T8" t="n">
-        <v>3</v>
+        <v>3.52</v>
       </c>
       <c r="U8" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="V8" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W8" t="n">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="X8" t="n">
-        <v>2.9</v>
+        <v>2.25</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.2</v>
+        <v>2.54</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.62</v>
+        <v>1.43</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.9</v>
+        <v>4.85</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.71</v>
+        <v>1.56</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['61']</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -1510,16 +1510,16 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.26</v>
+        <v>1.9</v>
       </c>
       <c r="AI8" t="n">
-        <v>2.75</v>
+        <v>1.65</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.57</v>
+        <v>2.81</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45918.47916666666</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="M9" t="n">
-        <v>3.58</v>
+        <v>3.2</v>
       </c>
       <c r="N9" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="O9" t="n">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="P9" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.8</v>
+        <v>3.62</v>
       </c>
       <c r="R9" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="T9" t="n">
         <v>2.6</v>
       </c>
       <c r="U9" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="V9" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="W9" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="X9" t="n">
-        <v>3.65</v>
+        <v>3.52</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.94</v>
+        <v>3.4</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,16 +1639,16 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI9" t="n">
         <v>1.9</v>
       </c>
-      <c r="AI9" t="n">
-        <v>1.61</v>
-      </c>
       <c r="AJ9" t="n">
-        <v>2.37</v>
+        <v>2</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45918.52777777778</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,22 +1701,22 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="M10" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q10" t="n">
         <v>3.5</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="O10" t="n">
-        <v>3</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3.04</v>
       </c>
       <c r="R10" t="n">
         <v>1.35</v>
@@ -1725,37 +1725,37 @@
         <v>3</v>
       </c>
       <c r="T10" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="U10" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="V10" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="X10" t="n">
         <v>3.42</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,16 +1768,16 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.51</v>
+        <v>1.66</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.9</v>
+        <v>1.61</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2</v>
+        <v>2.37</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45918.52777777778</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,83 +2088,83 @@
         </is>
       </c>
       <c r="L13" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M13" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="N13" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="O13" t="n">
         <v>2.05</v>
       </c>
-      <c r="M13" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="N13" t="n">
-        <v>4.09</v>
-      </c>
-      <c r="O13" t="n">
-        <v>2.75</v>
-      </c>
       <c r="P13" t="n">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.75</v>
+        <v>7</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W13" t="n">
-        <v>1.63</v>
+        <v>1.32</v>
       </c>
       <c r="X13" t="n">
-        <v>2.13</v>
+        <v>2.9</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.75</v>
+        <v>2.08</v>
       </c>
       <c r="Z13" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AI13" t="n">
         <v>1.4</v>
       </c>
-      <c r="AA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AJ13" t="n">
-        <v>2.75</v>
+        <v>3.6</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45918.58333333334</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,58 +2217,58 @@
         </is>
       </c>
       <c r="L14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Z14" t="n">
         <v>1.4</v>
       </c>
-      <c r="M14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="N14" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O14" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AA14" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="AD14" t="n">
         <v>1.53</v>
@@ -2284,16 +2284,16 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="AJ14" t="n">
-        <v>3.6</v>
+        <v>2.75</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45918.58333333334</v>
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="M15" t="n">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="N15" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="O15" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="P15" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="Q15" t="n">
-        <v>5</v>
+        <v>6.55</v>
       </c>
       <c r="R15" t="n">
         <v>1.3</v>
       </c>
       <c r="S15" t="n">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="T15" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="U15" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="V15" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="X15" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="AH15" t="n">
         <v>2.5</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.02</v>
+        <v>1.11</v>
       </c>
       <c r="M16" t="n">
-        <v>3.85</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>3.17</v>
+        <v>19</v>
       </c>
       <c r="O16" t="n">
-        <v>2.49</v>
+        <v>1.42</v>
       </c>
       <c r="P16" t="n">
-        <v>2.3</v>
+        <v>3.13</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.6</v>
+        <v>12</v>
       </c>
       <c r="R16" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="S16" t="n">
-        <v>3.62</v>
+        <v>4.2</v>
       </c>
       <c r="T16" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="U16" t="n">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="V16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X16" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AI16" t="n">
         <v>1.12</v>
       </c>
-      <c r="X16" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AJ16" t="n">
-        <v>2.19</v>
+        <v>6</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45918.66666666666</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,83 +2604,83 @@
         </is>
       </c>
       <c r="L17" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X17" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Y17" t="n">
         <v>1.63</v>
       </c>
-      <c r="M17" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="N17" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="O17" t="n">
+      <c r="Z17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AJ17" t="n">
         <v>2.19</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X17" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>2.6</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45918.66666666666</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,83 +2733,83 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.11</v>
+        <v>1.63</v>
       </c>
       <c r="M18" t="n">
-        <v>8.800000000000001</v>
+        <v>3.95</v>
       </c>
       <c r="N18" t="n">
-        <v>19</v>
+        <v>4.9</v>
       </c>
       <c r="O18" t="n">
-        <v>1.42</v>
+        <v>2.19</v>
       </c>
       <c r="P18" t="n">
-        <v>3.13</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>12</v>
+        <v>5.2</v>
       </c>
       <c r="R18" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="S18" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="T18" t="n">
-        <v>2</v>
+        <v>2.43</v>
       </c>
       <c r="U18" t="n">
-        <v>1.83</v>
+        <v>1.54</v>
       </c>
       <c r="V18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W18" t="n">
-        <v>1.07</v>
+        <v>1.22</v>
       </c>
       <c r="X18" t="n">
-        <v>6.25</v>
+        <v>4.3</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.31</v>
+        <v>1.58</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.27</v>
+        <v>2.35</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.87</v>
+        <v>2.74</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.87</v>
+        <v>1.41</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.34</v>
+        <v>1.75</v>
       </c>
       <c r="AD18" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AI18" t="n">
         <v>1.53</v>
       </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AJ18" t="n">
-        <v>6</v>
+        <v>2.6</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45918.66666666666</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.84</v>
+        <v>2.9</v>
       </c>
       <c r="M20" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="N20" t="n">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="O20" t="n">
-        <v>2.65</v>
+        <v>3.52</v>
       </c>
       <c r="P20" t="n">
-        <v>1.92</v>
+        <v>1.74</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.9</v>
+        <v>3.46</v>
       </c>
       <c r="R20" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="S20" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="T20" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="U20" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="V20" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="W20" t="n">
-        <v>1.49</v>
+        <v>1.7</v>
       </c>
       <c r="X20" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.45</v>
+        <v>3.1</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="AA20" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.14</v>
+        <v>2.49</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.64</v>
+        <v>1.52</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,16 +3058,16 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.85</v>
+        <v>1.4</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.66</v>
+        <v>2.2</v>
       </c>
       <c r="AJ20" t="n">
-        <v>2.75</v>
+        <v>2.18</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45918.79166666666</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,83 +3120,83 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.78</v>
+        <v>1.84</v>
       </c>
       <c r="M21" t="n">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="N21" t="n">
-        <v>2.85</v>
+        <v>4.2</v>
       </c>
       <c r="O21" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="T21" t="n">
         <v>3.5</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3.75</v>
       </c>
       <c r="U21" t="n">
         <v>1.23</v>
       </c>
       <c r="V21" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="W21" t="n">
-        <v>1.6</v>
+        <v>1.49</v>
       </c>
       <c r="X21" t="n">
-        <v>2.23</v>
+        <v>2.6</v>
       </c>
       <c r="Y21" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AJ21" t="n">
         <v>2.75</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>6.48</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>2.18</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45918.79166666666</v>
@@ -3249,22 +3249,22 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.08</v>
+        <v>2.75</v>
       </c>
       <c r="M22" t="n">
-        <v>3.82</v>
+        <v>3.74</v>
       </c>
       <c r="N22" t="n">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="O22" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="P22" t="n">
         <v>2.45</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -3282,28 +3282,28 @@
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X22" t="n">
-        <v>5.45</v>
+        <v>5.15</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.7</v>
+        <v>2.46</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.02</v>
+        <v>2.23</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="AC22" t="n">
         <v>1.48</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3516,25 +3516,25 @@
         <v>2.1</v>
       </c>
       <c r="O24" t="n">
-        <v>3.64</v>
+        <v>3.4</v>
       </c>
       <c r="P24" t="n">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="Q24" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S24" t="n">
         <v>2.9</v>
       </c>
-      <c r="R24" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.94</v>
-      </c>
       <c r="T24" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="U24" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="V24" t="n">
         <v>1.01</v>
@@ -3543,25 +3543,25 @@
         <v>1.22</v>
       </c>
       <c r="X24" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AI24" t="n">
         <v>2.2</v>

--- a/jogos_2025-09-18.xlsx
+++ b/jogos_2025-09-18.xlsx
@@ -633,35 +633,35 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -669,83 +669,83 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.73</v>
+        <v>3.2</v>
       </c>
       <c r="M2" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N2" t="n">
-        <v>4.33</v>
+        <v>2.12</v>
       </c>
       <c r="O2" t="n">
-        <v>2.17</v>
+        <v>4</v>
       </c>
       <c r="P2" t="n">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.84</v>
+        <v>2.8</v>
       </c>
       <c r="R2" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S2" t="n">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="T2" t="n">
-        <v>3.1</v>
+        <v>2.84</v>
       </c>
       <c r="U2" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="V2" t="n">
         <v>1.03</v>
       </c>
       <c r="W2" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="X2" t="n">
-        <v>2.74</v>
+        <v>2.87</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.25</v>
+        <v>2.03</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.03</v>
+        <v>1.88</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['72']</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['9', '29', '35', '47']</t>
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.02</v>
+        <v>1.33</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.61</v>
+        <v>2.05</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2.87</v>
+        <v>2</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>45918.4375</v>
@@ -772,25 +772,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -798,83 +798,83 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.2</v>
+        <v>1.55</v>
       </c>
       <c r="M3" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="N3" t="n">
-        <v>2.12</v>
+        <v>5.8</v>
       </c>
       <c r="O3" t="n">
-        <v>4</v>
+        <v>2.26</v>
       </c>
       <c r="P3" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.8</v>
+        <v>5.71</v>
       </c>
       <c r="R3" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="S3" t="n">
-        <v>2.53</v>
+        <v>2.57</v>
       </c>
       <c r="T3" t="n">
-        <v>2.84</v>
+        <v>2.94</v>
       </c>
       <c r="U3" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="V3" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W3" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="X3" t="n">
-        <v>2.87</v>
+        <v>2.92</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.03</v>
+        <v>1.97</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="AB3" t="n">
         <v>1.22</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>['72']</t>
+          <t>['31', '43', '75']</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>['9', '29', '35', '47']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.33</v>
+        <v>2.02</v>
       </c>
       <c r="AI3" t="n">
-        <v>2.05</v>
+        <v>1.5</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45918.4375</v>
@@ -891,32 +891,32 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -927,65 +927,65 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="M4" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N4" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AA4" t="n">
         <v>3.8</v>
       </c>
-      <c r="N4" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="O4" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>5.71</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="X4" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>3.48</v>
-      </c>
       <c r="AB4" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.93</v>
+        <v>2.03</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>['31', '43', '75']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -994,16 +994,16 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AH4" t="n">
         <v>2.02</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="AJ4" t="n">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45918.4375</v>
@@ -1030,16 +1030,16 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>2</v>
@@ -1056,83 +1056,83 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.3</v>
+        <v>7</v>
       </c>
       <c r="M5" t="n">
-        <v>2.8</v>
+        <v>3.47</v>
       </c>
       <c r="N5" t="n">
-        <v>3.25</v>
+        <v>1.45</v>
       </c>
       <c r="O5" t="n">
-        <v>3.04</v>
+        <v>9.25</v>
       </c>
       <c r="P5" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.66</v>
+        <v>2.01</v>
       </c>
       <c r="R5" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="S5" t="n">
-        <v>2.15</v>
+        <v>2.44</v>
       </c>
       <c r="T5" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="U5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AB5" t="n">
         <v>1.18</v>
       </c>
-      <c r="V5" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>6.79</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AC5" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.51</v>
+        <v>1.41</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>['53', '90+5']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>['39', '79']</t>
+          <t>['7', '56']</t>
         </is>
       </c>
       <c r="AG5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AJ5" t="n">
         <v>1.44</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>2.45</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45918.45833333334</v>
@@ -1159,16 +1159,16 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
         <v>2</v>
@@ -1185,83 +1185,83 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>7</v>
+        <v>2.3</v>
       </c>
       <c r="M6" t="n">
-        <v>3.47</v>
+        <v>2.8</v>
       </c>
       <c r="N6" t="n">
-        <v>1.45</v>
+        <v>3.25</v>
       </c>
       <c r="O6" t="n">
-        <v>9.25</v>
+        <v>3.04</v>
       </c>
       <c r="P6" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.01</v>
+        <v>4.66</v>
       </c>
       <c r="R6" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>['53', '90+5']</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>['39', '79']</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
         <v>1.44</v>
       </c>
-      <c r="S6" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="X6" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>['7', '56']</t>
-        </is>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AH6" t="n">
-        <v>1.05</v>
+        <v>1.57</v>
       </c>
       <c r="AI6" t="n">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.44</v>
+        <v>2.45</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45918.45833333334</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,65 +1314,65 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4.2</v>
+        <v>2.35</v>
       </c>
       <c r="M7" t="n">
-        <v>3.58</v>
+        <v>3</v>
       </c>
       <c r="N7" t="n">
-        <v>1.72</v>
+        <v>3.1</v>
       </c>
       <c r="O7" t="n">
-        <v>4.2</v>
+        <v>2.3</v>
       </c>
       <c r="P7" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.66</v>
+        <v>5.89</v>
       </c>
       <c r="R7" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="S7" t="n">
-        <v>2.59</v>
+        <v>2.34</v>
       </c>
       <c r="T7" t="n">
-        <v>3</v>
+        <v>3.52</v>
       </c>
       <c r="U7" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="V7" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="W7" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="X7" t="n">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.15</v>
+        <v>2.54</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.7</v>
+        <v>1.43</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.32</v>
+        <v>4.85</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.8</v>
+        <v>1.56</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>['89']</t>
+          <t>['61']</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -1381,16 +1381,16 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.27</v>
+        <v>1.9</v>
       </c>
       <c r="AI7" t="n">
-        <v>2.75</v>
+        <v>1.65</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.57</v>
+        <v>2.81</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45918.47916666666</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,65 +1443,65 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.35</v>
+        <v>4.2</v>
       </c>
       <c r="M8" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="O8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="T8" t="n">
         <v>3</v>
       </c>
-      <c r="N8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O8" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="P8" t="n">
+      <c r="U8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC8" t="n">
         <v>1.91</v>
       </c>
-      <c r="Q8" t="n">
-        <v>5.89</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="X8" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AD8" t="n">
-        <v>1.56</v>
+        <v>1.8</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>['61']</t>
+          <t>['89']</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -1510,16 +1510,16 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.9</v>
+        <v>1.27</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.65</v>
+        <v>2.75</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.81</v>
+        <v>1.57</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45918.47916666666</v>
@@ -1555,20 +1555,20 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -1630,12 +1630,12 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['9', '51', '56', '70']</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['82']</t>
         </is>
       </c>
       <c r="AG9" t="n">
@@ -1684,20 +1684,20 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['11', '81']</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['23']</t>
         </is>
       </c>
       <c r="AG10" t="n">
@@ -1813,20 +1813,20 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L11" t="n">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['9', '86']</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['82', '90+1']</t>
         </is>
       </c>
       <c r="AG11" t="n">
@@ -1942,20 +1942,20 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -2017,12 +2017,12 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['32', '39', '42', '75']</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+1']</t>
         </is>
       </c>
       <c r="AG12" t="n">
@@ -2071,7 +2071,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L13" t="n">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['73']</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -2203,7 +2203,7 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -2213,7 +2213,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L14" t="n">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['71']</t>
         </is>
       </c>
       <c r="AG14" t="n">
@@ -2329,20 +2329,20 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L15" t="n">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['28']</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.11</v>
+        <v>2.02</v>
       </c>
       <c r="M16" t="n">
-        <v>8.800000000000001</v>
+        <v>3.85</v>
       </c>
       <c r="N16" t="n">
-        <v>19</v>
+        <v>3.17</v>
       </c>
       <c r="O16" t="n">
-        <v>1.42</v>
+        <v>2.49</v>
       </c>
       <c r="P16" t="n">
-        <v>3.13</v>
+        <v>2.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>12</v>
+        <v>3.6</v>
       </c>
       <c r="R16" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="S16" t="n">
-        <v>4.2</v>
+        <v>3.62</v>
       </c>
       <c r="T16" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="U16" t="n">
-        <v>1.83</v>
+        <v>1.64</v>
       </c>
       <c r="V16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W16" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X16" t="n">
-        <v>6.25</v>
+        <v>4.9</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.31</v>
+        <v>1.63</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.27</v>
+        <v>2.25</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.87</v>
+        <v>2.25</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.87</v>
+        <v>1.57</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.34</v>
+        <v>1.44</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.53</v>
+        <v>2.5</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,16 +2542,16 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="AH16" t="n">
-        <v>7.2</v>
+        <v>1.8</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.12</v>
+        <v>1.72</v>
       </c>
       <c r="AJ16" t="n">
-        <v>6</v>
+        <v>2.19</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45918.66666666666</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,83 +2604,83 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.02</v>
+        <v>3.02</v>
       </c>
       <c r="M17" t="n">
-        <v>3.85</v>
+        <v>3.68</v>
       </c>
       <c r="N17" t="n">
-        <v>3.17</v>
+        <v>2.14</v>
       </c>
       <c r="O17" t="n">
-        <v>2.49</v>
+        <v>3.56</v>
       </c>
       <c r="P17" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="R17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
         <v>1.25</v>
       </c>
-      <c r="S17" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X17" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AH17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ17" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>2.19</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45918.66666666666</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.02</v>
+        <v>1.11</v>
       </c>
       <c r="M19" t="n">
-        <v>3.68</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="N19" t="n">
-        <v>2.14</v>
+        <v>19</v>
       </c>
       <c r="O19" t="n">
-        <v>3.56</v>
+        <v>1.42</v>
       </c>
       <c r="P19" t="n">
-        <v>2.5</v>
+        <v>3.13</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.5</v>
+        <v>12</v>
       </c>
       <c r="R19" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="S19" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="T19" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="U19" t="n">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="V19" t="n">
         <v>1.01</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X19" t="n">
-        <v>5.5</v>
+        <v>6.25</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.43</v>
+        <v>1.31</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.7</v>
+        <v>3.27</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.41</v>
+        <v>2.34</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.75</v>
+        <v>1.53</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,16 +2929,16 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.38</v>
+        <v>7.2</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.95</v>
+        <v>1.12</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.8</v>
+        <v>6</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45918.66666666666</v>
@@ -3249,34 +3249,34 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.75</v>
+        <v>2.58</v>
       </c>
       <c r="M22" t="n">
-        <v>3.74</v>
+        <v>3.75</v>
       </c>
       <c r="N22" t="n">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="O22" t="n">
-        <v>3.35</v>
+        <v>3.08</v>
       </c>
       <c r="P22" t="n">
         <v>2.45</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.56</v>
+        <v>2.67</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="T22" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="U22" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -3288,22 +3288,22 @@
         <v>5.15</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.46</v>
+        <v>2.55</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.23</v>
+        <v>2.16</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AI22" t="n">
         <v>2.11</v>
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.15</v>
+        <v>2.84</v>
       </c>
       <c r="M24" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N24" t="n">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="O24" t="n">
         <v>3.4</v>
       </c>
       <c r="P24" t="n">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.7</v>
+        <v>2.61</v>
       </c>
       <c r="R24" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S24" t="n">
         <v>2.9</v>
       </c>
       <c r="T24" t="n">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="U24" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="V24" t="n">
         <v>1.01</v>
       </c>
       <c r="W24" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="X24" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AA24" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="AI24" t="n">
         <v>2.2</v>
